--- a/output/japan/report.xlsx
+++ b/output/japan/report.xlsx
@@ -1,32 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j1 table" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j1 next" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j1 outrights" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j1 positions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j2 table" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j2 next" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j2 outrights" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j2 positions" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j3 table" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j3 next" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j3 outrights" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j3 positions" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jfl table" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jfl next" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jfl outrights" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jfl positions" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="emperors_cup outrights" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="league_cup outrights" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Ratings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Parameters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="j1 table" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="j1 next" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="j1 outrights" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="j1 positions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="j2 table" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="j2 next" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="j2 outrights" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="j2 positions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="j3 table" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="j3 next" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="j3 outrights" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="j3 positions" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="jfl table" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="jfl next" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="jfl outrights" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="jfl positions" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="emperors_cup outrights" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="league_cup outrights" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,16 +36,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -56,7 +53,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -64,21 +61,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -448,27 +436,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>elo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>tilt</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>last_match</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>last_tournament</t>
         </is>
@@ -1558,18 +1546,18 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Gainare Tottori</t>
+          <t>Zweigen Kanazawa</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>1139</v>
       </c>
       <c r="C49" t="n">
-        <v>1.0785</v>
+        <v>1.0136</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1581,18 +1569,18 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Zweigen Kanazawa</t>
+          <t>Gainare Tottori</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>1139</v>
       </c>
       <c r="C50" t="n">
-        <v>1.0136</v>
+        <v>1.0785</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2064,18 +2052,18 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Matsue City</t>
+          <t>Reinmeer Aomori</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>953</v>
       </c>
       <c r="C71" t="n">
-        <v>0.9439</v>
+        <v>0.9447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2022-11-20</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2087,18 +2075,18 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Reinmeer Aomori</t>
+          <t>Matsue City</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>953</v>
       </c>
       <c r="C72" t="n">
-        <v>0.9447</v>
+        <v>0.9439</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2022-11-20</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2156,18 +2144,18 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Japan Soccer College</t>
+          <t>Beluga Rosso Iwami</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>934</v>
       </c>
       <c r="C75" t="n">
-        <v>0.9782</v>
+        <v>0.9939</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2179,18 +2167,18 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Beluga Rosso Iwami</t>
+          <t>Japan Soccer College</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>934</v>
       </c>
       <c r="C76" t="n">
-        <v>0.9939</v>
+        <v>0.9782</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2248,46 +2236,46 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ococias Kyoto</t>
+          <t>Urayasu</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>924</v>
       </c>
       <c r="C79" t="n">
-        <v>1.0239</v>
+        <v>0.9114</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Emperor Cup</t>
+          <t>JFL</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Urayasu</t>
+          <t>Ococias Kyoto</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>924</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9114</v>
+        <v>1.0239</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>JFL</t>
+          <t>Emperor Cup</t>
         </is>
       </c>
     </row>
@@ -3283,18 +3271,18 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sapporo University FC</t>
+          <t>Juntendo University</t>
         </is>
       </c>
       <c r="B124" t="n">
         <v>800</v>
       </c>
       <c r="C124" t="n">
-        <v>1.0017</v>
+        <v>1.0338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -3306,18 +3294,18 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Juntendo University</t>
+          <t>Sapporo University FC</t>
         </is>
       </c>
       <c r="B125" t="n">
         <v>800</v>
       </c>
       <c r="C125" t="n">
-        <v>1.0338</v>
+        <v>1.0017</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -3582,18 +3570,18 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FC Tokushima</t>
+          <t>Tonan Maebashi</t>
         </is>
       </c>
       <c r="B137" t="n">
         <v>780</v>
       </c>
       <c r="C137" t="n">
-        <v>1.03</v>
+        <v>1.058</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -3605,18 +3593,18 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Tonan Maebashi</t>
+          <t>FC Tokushima</t>
         </is>
       </c>
       <c r="B138" t="n">
         <v>780</v>
       </c>
       <c r="C138" t="n">
-        <v>1.058</v>
+        <v>1.03</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -3743,46 +3731,46 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Ryutsu Keizai Dragons</t>
+          <t>Saga LIXIL</t>
         </is>
       </c>
       <c r="B144" t="n">
         <v>765</v>
       </c>
       <c r="C144" t="n">
-        <v>1.2111</v>
+        <v>0.9917</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>JFL</t>
+          <t>Emperor Cup</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Saga LIXIL</t>
+          <t>Ryutsu Keizai Dragons</t>
         </is>
       </c>
       <c r="B145" t="n">
         <v>765</v>
       </c>
       <c r="C145" t="n">
-        <v>0.9917</v>
+        <v>1.2111</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2019-12-01</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Emperor Cup</t>
+          <t>JFL</t>
         </is>
       </c>
     </row>
@@ -4019,18 +4007,18 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Hokkaido Tokachi</t>
+          <t>Pacific University</t>
         </is>
       </c>
       <c r="B156" t="n">
         <v>735</v>
       </c>
       <c r="C156" t="n">
-        <v>0.9963</v>
+        <v>1.0026</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4042,18 +4030,18 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Pacific University</t>
+          <t>Hokkaido Tokachi</t>
         </is>
       </c>
       <c r="B157" t="n">
         <v>735</v>
       </c>
       <c r="C157" t="n">
-        <v>1.0026</v>
+        <v>0.9963</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -4548,18 +4536,18 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Konan University</t>
+          <t>Kanagawa University</t>
         </is>
       </c>
       <c r="B179" t="n">
         <v>620</v>
       </c>
       <c r="C179" t="n">
-        <v>0.9949</v>
+        <v>0.9789</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2016-09-03</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -4594,18 +4582,18 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Kanagawa University</t>
+          <t>Konan University</t>
         </is>
       </c>
       <c r="B181" t="n">
         <v>620</v>
       </c>
       <c r="C181" t="n">
-        <v>0.9789</v>
+        <v>0.9949</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2016-09-03</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -4640,18 +4628,18 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Fukuoka University FC</t>
+          <t>Ritsumeikan University SC</t>
         </is>
       </c>
       <c r="B183" t="n">
         <v>618</v>
       </c>
       <c r="C183" t="n">
-        <v>0.9488</v>
+        <v>1.0021</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -4663,18 +4651,18 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Ritsumeikan University SC</t>
+          <t>Fukuoka University FC</t>
         </is>
       </c>
       <c r="B184" t="n">
         <v>618</v>
       </c>
       <c r="C184" t="n">
-        <v>1.0021</v>
+        <v>0.9488</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -4847,18 +4835,18 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Rissho University</t>
+          <t>Akita University</t>
         </is>
       </c>
       <c r="B192" t="n">
         <v>598</v>
       </c>
       <c r="C192" t="n">
-        <v>0.9858</v>
+        <v>1.0857</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2022-05-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -4870,18 +4858,18 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Akita University</t>
+          <t>Rissho University</t>
         </is>
       </c>
       <c r="B193" t="n">
         <v>598</v>
       </c>
       <c r="C193" t="n">
-        <v>1.0857</v>
+        <v>0.9858</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2022-05-22</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -4939,18 +4927,18 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>North Asia University</t>
+          <t>Hokkaido University</t>
         </is>
       </c>
       <c r="B196" t="n">
         <v>596</v>
       </c>
       <c r="C196" t="n">
-        <v>1.051</v>
+        <v>0.9827</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2019-05-26</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -4962,18 +4950,18 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Hokkaido University</t>
+          <t>North Asia University</t>
         </is>
       </c>
       <c r="B197" t="n">
         <v>596</v>
       </c>
       <c r="C197" t="n">
-        <v>0.9827</v>
+        <v>1.051</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2019-05-26</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -5181,117 +5169,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>exp_pts</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>exp_pos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>P12</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>P13</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>P14</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>P15</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>P16</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>P17</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>P18</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>P19</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>P20</t>
         </is>
@@ -6772,52 +6760,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>GF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>GD</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Pts</t>
         </is>
@@ -7518,97 +7506,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>away</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>home_elo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>away_elo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_diff_adj</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_tilt</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>away_tilt</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>probX</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>expg1</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>expg2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>odds1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>oddsX</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>odds2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>oddsO25</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>oddsU25</t>
         </is>
@@ -8929,67 +8917,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Winner %</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Winner Yes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Winner No</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Top 2 %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Top 2 Yes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Top 2 No</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Top 6 %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Top 6 Yes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Top 6 No</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Bottom 2 %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Bottom 2 Yes</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Bottom 2 No</t>
         </is>
@@ -9840,117 +9828,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>exp_pts</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>exp_pos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>P12</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>P13</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>P14</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>P15</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>P16</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>P17</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>P18</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>P19</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>P20</t>
         </is>
@@ -11431,52 +11419,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>GF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>GD</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Pts</t>
         </is>
@@ -12041,97 +12029,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>away</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>home_elo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>away_elo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_diff_adj</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_tilt</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>away_tilt</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>probX</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>expg1</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>expg2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>odds1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>oddsX</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>odds2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>oddsO25</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>oddsU25</t>
         </is>
@@ -12672,52 +12660,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Winner %</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Winner Yes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Winner No</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Top 4 %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Top 4 Yes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Top 4 No</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Bottom 2 %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Bottom 2 Yes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Bottom 2 No</t>
         </is>
@@ -13278,97 +13266,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>exp_pts</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>exp_pos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>P12</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>P13</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>P14</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>P15</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>P16</t>
         </is>
@@ -14365,67 +14353,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Reach QF %</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Reach QF Yes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Reach QF No</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Reach SF %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Reach SF Yes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Reach SF No</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Reach Final %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Reach Final Yes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Reach Final No</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Winner %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Winner Yes</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Winner No</t>
         </is>
@@ -15130,62 +15118,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tournament</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>matches</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>hfa_elo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>draw_rate</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>avg_goals_x</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>season_matches</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>season_hfa_elo</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>season_draw_rate</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>season_avg_goals</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>elo_hfa</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>avg_goals_y</t>
         </is>
@@ -15888,67 +15876,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Reach QF %</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Reach QF Yes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Reach QF No</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Reach SF %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Reach SF Yes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Reach SF No</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Reach Final %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Reach Final Yes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Reach Final No</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Winner %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Winner Yes</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Winner No</t>
         </is>
@@ -16559,23 +16547,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Gainare Tottori</t>
+          <t>Matsumoto Yamaga</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18.3</v>
+        <v>17.7</v>
       </c>
       <c r="C16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="F16" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G16" t="n">
         <v>1.02</v>
@@ -16584,7 +16572,7 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>201</v>
+        <v>251</v>
       </c>
       <c r="J16" t="n">
         <v>1.002</v>
@@ -16602,23 +16590,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Matsumoto Yamaga</t>
+          <t>Gainare Tottori</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.7</v>
+        <v>18.3</v>
       </c>
       <c r="C17" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="F17" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G17" t="n">
         <v>1.02</v>
@@ -16627,7 +16615,7 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>251</v>
+        <v>201</v>
       </c>
       <c r="J17" t="n">
         <v>1.002</v>
@@ -16657,52 +16645,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>GF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>GD</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Pts</t>
         </is>
@@ -17403,97 +17391,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>away</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>home_elo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>away_elo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_diff_adj</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_tilt</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>away_tilt</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>probX</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>expg1</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>expg2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>odds1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>oddsX</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>odds2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>oddsO25</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>oddsU25</t>
         </is>
@@ -18814,52 +18802,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Winner %</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Winner Yes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Winner No</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Top 3 %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Top 3 Yes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Top 3 No</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Relegation %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Relegation Yes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Relegation No</t>
         </is>
@@ -19520,117 +19508,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>exp_pts</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>exp_pos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>P12</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>P13</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>P14</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>P15</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>P16</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>P17</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>P18</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>P19</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>P20</t>
         </is>
@@ -21111,52 +21099,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>GF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>GD</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Pts</t>
         </is>
@@ -21857,97 +21845,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>away</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>home_elo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>away_elo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_diff_adj</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_tilt</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>away_tilt</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>probX</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>expg1</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>expg2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>odds1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>oddsX</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>odds2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>oddsO25</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>oddsU25</t>
         </is>
@@ -23268,67 +23256,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Winner %</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Winner Yes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Winner No</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Top 2 %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Top 2 Yes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Top 2 No</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Top 6 %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Top 6 Yes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Top 6 No</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Relegation %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Relegation Yes</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Relegation No</t>
         </is>

--- a/output/japan/report.xlsx
+++ b/output/japan/report.xlsx
@@ -7652,19 +7652,19 @@
         <v>0.7615</v>
       </c>
       <c r="O2" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="P2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R2" t="n">
         <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="3">
@@ -7717,13 +7717,13 @@
         <v>0.6294</v>
       </c>
       <c r="O3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="P3" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
         <v>1.5</v>
@@ -7782,19 +7782,19 @@
         <v>0.395</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="5">
@@ -7847,19 +7847,19 @@
         <v>0.585</v>
       </c>
       <c r="O5" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="P5" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S5" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="6">
@@ -7912,19 +7912,19 @@
         <v>0.513</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="P6" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
         <v>1.8</v>
       </c>
       <c r="S6" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="7">
@@ -7977,13 +7977,13 @@
         <v>0.4117</v>
       </c>
       <c r="O7" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R7" t="n">
         <v>2.2</v>
@@ -8042,16 +8042,16 @@
         <v>0.5422</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -8107,13 +8107,13 @@
         <v>0.3996</v>
       </c>
       <c r="O9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P9" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
         <v>2.25</v>
@@ -8172,19 +8172,19 @@
         <v>0.4375</v>
       </c>
       <c r="O10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P10" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R10" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="11">
@@ -8237,19 +8237,19 @@
         <v>0.4168</v>
       </c>
       <c r="O11" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="12">
@@ -8302,19 +8302,19 @@
         <v>0.6992</v>
       </c>
       <c r="O12" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="P12" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R12" t="n">
         <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="13">
@@ -8367,19 +8367,19 @@
         <v>0.4276</v>
       </c>
       <c r="O13" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="P13" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S13" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="14">
@@ -8435,16 +8435,16 @@
         <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="R14" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="15">
@@ -8497,16 +8497,16 @@
         <v>0.5594</v>
       </c>
       <c r="O15" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="P15" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S15" t="n">
         <v>2.05</v>
@@ -8562,19 +8562,19 @@
         <v>0.586</v>
       </c>
       <c r="O16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q16" t="n">
         <v>2.45</v>
       </c>
-      <c r="P16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.4</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S16" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="17">
@@ -8627,19 +8627,19 @@
         <v>0.4978</v>
       </c>
       <c r="O17" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="P17" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="R17" t="n">
         <v>1.85</v>
       </c>
       <c r="S17" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="18">
@@ -8692,19 +8692,19 @@
         <v>0.5224</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P18" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q18" t="n">
         <v>1.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="S18" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="19">
@@ -8757,19 +8757,19 @@
         <v>0.4799</v>
       </c>
       <c r="O19" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="P19" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="R19" t="n">
         <v>1.9</v>
       </c>
       <c r="S19" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="20">
@@ -8822,19 +8822,19 @@
         <v>0.4468</v>
       </c>
       <c r="O20" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="P20" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S20" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="21">
@@ -8887,13 +8887,13 @@
         <v>0.4307</v>
       </c>
       <c r="O21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P21" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="R21" t="n">
         <v>2.1</v>
@@ -12175,16 +12175,16 @@
         <v>0.404</v>
       </c>
       <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="n">
         <v>3.85</v>
       </c>
-      <c r="P2" t="n">
-        <v>3.75</v>
-      </c>
       <c r="Q2" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S2" t="n">
         <v>1.57</v>
@@ -12240,19 +12240,19 @@
         <v>0.395</v>
       </c>
       <c r="O3" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="P3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="4">
@@ -12308,16 +12308,16 @@
         <v>1.53</v>
       </c>
       <c r="P4" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="S4" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="5">
@@ -12370,16 +12370,16 @@
         <v>0.3668</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q5" t="n">
         <v>2.05</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S5" t="n">
         <v>1.5</v>
@@ -12435,19 +12435,19 @@
         <v>0.5027</v>
       </c>
       <c r="O6" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="P6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="R6" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S6" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="7">
@@ -12500,13 +12500,13 @@
         <v>0.4098</v>
       </c>
       <c r="O7" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="P7" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="R7" t="n">
         <v>2.2</v>
@@ -12565,19 +12565,19 @@
         <v>0.714</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="P8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="R8" t="n">
         <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="9">
@@ -12630,13 +12630,13 @@
         <v>0.346</v>
       </c>
       <c r="O9" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="R9" t="n">
         <v>2.55</v>
@@ -17537,13 +17537,13 @@
         <v>0.5906</v>
       </c>
       <c r="O2" t="n">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="P2" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="R2" t="n">
         <v>1.6</v>
@@ -17602,13 +17602,13 @@
         <v>0.3536</v>
       </c>
       <c r="O3" t="n">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="P3" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="R3" t="n">
         <v>2.5</v>
@@ -17667,16 +17667,16 @@
         <v>0.3514</v>
       </c>
       <c r="O4" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S4" t="n">
         <v>1.47</v>
@@ -17735,16 +17735,16 @@
         <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="6">
@@ -17797,19 +17797,19 @@
         <v>0.5374</v>
       </c>
       <c r="O6" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="P6" t="n">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="S6" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -17862,13 +17862,13 @@
         <v>0.6456</v>
       </c>
       <c r="O7" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="P7" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
         <v>1.47</v>
@@ -17927,13 +17927,13 @@
         <v>0.4839</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
         <v>1.9</v>
@@ -17992,19 +17992,19 @@
         <v>0.5732</v>
       </c>
       <c r="O9" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="P9" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="R9" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="S9" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="10">
@@ -18057,13 +18057,13 @@
         <v>0.4807</v>
       </c>
       <c r="O10" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="P10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="R10" t="n">
         <v>1.9</v>
@@ -18122,16 +18122,16 @@
         <v>0.4034</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S11" t="n">
         <v>1.57</v>
@@ -18187,10 +18187,10 @@
         <v>0.519</v>
       </c>
       <c r="O12" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="P12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q12" t="n">
         <v>2.75</v>
@@ -18252,13 +18252,13 @@
         <v>0.5692</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R13" t="n">
         <v>1.65</v>
@@ -18317,19 +18317,19 @@
         <v>0.417</v>
       </c>
       <c r="O14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S14" t="n">
         <v>1.62</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.6</v>
       </c>
     </row>
     <row r="15">
@@ -18382,19 +18382,19 @@
         <v>0.4049</v>
       </c>
       <c r="O15" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P15" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S15" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="16">
@@ -18447,16 +18447,16 @@
         <v>0.5659</v>
       </c>
       <c r="O16" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P16" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q16" t="n">
         <v>2.15</v>
       </c>
       <c r="R16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S16" t="n">
         <v>2.1</v>
@@ -18512,19 +18512,19 @@
         <v>0.5052</v>
       </c>
       <c r="O17" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="P17" t="n">
         <v>4</v>
       </c>
-      <c r="P17" t="n">
-        <v>3.8</v>
-      </c>
       <c r="Q17" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R17" t="n">
         <v>1.83</v>
       </c>
       <c r="S17" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="18">
@@ -18580,10 +18580,10 @@
         <v>1.75</v>
       </c>
       <c r="P18" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
         <v>2.1</v>
@@ -18642,16 +18642,16 @@
         <v>0.4229</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="P19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S19" t="n">
         <v>1.62</v>
@@ -18707,16 +18707,16 @@
         <v>0.554</v>
       </c>
       <c r="O20" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="S20" t="n">
         <v>2.05</v>
@@ -18772,19 +18772,19 @@
         <v>0.5358000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="P21" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="S21" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -21991,13 +21991,13 @@
         <v>0.4529</v>
       </c>
       <c r="O2" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="P2" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
         <v>2</v>
@@ -22056,16 +22056,16 @@
         <v>0.4019</v>
       </c>
       <c r="O3" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="P3" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S3" t="n">
         <v>1.57</v>
@@ -22121,19 +22121,19 @@
         <v>0.6153</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P4" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="R4" t="n">
         <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="5">
@@ -22186,19 +22186,19 @@
         <v>0.4365</v>
       </c>
       <c r="O5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R5" t="n">
         <v>2.1</v>
       </c>
-      <c r="P5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.05</v>
-      </c>
       <c r="S5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="6">
@@ -22251,19 +22251,19 @@
         <v>0.3043</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="P6" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="S6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="7">
@@ -22316,19 +22316,19 @@
         <v>0.5128</v>
       </c>
       <c r="O7" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="R7" t="n">
         <v>1.8</v>
       </c>
       <c r="S7" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="8">
@@ -22381,13 +22381,13 @@
         <v>0.3178</v>
       </c>
       <c r="O8" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R8" t="n">
         <v>2.75</v>
@@ -22446,19 +22446,19 @@
         <v>0.5076000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="P9" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S9" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="10">
@@ -22514,10 +22514,10 @@
         <v>2.05</v>
       </c>
       <c r="P10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R10" t="n">
         <v>1.8</v>
@@ -22576,13 +22576,13 @@
         <v>0.3985</v>
       </c>
       <c r="O11" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="P11" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="R11" t="n">
         <v>2.25</v>
@@ -22641,19 +22641,19 @@
         <v>0.5649</v>
       </c>
       <c r="O12" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="P12" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="R12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S12" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -22706,19 +22706,19 @@
         <v>0.4287</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P13" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
         <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="14">
@@ -22771,19 +22771,19 @@
         <v>0.51</v>
       </c>
       <c r="O14" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S14" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="15">
@@ -22836,19 +22836,19 @@
         <v>0.6424</v>
       </c>
       <c r="O15" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="P15" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="R15" t="n">
         <v>1.47</v>
       </c>
       <c r="S15" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="16">
@@ -22901,19 +22901,19 @@
         <v>0.4383</v>
       </c>
       <c r="O16" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="P16" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="17">
@@ -22966,19 +22966,19 @@
         <v>0.4476</v>
       </c>
       <c r="O17" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P17" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S17" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="18">
@@ -23031,16 +23031,16 @@
         <v>0.3783</v>
       </c>
       <c r="O18" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="P18" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="R18" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="S18" t="n">
         <v>1.53</v>
@@ -23096,16 +23096,16 @@
         <v>0.3685</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="P19" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S19" t="n">
         <v>1.5</v>
@@ -23161,19 +23161,19 @@
         <v>0.2823</v>
       </c>
       <c r="O20" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="P20" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="S20" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="21">
@@ -23226,19 +23226,19 @@
         <v>0.4059</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="P21" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S21" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan/report.xlsx
+++ b/output/japan/report.xlsx
@@ -607,10 +607,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1507</v>
+        <v>1504</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0958</v>
+        <v>1.0961</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0176</v>
+        <v>1.0214</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4451,11 +4451,11 @@
         <v>661</v>
       </c>
       <c r="C175" t="n">
-        <v>1.0153</v>
+        <v>1.0119</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -14426,37 +14426,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>67.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="D2" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="E2" t="n">
-        <v>43.6</v>
+        <v>41.6</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G2" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="H2" t="n">
-        <v>26.9</v>
+        <v>26</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="K2" t="n">
-        <v>16.3</v>
+        <v>15.9</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="M2" t="n">
         <v>1.17</v>
@@ -14465,29 +14465,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63.3</v>
+        <v>61.5</v>
       </c>
       <c r="C3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="E3" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G3" t="n">
         <v>1.5</v>
       </c>
-      <c r="D3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="E3" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.53</v>
-      </c>
       <c r="H3" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="I3" t="n">
         <v>3.85</v>
@@ -14496,50 +14496,50 @@
         <v>1.25</v>
       </c>
       <c r="K3" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="L3" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>64.09999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="C4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="E4" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G4" t="n">
         <v>1.5</v>
       </c>
-      <c r="D4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.53</v>
-      </c>
       <c r="H4" t="n">
-        <v>21.8</v>
+        <v>21.4</v>
       </c>
       <c r="I4" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>1.25</v>
       </c>
       <c r="K4" t="n">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
         <v>6.5</v>
@@ -14555,34 +14555,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.7</v>
+        <v>58.8</v>
       </c>
       <c r="C5" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="D5" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="E5" t="n">
-        <v>34.8</v>
+        <v>33.9</v>
       </c>
       <c r="F5" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="G5" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="H5" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="J5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="L5" t="n">
         <v>7.5</v>
@@ -14598,40 +14598,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60.5</v>
+        <v>59.7</v>
       </c>
       <c r="C6" t="n">
         <v>1.57</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="E6" t="n">
-        <v>34.3</v>
+        <v>33.6</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="G6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H6" t="n">
-        <v>18.8</v>
+        <v>18.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="J6" t="n">
         <v>1.2</v>
       </c>
       <c r="K6" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="L6" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="7">
@@ -14641,25 +14641,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59.3</v>
+        <v>57.7</v>
       </c>
       <c r="C7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="E7" t="n">
-        <v>32.7</v>
+        <v>31.7</v>
       </c>
       <c r="F7" t="n">
         <v>2.75</v>
       </c>
       <c r="G7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="H7" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="I7" t="n">
         <v>4.75</v>
@@ -14668,7 +14668,7 @@
         <v>1.18</v>
       </c>
       <c r="K7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L7" t="n">
         <v>8.5</v>
@@ -14684,34 +14684,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>53.3</v>
       </c>
       <c r="C8" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="D8" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="E8" t="n">
-        <v>28.2</v>
+        <v>27.5</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G8" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="H8" t="n">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="I8" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
         <v>1.14</v>
       </c>
       <c r="K8" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="L8" t="n">
         <v>12</v>
@@ -14727,31 +14727,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>51.8</v>
       </c>
       <c r="C9" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="E9" t="n">
-        <v>26.4</v>
+        <v>25.8</v>
       </c>
       <c r="F9" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="G9" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="H9" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="I9" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="J9" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="K9" t="n">
         <v>5.6</v>
@@ -14770,34 +14770,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50.1</v>
+        <v>47.3</v>
       </c>
       <c r="C10" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="D10" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="E10" t="n">
-        <v>22.7</v>
+        <v>21.4</v>
       </c>
       <c r="F10" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
         <v>1.25</v>
       </c>
       <c r="H10" t="n">
-        <v>9.9</v>
+        <v>9.1</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
         <v>17</v>
@@ -14813,25 +14813,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49.7</v>
+        <v>46.8</v>
       </c>
       <c r="C11" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="D11" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="E11" t="n">
-        <v>21.9</v>
+        <v>21.2</v>
       </c>
       <c r="F11" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
         <v>1.25</v>
       </c>
       <c r="H11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>8.5</v>
@@ -14856,37 +14856,37 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48.2</v>
+        <v>45.9</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="E12" t="n">
-        <v>21</v>
+        <v>19.8</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="G12" t="n">
         <v>1.22</v>
       </c>
       <c r="H12" t="n">
-        <v>8.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="L12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M12" t="n">
         <v>1.03</v>
@@ -14899,25 +14899,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>45</v>
+        <v>42.2</v>
       </c>
       <c r="C13" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="D13" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="E13" t="n">
-        <v>17.8</v>
+        <v>17</v>
       </c>
       <c r="F13" t="n">
-        <v>4.6</v>
+        <v>4.85</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="H13" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="I13" t="n">
         <v>11</v>
@@ -14926,10 +14926,10 @@
         <v>1.06</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="L13" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
@@ -14942,31 +14942,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>43.5</v>
+        <v>40.4</v>
       </c>
       <c r="C14" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="D14" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="E14" t="n">
-        <v>16.3</v>
+        <v>15.8</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="G14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="H14" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="K14" t="n">
         <v>2.2</v>
@@ -14981,72 +14981,72 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38.2</v>
+        <v>39.9</v>
       </c>
       <c r="C15" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="D15" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="E15" t="n">
-        <v>12.4</v>
+        <v>15.1</v>
       </c>
       <c r="F15" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="G15" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="L15" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>36.4</v>
+        <v>33.9</v>
       </c>
       <c r="C16" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="E16" t="n">
-        <v>11.5</v>
+        <v>10.8</v>
       </c>
       <c r="F16" t="n">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="G16" t="n">
         <v>1.11</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I16" t="n">
         <v>19</v>
@@ -15055,7 +15055,7 @@
         <v>1.03</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="L16" t="n">
         <v>51</v>
@@ -15067,40 +15067,44 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kyoto Sangyo University SC</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.4</v>
+        <v>33.9</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2.62</v>
       </c>
       <c r="D17" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="F17" t="n">
-        <v>1001</v>
+        <v>7.25</v>
       </c>
       <c r="G17" t="n">
-        <v>1.001</v>
+        <v>1.11</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
+        <v>3.2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>21</v>
+      </c>
       <c r="J17" t="n">
-        <v>1.001</v>
+        <v>1.03</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>67</v>
+      </c>
       <c r="M17" t="n">
-        <v>1.001</v>
+        <v>1.008</v>
       </c>
     </row>
   </sheetData>
@@ -15331,7 +15335,7 @@
         <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>204.7533443915497</v>
+        <v>204.7533443915498</v>
       </c>
       <c r="D6" t="n">
         <v>0.2916666666666667</v>
@@ -15399,7 +15403,7 @@
         <v>3990</v>
       </c>
       <c r="C8" t="n">
-        <v>29.75998964065703</v>
+        <v>29.75998964065702</v>
       </c>
       <c r="D8" t="n">
         <v>0.2491228070175439</v>
@@ -15411,7 +15415,7 @@
         <v>90</v>
       </c>
       <c r="G8" t="n">
-        <v>54.26504080002923</v>
+        <v>54.26504080002922</v>
       </c>
       <c r="H8" t="n">
         <v>0.2111111111111111</v>
@@ -15837,7 +15841,7 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>97.21521947451778</v>
+        <v>97.21521947451777</v>
       </c>
       <c r="D20" t="n">
         <v>0.08333333333333333</v>
@@ -15949,16 +15953,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="E2" t="n">
-        <v>61.9</v>
+        <v>61.8</v>
       </c>
       <c r="F2" t="n">
         <v>1.53</v>
@@ -15976,7 +15980,7 @@
         <v>1.7</v>
       </c>
       <c r="K2" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="L2" t="n">
         <v>2.95</v>
@@ -15992,7 +15996,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C3" t="n">
         <v>1.32</v>
@@ -16001,16 +16005,16 @@
         <v>3.25</v>
       </c>
       <c r="E3" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="F3" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G3" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="H3" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="I3" t="n">
         <v>2.75</v>
@@ -16019,13 +16023,13 @@
         <v>1.4</v>
       </c>
       <c r="K3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="L3" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="4">
@@ -16044,25 +16048,25 @@
         <v>2.75</v>
       </c>
       <c r="E4" t="n">
-        <v>40.7</v>
+        <v>41.5</v>
       </c>
       <c r="F4" t="n">
         <v>2.2</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H4" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J4" t="n">
         <v>1.25</v>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="L4" t="n">
         <v>7</v>
@@ -16078,25 +16082,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.09999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="C5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="D5" t="n">
         <v>2.62</v>
       </c>
       <c r="E5" t="n">
-        <v>39.9</v>
+        <v>39.2</v>
       </c>
       <c r="F5" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="G5" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="H5" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
@@ -16105,10 +16109,10 @@
         <v>1.22</v>
       </c>
       <c r="K5" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
@@ -16121,25 +16125,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60.8</v>
+        <v>61.4</v>
       </c>
       <c r="C6" t="n">
         <v>1.55</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="E6" t="n">
-        <v>32.2</v>
+        <v>32.9</v>
       </c>
       <c r="F6" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="G6" t="n">
         <v>1.42</v>
       </c>
       <c r="H6" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="I6" t="n">
         <v>5.25</v>
@@ -16148,13 +16152,13 @@
         <v>1.16</v>
       </c>
       <c r="K6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
         <v>11</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="7">
@@ -16164,7 +16168,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>60</v>
+        <v>60.3</v>
       </c>
       <c r="C7" t="n">
         <v>1.57</v>
@@ -16173,16 +16177,16 @@
         <v>2.25</v>
       </c>
       <c r="E7" t="n">
-        <v>31.8</v>
+        <v>31.3</v>
       </c>
       <c r="F7" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="G7" t="n">
         <v>1.4</v>
       </c>
       <c r="H7" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="I7" t="n">
         <v>5.5</v>
@@ -16191,7 +16195,7 @@
         <v>1.15</v>
       </c>
       <c r="K7" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="L7" t="n">
         <v>12</v>
@@ -16207,34 +16211,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58.4</v>
+        <v>58.9</v>
       </c>
       <c r="C8" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="D8" t="n">
         <v>2.2</v>
       </c>
       <c r="E8" t="n">
-        <v>30</v>
+        <v>30.5</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="G8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H8" t="n">
-        <v>13.6</v>
+        <v>14</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="J8" t="n">
         <v>1.14</v>
       </c>
       <c r="K8" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="L8" t="n">
         <v>12</v>
@@ -16250,7 +16254,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54.3</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
         <v>1.72</v>
@@ -16259,28 +16263,28 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>25.1</v>
+        <v>24.7</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="H9" t="n">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
       <c r="I9" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
         <v>1.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
@@ -16293,7 +16297,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53.3</v>
+        <v>52.5</v>
       </c>
       <c r="C10" t="n">
         <v>1.75</v>
@@ -16302,16 +16306,16 @@
         <v>1.95</v>
       </c>
       <c r="E10" t="n">
-        <v>23.4</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="G10" t="n">
         <v>1.27</v>
       </c>
       <c r="H10" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>8.5</v>
@@ -16320,7 +16324,7 @@
         <v>1.09</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
         <v>19</v>
@@ -16336,7 +16340,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>48.8</v>
+        <v>48.4</v>
       </c>
       <c r="C11" t="n">
         <v>1.9</v>
@@ -16354,7 +16358,7 @@
         <v>1.22</v>
       </c>
       <c r="H11" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="I11" t="n">
         <v>11</v>
@@ -16363,7 +16367,7 @@
         <v>1.06</v>
       </c>
       <c r="K11" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="L11" t="n">
         <v>29</v>
@@ -16375,32 +16379,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>42.5</v>
       </c>
       <c r="C12" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="E12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="F12" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="G12" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J12" t="n">
         <v>1.04</v>
@@ -16418,38 +16422,38 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42.7</v>
+        <v>41.1</v>
       </c>
       <c r="C13" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="D13" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="E13" t="n">
-        <v>14.4</v>
+        <v>13.6</v>
       </c>
       <c r="F13" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I13" t="n">
         <v>19</v>
       </c>
       <c r="J13" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>51</v>
@@ -16465,7 +16469,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29.3</v>
+        <v>29.1</v>
       </c>
       <c r="C14" t="n">
         <v>3</v>
@@ -16508,16 +16512,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26.8</v>
+        <v>27.3</v>
       </c>
       <c r="C15" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="D15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="E15" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="F15" t="n">
         <v>13</v>
@@ -16529,7 +16533,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="J15" t="n">
         <v>1.01</v>
@@ -16538,7 +16542,7 @@
         <v>0.2</v>
       </c>
       <c r="L15" t="n">
-        <v>251</v>
+        <v>201</v>
       </c>
       <c r="M15" t="n">
         <v>1.002</v>
@@ -16551,37 +16555,37 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
         <v>4.6</v>
       </c>
       <c r="D16" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="F16" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G16" t="n">
         <v>1.02</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I16" t="n">
-        <v>251</v>
+        <v>201</v>
       </c>
       <c r="J16" t="n">
         <v>1.002</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1001</v>
+        <v>751</v>
       </c>
       <c r="M16" t="n">
         <v>1.001</v>
@@ -16594,10 +16598,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18.3</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="D17" t="n">
         <v>1.2</v>
@@ -16606,25 +16610,25 @@
         <v>2.4</v>
       </c>
       <c r="F17" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G17" t="n">
         <v>1.02</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I17" t="n">
         <v>201</v>
       </c>
       <c r="J17" t="n">
-        <v>1.002</v>
+        <v>1.003</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1001</v>
+        <v>1501</v>
       </c>
       <c r="M17" t="n">
         <v>1.001</v>
@@ -17507,34 +17511,34 @@
         <v>1299</v>
       </c>
       <c r="E2" t="n">
-        <v>1507</v>
+        <v>1504</v>
       </c>
       <c r="F2" t="n">
-        <v>-178</v>
+        <v>-176</v>
       </c>
       <c r="G2" t="n">
         <v>1.0783</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0958</v>
+        <v>1.0961</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2044</v>
+        <v>0.2061</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2263</v>
+        <v>0.2268</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5693</v>
+        <v>0.5671</v>
       </c>
       <c r="L2" t="n">
-        <v>1.08</v>
+        <v>1.086</v>
       </c>
       <c r="M2" t="n">
-        <v>1.982</v>
+        <v>1.977</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5906</v>
+        <v>0.5908</v>
       </c>
       <c r="O2" t="n">
         <v>4.35</v>
@@ -17649,7 +17653,7 @@
         <v>0.8358</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6247</v>
+        <v>0.6248</v>
       </c>
       <c r="J4" t="n">
         <v>0.2119</v>
@@ -17702,40 +17706,40 @@
         <v>1611</v>
       </c>
       <c r="E5" t="n">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="F5" t="n">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G5" t="n">
         <v>1.0478</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0176</v>
+        <v>1.0214</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6443</v>
+        <v>0.6423</v>
       </c>
       <c r="J5" t="n">
-        <v>0.206</v>
+        <v>0.2067</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1496</v>
+        <v>0.1511</v>
       </c>
       <c r="L5" t="n">
-        <v>1.988</v>
+        <v>1.991</v>
       </c>
       <c r="M5" t="n">
-        <v>0.775</v>
+        <v>0.782</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5218</v>
+        <v>0.5242</v>
       </c>
       <c r="O5" t="n">
         <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="Q5" t="n">
         <v>5.75</v>
@@ -17850,10 +17854,10 @@
         <v>0.2451</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2999</v>
+        <v>0.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.896</v>
+        <v>1.895</v>
       </c>
       <c r="M7" t="n">
         <v>1.43</v>
@@ -18284,40 +18288,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1507</v>
+        <v>1504</v>
       </c>
       <c r="E14" t="n">
         <v>1345</v>
       </c>
       <c r="F14" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0958</v>
+        <v>1.0961</v>
       </c>
       <c r="H14" t="n">
         <v>0.8273</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5835</v>
+        <v>0.5813</v>
       </c>
       <c r="J14" t="n">
-        <v>0.223</v>
+        <v>0.2235</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1935</v>
+        <v>0.1952</v>
       </c>
       <c r="L14" t="n">
-        <v>1.576</v>
+        <v>1.572</v>
       </c>
       <c r="M14" t="n">
-        <v>0.773</v>
+        <v>0.777</v>
       </c>
       <c r="N14" t="n">
-        <v>0.417</v>
+        <v>0.4172</v>
       </c>
       <c r="O14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="P14" t="n">
         <v>4</v>
@@ -18364,13 +18368,13 @@
         <v>0.9714</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2302</v>
+        <v>0.2301</v>
       </c>
       <c r="J15" t="n">
         <v>0.2332</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5366</v>
+        <v>0.5367</v>
       </c>
       <c r="L15" t="n">
         <v>0.872</v>
@@ -18479,43 +18483,43 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="E17" t="n">
         <v>1582</v>
       </c>
       <c r="F17" t="n">
-        <v>-165</v>
+        <v>-163</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0176</v>
+        <v>1.0214</v>
       </c>
       <c r="H17" t="n">
         <v>1.0221</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2152</v>
+        <v>0.217</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2294</v>
+        <v>0.2299</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5554</v>
+        <v>0.5531</v>
       </c>
       <c r="L17" t="n">
-        <v>0.981</v>
+        <v>0.989</v>
       </c>
       <c r="M17" t="n">
-        <v>1.715</v>
+        <v>1.716</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5052</v>
+        <v>0.5077</v>
       </c>
       <c r="O17" t="n">
         <v>4.15</v>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q17" t="n">
         <v>1.72</v>
@@ -18860,16 +18864,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34</v>
+        <v>33.8</v>
       </c>
       <c r="C2" t="n">
         <v>2.62</v>
       </c>
       <c r="D2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="E2" t="n">
-        <v>71.2</v>
+        <v>71.3</v>
       </c>
       <c r="F2" t="n">
         <v>1.35</v>
@@ -18892,7 +18896,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="C3" t="n">
         <v>4</v>
@@ -18901,7 +18905,7 @@
         <v>1.25</v>
       </c>
       <c r="E3" t="n">
-        <v>57.3</v>
+        <v>57.5</v>
       </c>
       <c r="F3" t="n">
         <v>1.65</v>
@@ -18924,7 +18928,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="C4" t="n">
         <v>6.25</v>
@@ -18933,7 +18937,7 @@
         <v>1.13</v>
       </c>
       <c r="E4" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="F4" t="n">
         <v>2.1</v>
@@ -18959,7 +18963,7 @@
         <v>11.9</v>
       </c>
       <c r="C5" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="D5" t="n">
         <v>1.12</v>
@@ -18988,7 +18992,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="C6" t="n">
         <v>7.5</v>
@@ -19052,7 +19056,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="C8" t="n">
         <v>51</v>
@@ -19061,13 +19065,13 @@
         <v>1.01</v>
       </c>
       <c r="E8" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="F8" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -19110,7 +19114,7 @@
         <v>201</v>
       </c>
       <c r="J9" t="n">
-        <v>1.002</v>
+        <v>1.003</v>
       </c>
     </row>
     <row r="10">
@@ -19172,10 +19176,10 @@
         <v>1.007</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="J11" t="n">
         <v>1.01</v>
@@ -19191,7 +19195,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2001</v>
+        <v>1501</v>
       </c>
       <c r="D12" t="n">
         <v>1.001</v>
@@ -19270,7 +19274,7 @@
         <v>1.001</v>
       </c>
       <c r="H14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I14" t="n">
         <v>8.5</v>
@@ -19296,7 +19300,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>3501</v>
+        <v>5001</v>
       </c>
       <c r="G15" t="n">
         <v>1.001</v>
@@ -19328,16 +19332,16 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2501</v>
+        <v>3501</v>
       </c>
       <c r="G16" t="n">
         <v>1.001</v>
       </c>
       <c r="H16" t="n">
-        <v>20.5</v>
+        <v>19.7</v>
       </c>
       <c r="I16" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="J16" t="n">
         <v>1.22</v>
@@ -19394,7 +19398,7 @@
         <v>1.001</v>
       </c>
       <c r="H18" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="I18" t="n">
         <v>3</v>
@@ -19424,7 +19428,7 @@
         <v>1.001</v>
       </c>
       <c r="H19" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
       <c r="I19" t="n">
         <v>2.05</v>
@@ -19454,13 +19458,13 @@
         <v>1.001</v>
       </c>
       <c r="H20" t="n">
-        <v>62.2</v>
+        <v>62.4</v>
       </c>
       <c r="I20" t="n">
         <v>1.53</v>
       </c>
       <c r="J20" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21">
@@ -19484,7 +19488,7 @@
         <v>1.001</v>
       </c>
       <c r="H21" t="n">
-        <v>81.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I21" t="n">
         <v>1.2</v>
@@ -19634,43 +19638,43 @@
         <v>73.5</v>
       </c>
       <c r="C2" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3398</v>
+        <v>0.33845</v>
       </c>
       <c r="E2" t="n">
-        <v>0.215</v>
+        <v>0.217</v>
       </c>
       <c r="F2" t="n">
-        <v>0.15765</v>
+        <v>0.1574</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1101</v>
+        <v>0.1107</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0774</v>
+        <v>0.0771</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05255</v>
+        <v>0.05325</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0291</v>
+        <v>0.0281</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01205</v>
+        <v>0.01165</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00375</v>
+        <v>0.0037</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0015</v>
+        <v>0.00145</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008</v>
+        <v>0.00085</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00015</v>
+        <v>0.0002</v>
       </c>
       <c r="P2" t="n">
         <v>0.0001</v>
@@ -19707,46 +19711,46 @@
         <v>71.3</v>
       </c>
       <c r="C3" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2131</v>
+        <v>0.2138</v>
       </c>
       <c r="E3" t="n">
-        <v>0.19495</v>
+        <v>0.19515</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1649</v>
+        <v>0.1659</v>
       </c>
       <c r="G3" t="n">
-        <v>0.14585</v>
+        <v>0.1457</v>
       </c>
       <c r="H3" t="n">
-        <v>0.11585</v>
+        <v>0.1155</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07955</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0448</v>
+        <v>0.0434</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0226</v>
+        <v>0.02325</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0107</v>
+        <v>0.01015</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0043</v>
+        <v>0.0044</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00195</v>
+        <v>0.00205</v>
       </c>
       <c r="O3" t="n">
         <v>0.001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00025</v>
+        <v>0.0003</v>
       </c>
       <c r="Q3" t="n">
         <v>0.00015</v>
@@ -19783,37 +19787,37 @@
         <v>4.12</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1271</v>
+        <v>0.12775</v>
       </c>
       <c r="E4" t="n">
-        <v>0.15285</v>
+        <v>0.1514</v>
       </c>
       <c r="F4" t="n">
-        <v>0.15815</v>
+        <v>0.1597</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1579</v>
+        <v>0.1572</v>
       </c>
       <c r="H4" t="n">
-        <v>0.137</v>
+        <v>0.1384</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1134</v>
+        <v>0.11225</v>
       </c>
       <c r="J4" t="n">
         <v>0.07514999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0415</v>
+        <v>0.04125</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0199</v>
+        <v>0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>0.009650000000000001</v>
+        <v>0.0097</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00445</v>
+        <v>0.0043</v>
       </c>
       <c r="O4" t="n">
         <v>0.00165</v>
@@ -19822,7 +19826,7 @@
         <v>0.00055</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.00045</v>
+        <v>0.0004</v>
       </c>
       <c r="R4" t="n">
         <v>0.00025</v>
@@ -19853,52 +19857,52 @@
         <v>68.90000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1187</v>
+        <v>0.11925</v>
       </c>
       <c r="E5" t="n">
-        <v>0.14145</v>
+        <v>0.1409</v>
       </c>
       <c r="F5" t="n">
-        <v>0.15555</v>
+        <v>0.15585</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1547</v>
+        <v>0.1557</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1404</v>
+        <v>0.14045</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1242</v>
+        <v>0.12395</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0796</v>
+        <v>0.0795</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04305</v>
+        <v>0.04235</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02365</v>
+        <v>0.0231</v>
       </c>
       <c r="M5" t="n">
-        <v>0.009849999999999999</v>
+        <v>0.0101</v>
       </c>
       <c r="N5" t="n">
         <v>0.00535</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0024</v>
+        <v>0.00235</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0007</v>
+        <v>0.00075</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003</v>
+        <v>0.00025</v>
       </c>
       <c r="R5" t="n">
-        <v>5e-05</v>
+        <v>0.0001</v>
       </c>
       <c r="S5" t="n">
         <v>5e-05</v>
@@ -19926,55 +19930,55 @@
         <v>68.3</v>
       </c>
       <c r="C6" t="n">
-        <v>4.38</v>
+        <v>4.37</v>
       </c>
       <c r="D6" t="n">
-        <v>0.10405</v>
+        <v>0.10455</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1379</v>
+        <v>0.1371</v>
       </c>
       <c r="F6" t="n">
-        <v>0.15085</v>
+        <v>0.1512</v>
       </c>
       <c r="G6" t="n">
-        <v>0.14945</v>
+        <v>0.1507</v>
       </c>
       <c r="H6" t="n">
-        <v>0.148</v>
+        <v>0.14815</v>
       </c>
       <c r="I6" t="n">
-        <v>0.13285</v>
+        <v>0.13295</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0844</v>
+        <v>0.0838</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04795</v>
+        <v>0.04725</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0246</v>
+        <v>0.02455</v>
       </c>
       <c r="M6" t="n">
         <v>0.01105</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0052</v>
+        <v>0.005</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0023</v>
+        <v>0.00235</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0008</v>
+        <v>0.0009</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0005</v>
+        <v>0.00035</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001</v>
+        <v>5e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>5e-05</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -19999,55 +20003,55 @@
         <v>67.2</v>
       </c>
       <c r="C7" t="n">
-        <v>4.72</v>
+        <v>4.71</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0815</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1162</v>
+        <v>0.11685</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1349</v>
+        <v>0.13435</v>
       </c>
       <c r="G7" t="n">
-        <v>0.14875</v>
+        <v>0.14995</v>
       </c>
       <c r="H7" t="n">
-        <v>0.155</v>
+        <v>0.15555</v>
       </c>
       <c r="I7" t="n">
-        <v>0.14205</v>
+        <v>0.14125</v>
       </c>
       <c r="J7" t="n">
-        <v>0.10285</v>
+        <v>0.10305</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0604</v>
+        <v>0.0602</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0303</v>
+        <v>0.02895</v>
       </c>
       <c r="M7" t="n">
-        <v>0.014</v>
+        <v>0.0148</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0076</v>
+        <v>0.00735</v>
       </c>
       <c r="O7" t="n">
-        <v>0.00385</v>
+        <v>0.00365</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0016</v>
+        <v>0.00165</v>
       </c>
       <c r="Q7" t="n">
         <v>0.0005999999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00025</v>
+        <v>0.0002</v>
       </c>
       <c r="S7" t="n">
-        <v>5e-05</v>
+        <v>0.0001</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -20069,70 +20073,70 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>60.8</v>
+        <v>60.6</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>7.07</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0122</v>
+        <v>0.01115</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02895</v>
+        <v>0.02855</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04745</v>
+        <v>0.04515</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0712</v>
       </c>
       <c r="H8" t="n">
-        <v>0.10945</v>
+        <v>0.1067</v>
       </c>
       <c r="I8" t="n">
-        <v>0.14095</v>
+        <v>0.1401</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1831</v>
+        <v>0.1821</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1484</v>
+        <v>0.1505</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1019</v>
+        <v>0.10605</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06775</v>
+        <v>0.06925000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03885</v>
+        <v>0.03915</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02215</v>
+        <v>0.0229</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01205</v>
+        <v>0.01355</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0075</v>
+        <v>0.0076</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0031</v>
+        <v>0.00335</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0015</v>
+        <v>0.0016</v>
       </c>
       <c r="T8" t="n">
-        <v>0.00045</v>
+        <v>0.0007</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0003</v>
+        <v>0.00025</v>
       </c>
       <c r="V8" t="n">
+        <v>0.00015</v>
+      </c>
+      <c r="W8" t="n">
         <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>5e-05</v>
       </c>
     </row>
     <row r="9">
@@ -20145,64 +20149,64 @@
         <v>55.8</v>
       </c>
       <c r="C9" t="n">
-        <v>8.99</v>
+        <v>8.98</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0021</v>
+        <v>0.00205</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00615</v>
+        <v>0.0064</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0143</v>
+        <v>0.01455</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0247</v>
+        <v>0.02395</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0456</v>
+        <v>0.04645</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07635</v>
+        <v>0.07685</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1231</v>
+        <v>0.12385</v>
       </c>
       <c r="K9" t="n">
-        <v>0.16015</v>
+        <v>0.15995</v>
       </c>
       <c r="L9" t="n">
-        <v>0.151</v>
+        <v>0.15005</v>
       </c>
       <c r="M9" t="n">
-        <v>0.12915</v>
+        <v>0.1277</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0929</v>
+        <v>0.09345000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06695</v>
+        <v>0.0669</v>
       </c>
       <c r="P9" t="n">
-        <v>0.04445</v>
+        <v>0.0446</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02895</v>
+        <v>0.02865</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0158</v>
+        <v>0.01585</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01035</v>
+        <v>0.0107</v>
       </c>
       <c r="T9" t="n">
-        <v>0.00525</v>
+        <v>0.00515</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.00065</v>
       </c>
       <c r="W9" t="n">
         <v>0.00025</v>
@@ -20221,61 +20225,61 @@
         <v>9.949999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.00065</v>
       </c>
       <c r="E10" t="n">
         <v>0.0027</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00635</v>
+        <v>0.00625</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01415</v>
+        <v>0.0142</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0267</v>
+        <v>0.02735</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04895</v>
+        <v>0.0488</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0896</v>
+        <v>0.09014999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1275</v>
+        <v>0.1278</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1495</v>
+        <v>0.1483</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1417</v>
+        <v>0.1412</v>
       </c>
       <c r="N10" t="n">
-        <v>0.11685</v>
+        <v>0.11805</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0892</v>
+        <v>0.0878</v>
       </c>
       <c r="P10" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.06665</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0491</v>
+        <v>0.04815</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0332</v>
+        <v>0.0329</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01845</v>
+        <v>0.01945</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01055</v>
+        <v>0.01095</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0059</v>
+        <v>0.00575</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0021</v>
+        <v>0.0022</v>
       </c>
       <c r="W10" t="n">
         <v>0.0007</v>
@@ -20297,58 +20301,58 @@
         <v>0.00055</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002</v>
+        <v>0.0021</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00565</v>
+        <v>0.0056</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0097</v>
+        <v>0.00975</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0202</v>
+        <v>0.02015</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03635</v>
+        <v>0.03735</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0733</v>
+        <v>0.0741</v>
       </c>
       <c r="K11" t="n">
-        <v>0.11455</v>
+        <v>0.11375</v>
       </c>
       <c r="L11" t="n">
-        <v>0.13865</v>
+        <v>0.1397</v>
       </c>
       <c r="M11" t="n">
-        <v>0.14235</v>
+        <v>0.13895</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1256</v>
+        <v>0.1267</v>
       </c>
       <c r="O11" t="n">
-        <v>0.10335</v>
+        <v>0.10365</v>
       </c>
       <c r="P11" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.08085000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.05705</v>
+        <v>0.05625</v>
       </c>
       <c r="R11" t="n">
-        <v>0.03745</v>
+        <v>0.039</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0257</v>
+        <v>0.0253</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0158</v>
+        <v>0.0161</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0074</v>
+        <v>0.00685</v>
       </c>
       <c r="V11" t="n">
-        <v>0.00245</v>
+        <v>0.0026</v>
       </c>
       <c r="W11" t="n">
         <v>0.0007</v>
@@ -20367,52 +20371,52 @@
         <v>10.84</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="E12" t="n">
-        <v>0.00155</v>
+        <v>0.0016</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0033</v>
+        <v>0.00325</v>
       </c>
       <c r="G12" t="n">
-        <v>0.00775</v>
+        <v>0.007849999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>0.0153</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0295</v>
+        <v>0.03005</v>
       </c>
       <c r="J12" t="n">
-        <v>0.05855</v>
+        <v>0.05945</v>
       </c>
       <c r="K12" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.0946</v>
       </c>
       <c r="L12" t="n">
-        <v>0.123</v>
+        <v>0.12105</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1394</v>
+        <v>0.1401</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1344</v>
+        <v>0.1342</v>
       </c>
       <c r="O12" t="n">
-        <v>0.12085</v>
+        <v>0.1211</v>
       </c>
       <c r="P12" t="n">
-        <v>0.08945</v>
+        <v>0.08885</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.068</v>
+        <v>0.06834999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>0.04625</v>
+        <v>0.0466</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0327</v>
+        <v>0.0332</v>
       </c>
       <c r="T12" t="n">
         <v>0.01755</v>
@@ -20421,7 +20425,7 @@
         <v>0.011</v>
       </c>
       <c r="V12" t="n">
-        <v>0.00445</v>
+        <v>0.0045</v>
       </c>
       <c r="W12" t="n">
         <v>0.0011</v>
@@ -20437,7 +20441,7 @@
         <v>47.5</v>
       </c>
       <c r="C13" t="n">
-        <v>12.47</v>
+        <v>12.48</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -20449,55 +20453,55 @@
         <v>0.00045</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00165</v>
+        <v>0.0015</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00495</v>
+        <v>0.0048</v>
       </c>
       <c r="I13" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0103</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0239</v>
+        <v>0.0237</v>
       </c>
       <c r="K13" t="n">
-        <v>0.04735</v>
+        <v>0.048</v>
       </c>
       <c r="L13" t="n">
         <v>0.08019999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>0.09825</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1225</v>
+        <v>0.12105</v>
       </c>
       <c r="O13" t="n">
-        <v>0.12445</v>
+        <v>0.12615</v>
       </c>
       <c r="P13" t="n">
-        <v>0.12075</v>
+        <v>0.11935</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1095</v>
+        <v>0.10905</v>
       </c>
       <c r="R13" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.08724999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0504</v>
+        <v>0.04895</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0328</v>
+        <v>0.03255</v>
       </c>
       <c r="V13" t="n">
-        <v>0.01495</v>
+        <v>0.0154</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0039</v>
+        <v>0.0041</v>
       </c>
     </row>
     <row r="14">
@@ -20519,58 +20523,58 @@
         <v>0.00015</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="G14" t="n">
-        <v>0.00085</v>
+        <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00205</v>
+        <v>0.0021</v>
       </c>
       <c r="I14" t="n">
-        <v>0.00725</v>
+        <v>0.00705</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01575</v>
+        <v>0.01605</v>
       </c>
       <c r="K14" t="n">
-        <v>0.03455</v>
+        <v>0.03505</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05405</v>
+        <v>0.05395</v>
       </c>
       <c r="M14" t="n">
-        <v>0.07835</v>
+        <v>0.0784</v>
       </c>
       <c r="N14" t="n">
-        <v>0.10495</v>
+        <v>0.1031</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1216</v>
+        <v>0.1202</v>
       </c>
       <c r="P14" t="n">
         <v>0.1246</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.114</v>
+        <v>0.1162</v>
       </c>
       <c r="R14" t="n">
-        <v>0.10385</v>
+        <v>0.10345</v>
       </c>
       <c r="S14" t="n">
-        <v>0.08535</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0641</v>
+        <v>0.0646</v>
       </c>
       <c r="U14" t="n">
-        <v>0.04835</v>
+        <v>0.04875</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0283</v>
+        <v>0.0286</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0116</v>
+        <v>0.01155</v>
       </c>
     </row>
     <row r="15">
@@ -20583,7 +20587,7 @@
         <v>42.6</v>
       </c>
       <c r="C15" t="n">
-        <v>14.51</v>
+        <v>14.52</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -20592,7 +20596,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0001</v>
+        <v>5e-05</v>
       </c>
       <c r="G15" t="n">
         <v>0.0002</v>
@@ -20601,49 +20605,49 @@
         <v>0.0009</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0027</v>
+        <v>0.00285</v>
       </c>
       <c r="J15" t="n">
-        <v>0.00555</v>
+        <v>0.0056</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01495</v>
+        <v>0.0148</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03015</v>
+        <v>0.02985</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0453</v>
+        <v>0.04605</v>
       </c>
       <c r="N15" t="n">
-        <v>0.07015</v>
+        <v>0.0697</v>
       </c>
       <c r="O15" t="n">
-        <v>0.08955</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1021</v>
+        <v>0.10325</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.11925</v>
+        <v>0.1185</v>
       </c>
       <c r="R15" t="n">
-        <v>0.12175</v>
+        <v>0.1216</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1153</v>
+        <v>0.11505</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1028</v>
+        <v>0.10375</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.0888</v>
       </c>
       <c r="V15" t="n">
-        <v>0.05995</v>
+        <v>0.06065</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0299</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="16">
@@ -20653,70 +20657,70 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>41.8</v>
+        <v>42</v>
       </c>
       <c r="C16" t="n">
-        <v>14.88</v>
+        <v>14.81</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>5e-05</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0.0001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00015</v>
+        <v>0.0002</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00065</v>
+        <v>0.00055</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00165</v>
+        <v>0.00195</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00515</v>
+        <v>0.0054</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0113</v>
+        <v>0.0117</v>
       </c>
       <c r="L16" t="n">
-        <v>0.021</v>
+        <v>0.0234</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0383</v>
+        <v>0.0397</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0563</v>
+        <v>0.0577</v>
       </c>
       <c r="O16" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.07655000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.10425</v>
+        <v>0.1041</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.11365</v>
+        <v>0.1167</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1234</v>
+        <v>0.1217</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1279</v>
+        <v>0.1275</v>
       </c>
       <c r="T16" t="n">
-        <v>0.11635</v>
+        <v>0.11545</v>
       </c>
       <c r="U16" t="n">
-        <v>0.10085</v>
+        <v>0.09825</v>
       </c>
       <c r="V16" t="n">
-        <v>0.06884999999999999</v>
+        <v>0.06575</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0352</v>
+        <v>0.0333</v>
       </c>
     </row>
     <row r="17">
@@ -20750,46 +20754,46 @@
         <v>0.0005999999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0036</v>
+        <v>0.0039</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0083</v>
+        <v>0.008149999999999999</v>
       </c>
       <c r="L17" t="n">
         <v>0.01575</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0283</v>
+        <v>0.02855</v>
       </c>
       <c r="N17" t="n">
-        <v>0.04225</v>
+        <v>0.0427</v>
       </c>
       <c r="O17" t="n">
-        <v>0.06505</v>
+        <v>0.06444999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>0.08434999999999999</v>
+        <v>0.08395</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1005</v>
+        <v>0.09925</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1252</v>
+        <v>0.12585</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1312</v>
+        <v>0.13135</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1292</v>
+        <v>0.1298</v>
       </c>
       <c r="U17" t="n">
-        <v>0.12225</v>
+        <v>0.12175</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0948</v>
+        <v>0.09575</v>
       </c>
       <c r="W17" t="n">
-        <v>0.04825</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="18">
@@ -20802,7 +20806,7 @@
         <v>39.7</v>
       </c>
       <c r="C18" t="n">
-        <v>15.65</v>
+        <v>15.66</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -20820,49 +20824,49 @@
         <v>0.00015</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0008</v>
+        <v>0.00085</v>
       </c>
       <c r="J18" t="n">
         <v>0.0017</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0063</v>
+        <v>0.0064</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0134</v>
+        <v>0.01315</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0243</v>
+        <v>0.02445</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0404</v>
+        <v>0.0402</v>
       </c>
       <c r="O18" t="n">
-        <v>0.056</v>
+        <v>0.05565</v>
       </c>
       <c r="P18" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0775</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.10155</v>
+        <v>0.10165</v>
       </c>
       <c r="R18" t="n">
-        <v>0.12</v>
+        <v>0.11965</v>
       </c>
       <c r="S18" t="n">
-        <v>0.12765</v>
+        <v>0.12725</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1393</v>
+        <v>0.1389</v>
       </c>
       <c r="U18" t="n">
-        <v>0.12665</v>
+        <v>0.12815</v>
       </c>
       <c r="V18" t="n">
-        <v>0.10195</v>
+        <v>0.1019</v>
       </c>
       <c r="W18" t="n">
-        <v>0.062</v>
+        <v>0.0624</v>
       </c>
     </row>
     <row r="19">
@@ -20875,7 +20879,7 @@
         <v>37.2</v>
       </c>
       <c r="C19" t="n">
-        <v>16.68</v>
+        <v>16.69</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -20896,46 +20900,46 @@
         <v>0.00035</v>
       </c>
       <c r="J19" t="n">
-        <v>0.00055</v>
+        <v>0.00075</v>
       </c>
       <c r="K19" t="n">
         <v>0.00265</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0059</v>
+        <v>0.00555</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0101</v>
+        <v>0.01015</v>
       </c>
       <c r="N19" t="n">
-        <v>0.01805</v>
+        <v>0.0177</v>
       </c>
       <c r="O19" t="n">
-        <v>0.03385</v>
+        <v>0.0343</v>
       </c>
       <c r="P19" t="n">
-        <v>0.05135</v>
+        <v>0.0509</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0702</v>
+        <v>0.07035</v>
       </c>
       <c r="R19" t="n">
-        <v>0.09325</v>
+        <v>0.09265</v>
       </c>
       <c r="S19" t="n">
-        <v>0.12065</v>
+        <v>0.11975</v>
       </c>
       <c r="T19" t="n">
-        <v>0.14645</v>
+        <v>0.1467</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1681</v>
+        <v>0.16915</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1659</v>
+        <v>0.1657</v>
       </c>
       <c r="W19" t="n">
-        <v>0.11255</v>
+        <v>0.11325</v>
       </c>
     </row>
     <row r="20">
@@ -20972,43 +20976,43 @@
         <v>0.00025</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00065</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.00205</v>
+        <v>0.002</v>
       </c>
       <c r="M20" t="n">
-        <v>0.00525</v>
+        <v>0.00515</v>
       </c>
       <c r="N20" t="n">
         <v>0.0092</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0159</v>
+        <v>0.0161</v>
       </c>
       <c r="P20" t="n">
-        <v>0.02795</v>
+        <v>0.028</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.0434</v>
+        <v>0.0426</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0599</v>
+        <v>0.0603</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0891</v>
+        <v>0.08774999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1243</v>
+        <v>0.124</v>
       </c>
       <c r="U20" t="n">
-        <v>0.16485</v>
+        <v>0.1658</v>
       </c>
       <c r="V20" t="n">
-        <v>0.23185</v>
+        <v>0.233</v>
       </c>
       <c r="W20" t="n">
-        <v>0.22525</v>
+        <v>0.22515</v>
       </c>
     </row>
     <row r="21">
@@ -21021,7 +21025,7 @@
         <v>31</v>
       </c>
       <c r="C21" t="n">
-        <v>18.73</v>
+        <v>18.74</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -21051,37 +21055,37 @@
         <v>0.00055</v>
       </c>
       <c r="M21" t="n">
-        <v>0.00115</v>
+        <v>0.00125</v>
       </c>
       <c r="N21" t="n">
-        <v>0.00225</v>
+        <v>0.0022</v>
       </c>
       <c r="O21" t="n">
-        <v>0.00485</v>
+        <v>0.00465</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0095</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.0153</v>
+        <v>0.0149</v>
       </c>
       <c r="R21" t="n">
-        <v>0.0293</v>
+        <v>0.02925</v>
       </c>
       <c r="S21" t="n">
-        <v>0.04685</v>
+        <v>0.0463</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0775</v>
+        <v>0.0774</v>
       </c>
       <c r="U21" t="n">
-        <v>0.12025</v>
+        <v>0.12095</v>
       </c>
       <c r="V21" t="n">
-        <v>0.22385</v>
+        <v>0.22315</v>
       </c>
       <c r="W21" t="n">
-        <v>0.46855</v>
+        <v>0.4697</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan/report.xlsx
+++ b/output/japan/report.xlsx
@@ -17497,61 +17497,61 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1299</v>
+        <v>1402</v>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>1417</v>
       </c>
       <c r="F2" t="n">
-        <v>-174</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
-        <v>1.0783</v>
+        <v>0.915</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0961</v>
+        <v>1.095</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2045</v>
+        <v>0.3854</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2371</v>
+        <v>0.2595</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5584</v>
+        <v>0.3551</v>
       </c>
       <c r="L2" t="n">
-        <v>1.081</v>
+        <v>1.335</v>
       </c>
       <c r="M2" t="n">
-        <v>1.982</v>
+        <v>1.261</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5908</v>
+        <v>0.4807</v>
       </c>
       <c r="O2" t="n">
-        <v>4.35</v>
+        <v>2.45</v>
       </c>
       <c r="P2" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.72</v>
+        <v>2.62</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="3">
@@ -17562,46 +17562,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1347</v>
+        <v>1299</v>
       </c>
       <c r="E3" t="n">
-        <v>1554</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="n">
-        <v>-177</v>
+        <v>-174</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8273</v>
+        <v>1.0783</v>
       </c>
       <c r="H3" t="n">
-        <v>0.985</v>
+        <v>1.0961</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2025</v>
+        <v>0.2045</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2365</v>
+        <v>0.2371</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5584</v>
       </c>
       <c r="L3" t="n">
-        <v>0.741</v>
+        <v>1.081</v>
       </c>
       <c r="M3" t="n">
-        <v>1.371</v>
+        <v>1.982</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3536</v>
+        <v>0.5908</v>
       </c>
       <c r="O3" t="n">
         <v>4.35</v>
@@ -17613,10 +17613,10 @@
         <v>1.72</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="S3" t="n">
-        <v>1.47</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="4">
@@ -17627,61 +17627,61 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1581</v>
+        <v>1607</v>
       </c>
       <c r="E4" t="n">
-        <v>1376</v>
+        <v>1390</v>
       </c>
       <c r="F4" t="n">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9714</v>
+        <v>1.0478</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8358</v>
+        <v>1.0214</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6183</v>
+        <v>0.6308</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2211</v>
+        <v>0.2172</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1606</v>
+        <v>0.152</v>
       </c>
       <c r="L4" t="n">
-        <v>1.469</v>
+        <v>1.965</v>
       </c>
       <c r="M4" t="n">
-        <v>0.635</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3514</v>
+        <v>0.5242</v>
       </c>
       <c r="O4" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="R4" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="S4" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="5">
@@ -17692,61 +17692,61 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1607</v>
+        <v>1347</v>
       </c>
       <c r="E5" t="n">
-        <v>1390</v>
+        <v>1554</v>
       </c>
       <c r="F5" t="n">
-        <v>247</v>
+        <v>-177</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0478</v>
+        <v>0.8273</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0214</v>
+        <v>0.985</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6308</v>
+        <v>0.2025</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2172</v>
+        <v>0.2365</v>
       </c>
       <c r="K5" t="n">
-        <v>0.152</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.965</v>
+        <v>0.741</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8090000000000001</v>
+        <v>1.371</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5242</v>
+        <v>0.3536</v>
       </c>
       <c r="O5" t="n">
-        <v>1.53</v>
+        <v>4.35</v>
       </c>
       <c r="P5" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.75</v>
+        <v>1.72</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="6">
@@ -18017,61 +18017,61 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1402</v>
+        <v>1445</v>
       </c>
       <c r="E10" t="n">
-        <v>1417</v>
+        <v>1558</v>
       </c>
       <c r="F10" t="n">
-        <v>14</v>
+        <v>-83</v>
       </c>
       <c r="G10" t="n">
-        <v>0.915</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>1.095</v>
+        <v>0.9514</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3854</v>
+        <v>0.2855</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2595</v>
+        <v>0.2543</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3551</v>
+        <v>0.4602</v>
       </c>
       <c r="L10" t="n">
-        <v>1.335</v>
+        <v>0.988</v>
       </c>
       <c r="M10" t="n">
-        <v>1.261</v>
+        <v>1.311</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4807</v>
+        <v>0.4034</v>
       </c>
       <c r="O10" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="S10" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="11">
@@ -18082,61 +18082,61 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1445</v>
+        <v>1581</v>
       </c>
       <c r="E11" t="n">
-        <v>1558</v>
+        <v>1376</v>
       </c>
       <c r="F11" t="n">
-        <v>-83</v>
+        <v>234</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9714</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9514</v>
+        <v>0.8358</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2855</v>
+        <v>0.6183</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2543</v>
+        <v>0.2211</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4602</v>
+        <v>0.1606</v>
       </c>
       <c r="L11" t="n">
-        <v>0.988</v>
+        <v>1.469</v>
       </c>
       <c r="M11" t="n">
-        <v>1.311</v>
+        <v>0.635</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4034</v>
+        <v>0.3514</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>1.57</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.05</v>
+        <v>5.5</v>
       </c>
       <c r="R11" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="S11" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="12">
@@ -18862,7 +18862,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="C2" t="n">
         <v>2.75</v>
@@ -18894,16 +18894,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="C3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="D3" t="n">
         <v>1.25</v>
       </c>
       <c r="E3" t="n">
-        <v>59.2</v>
+        <v>59.3</v>
       </c>
       <c r="F3" t="n">
         <v>1.6</v>
@@ -18926,7 +18926,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="C4" t="n">
         <v>6.25</v>
@@ -18935,7 +18935,7 @@
         <v>1.13</v>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>43.2</v>
       </c>
       <c r="F4" t="n">
         <v>2.1</v>
@@ -18967,13 +18967,13 @@
         <v>1.12</v>
       </c>
       <c r="E5" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="F5" t="n">
         <v>2.2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -18990,16 +18990,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="D6" t="n">
         <v>1.11</v>
       </c>
       <c r="E6" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="F6" t="n">
         <v>2.2</v>
@@ -19022,13 +19022,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="C7" t="n">
         <v>9.5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="E7" t="n">
         <v>32.1</v>
@@ -19063,7 +19063,7 @@
         <v>1.01</v>
       </c>
       <c r="E8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="F8" t="n">
         <v>9</v>
@@ -19072,10 +19072,10 @@
         <v>1.08</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>751</v>
+        <v>1001</v>
       </c>
       <c r="J8" t="n">
         <v>1.001</v>
@@ -19088,16 +19088,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C9" t="n">
-        <v>301</v>
+        <v>351</v>
       </c>
       <c r="D9" t="n">
         <v>1.001</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="F9" t="n">
         <v>29</v>
@@ -19134,13 +19134,13 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="G10" t="n">
         <v>1.01</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I10" t="n">
         <v>67</v>
@@ -19171,10 +19171,10 @@
         <v>67</v>
       </c>
       <c r="G11" t="n">
-        <v>1.007</v>
+        <v>1.008</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I11" t="n">
         <v>51</v>
@@ -19208,13 +19208,13 @@
         <v>1.005</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="I12" t="n">
         <v>41</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="13">
@@ -19240,7 +19240,7 @@
         <v>1.001</v>
       </c>
       <c r="H13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I13" t="n">
         <v>13</v>
@@ -19306,13 +19306,13 @@
         <v>1.001</v>
       </c>
       <c r="H15" t="n">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="I15" t="n">
         <v>4.6</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="16">
@@ -19338,10 +19338,10 @@
         <v>1.001</v>
       </c>
       <c r="H16" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="I16" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="J16" t="n">
         <v>1.22</v>
@@ -19363,7 +19363,9 @@
       <c r="E17" t="n">
         <v>0</v>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>5001</v>
+      </c>
       <c r="G17" t="n">
         <v>1.001</v>
       </c>
@@ -19398,13 +19400,13 @@
         <v>1.001</v>
       </c>
       <c r="H18" t="n">
-        <v>29.4</v>
+        <v>29.9</v>
       </c>
       <c r="I18" t="n">
         <v>2.95</v>
       </c>
       <c r="J18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="19">
@@ -19428,13 +19430,13 @@
         <v>1.001</v>
       </c>
       <c r="H19" t="n">
-        <v>43.9</v>
+        <v>43.6</v>
       </c>
       <c r="I19" t="n">
         <v>2.1</v>
       </c>
       <c r="J19" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="20">
@@ -19458,13 +19460,13 @@
         <v>1.001</v>
       </c>
       <c r="H20" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
       <c r="I20" t="n">
         <v>1.53</v>
       </c>
       <c r="J20" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="21">
@@ -19638,46 +19640,46 @@
         <v>73</v>
       </c>
       <c r="C2" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="D2" t="n">
-        <v>0.32555</v>
+        <v>0.3266</v>
       </c>
       <c r="E2" t="n">
-        <v>0.21885</v>
+        <v>0.2196</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1567</v>
+        <v>0.1551</v>
       </c>
       <c r="G2" t="n">
-        <v>0.11355</v>
+        <v>0.1159</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.08015</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05475</v>
+        <v>0.05405</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02955</v>
+        <v>0.02865</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0127</v>
+        <v>0.0118</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0042</v>
+        <v>0.0049</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0019</v>
+        <v>0.00205</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008</v>
+        <v>0.00075</v>
       </c>
       <c r="O2" t="n">
         <v>0.00025</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -19714,49 +19716,49 @@
         <v>3.33</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2211</v>
+        <v>0.2226</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1995</v>
+        <v>0.19755</v>
       </c>
       <c r="F3" t="n">
-        <v>0.17145</v>
+        <v>0.17305</v>
       </c>
       <c r="G3" t="n">
-        <v>0.14265</v>
+        <v>0.13925</v>
       </c>
       <c r="H3" t="n">
-        <v>0.11125</v>
+        <v>0.11235</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07645</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04075</v>
+        <v>0.03995</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0201</v>
+        <v>0.0216</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009549999999999999</v>
+        <v>0.009050000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00405</v>
+        <v>0.0039</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00185</v>
+        <v>0.0018</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001</v>
+        <v>0.0008</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0002</v>
+        <v>0.00015</v>
       </c>
       <c r="Q3" t="n">
         <v>5e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>5e-05</v>
+        <v>0.0001</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -19784,55 +19786,55 @@
         <v>68.90000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>4.14</v>
+        <v>4.15</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1268</v>
+        <v>0.12615</v>
       </c>
       <c r="E4" t="n">
-        <v>0.14805</v>
+        <v>0.14755</v>
       </c>
       <c r="F4" t="n">
-        <v>0.15475</v>
+        <v>0.15795</v>
       </c>
       <c r="G4" t="n">
-        <v>0.16125</v>
+        <v>0.15885</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1424</v>
+        <v>0.141</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1141</v>
+        <v>0.1154</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07345</v>
+        <v>0.07315000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04115</v>
+        <v>0.0426</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02085</v>
+        <v>0.0202</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0097</v>
+        <v>0.0098</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0048</v>
+        <v>0.0043</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00135</v>
+        <v>0.0016</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0008</v>
+        <v>0.00095</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0003</v>
+        <v>0.00025</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00015</v>
+        <v>0.00025</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -19860,46 +19862,46 @@
         <v>4.25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1183</v>
+        <v>0.11755</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1433</v>
+        <v>0.14555</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1528</v>
+        <v>0.14885</v>
       </c>
       <c r="G5" t="n">
-        <v>0.152</v>
+        <v>0.1561</v>
       </c>
       <c r="H5" t="n">
-        <v>0.14665</v>
+        <v>0.1466</v>
       </c>
       <c r="I5" t="n">
-        <v>0.12115</v>
+        <v>0.1193</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08185000000000001</v>
+        <v>0.08175</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04355</v>
+        <v>0.04375</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02135</v>
+        <v>0.02145</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01005</v>
+        <v>0.009950000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0049</v>
+        <v>0.0053</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00255</v>
+        <v>0.00235</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00115</v>
+        <v>0.0009</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003</v>
+        <v>0.0005</v>
       </c>
       <c r="R5" t="n">
         <v>5e-05</v>
@@ -19933,52 +19935,52 @@
         <v>4.27</v>
       </c>
       <c r="D6" t="n">
-        <v>0.11415</v>
+        <v>0.1145</v>
       </c>
       <c r="E6" t="n">
-        <v>0.14155</v>
+        <v>0.1407</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1565</v>
+        <v>0.15435</v>
       </c>
       <c r="G6" t="n">
-        <v>0.15225</v>
+        <v>0.154</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1426</v>
+        <v>0.14795</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1247</v>
+        <v>0.12275</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0844</v>
+        <v>0.0804</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04345</v>
+        <v>0.0423</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0222</v>
+        <v>0.024</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0101</v>
+        <v>0.0109</v>
       </c>
       <c r="N6" t="n">
         <v>0.00495</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0024</v>
+        <v>0.00205</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0004</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.00025</v>
+        <v>0.00035</v>
       </c>
       <c r="R6" t="n">
         <v>5e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>5e-05</v>
+        <v>0.00015</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -20006,52 +20008,52 @@
         <v>4.8</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07865</v>
+        <v>0.07745</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1103</v>
+        <v>0.10975</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1318</v>
+        <v>0.1341</v>
       </c>
       <c r="G7" t="n">
-        <v>0.14395</v>
+        <v>0.1443</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1569</v>
+        <v>0.1557</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1493</v>
+        <v>0.14855</v>
       </c>
       <c r="J7" t="n">
-        <v>0.10555</v>
+        <v>0.10635</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05935</v>
+        <v>0.05895</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03175</v>
+        <v>0.03235</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01705</v>
+        <v>0.01725</v>
       </c>
       <c r="N7" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.0089</v>
       </c>
       <c r="O7" t="n">
-        <v>0.00435</v>
+        <v>0.00395</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0016</v>
+        <v>0.0018</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.00045</v>
       </c>
       <c r="R7" t="n">
         <v>0.0001</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>5e-05</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -20073,67 +20075,67 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>60.2</v>
+        <v>60.3</v>
       </c>
       <c r="C8" t="n">
         <v>7.09</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01215</v>
+        <v>0.0121</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0262</v>
+        <v>0.02595</v>
       </c>
       <c r="F8" t="n">
-        <v>0.045</v>
+        <v>0.0455</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0711</v>
       </c>
       <c r="H8" t="n">
-        <v>0.10585</v>
+        <v>0.10255</v>
       </c>
       <c r="I8" t="n">
-        <v>0.13795</v>
+        <v>0.144</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1829</v>
+        <v>0.18365</v>
       </c>
       <c r="K8" t="n">
-        <v>0.14965</v>
+        <v>0.14885</v>
       </c>
       <c r="L8" t="n">
-        <v>0.10495</v>
+        <v>0.10535</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06775</v>
+        <v>0.0667</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0417</v>
+        <v>0.04155</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02355</v>
+        <v>0.0243</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01515</v>
+        <v>0.01525</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.00705</v>
+        <v>0.00695</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0037</v>
+        <v>0.0036</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00155</v>
+        <v>0.00145</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0009</v>
+        <v>0.00075</v>
       </c>
       <c r="U8" t="n">
-        <v>0.00045</v>
+        <v>0.00015</v>
       </c>
       <c r="V8" t="n">
-        <v>0.00015</v>
+        <v>0.00025</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -20152,64 +20154,64 @@
         <v>9.08</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00165</v>
+        <v>0.00145</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0054</v>
+        <v>0.0064</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0141</v>
+        <v>0.01375</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0239</v>
+        <v>0.024</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04255</v>
+        <v>0.0425</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07514999999999999</v>
+        <v>0.07335</v>
       </c>
       <c r="J9" t="n">
-        <v>0.12245</v>
+        <v>0.1241</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1583</v>
+        <v>0.15905</v>
       </c>
       <c r="L9" t="n">
-        <v>0.14855</v>
+        <v>0.1474</v>
       </c>
       <c r="M9" t="n">
-        <v>0.126</v>
+        <v>0.1252</v>
       </c>
       <c r="N9" t="n">
-        <v>0.098</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="O9" t="n">
         <v>0.0693</v>
       </c>
       <c r="P9" t="n">
-        <v>0.04555</v>
+        <v>0.04685</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0298</v>
+        <v>0.029</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01915</v>
+        <v>0.0183</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0114</v>
+        <v>0.0118</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0049</v>
+        <v>0.00515</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0029</v>
+        <v>0.0028</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.00055</v>
       </c>
       <c r="W9" t="n">
-        <v>0.00035</v>
+        <v>0.00045</v>
       </c>
     </row>
     <row r="10">
@@ -20225,10 +20227,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0007</v>
+        <v>0.00065</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00305</v>
+        <v>0.0033</v>
       </c>
       <c r="F10" t="n">
         <v>0.0064</v>
@@ -20237,52 +20239,52 @@
         <v>0.0138</v>
       </c>
       <c r="H10" t="n">
-        <v>0.02595</v>
+        <v>0.02555</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04955</v>
+        <v>0.0493</v>
       </c>
       <c r="J10" t="n">
-        <v>0.08735</v>
+        <v>0.0893</v>
       </c>
       <c r="K10" t="n">
-        <v>0.13435</v>
+        <v>0.13235</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1456</v>
+        <v>0.1443</v>
       </c>
       <c r="M10" t="n">
-        <v>0.13795</v>
+        <v>0.13995</v>
       </c>
       <c r="N10" t="n">
-        <v>0.11685</v>
+        <v>0.1163</v>
       </c>
       <c r="O10" t="n">
-        <v>0.08925</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>0.06575</v>
+        <v>0.06455</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.04845</v>
+        <v>0.0486</v>
       </c>
       <c r="R10" t="n">
-        <v>0.03455</v>
+        <v>0.03515</v>
       </c>
       <c r="S10" t="n">
-        <v>0.02025</v>
+        <v>0.0201</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01175</v>
+        <v>0.01135</v>
       </c>
       <c r="U10" t="n">
-        <v>0.00555</v>
+        <v>0.0057</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0022</v>
+        <v>0.0024</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0007</v>
+        <v>0.00065</v>
       </c>
     </row>
     <row r="11">
@@ -20295,67 +20297,67 @@
         <v>52</v>
       </c>
       <c r="C11" t="n">
-        <v>10.34</v>
+        <v>10.33</v>
       </c>
       <c r="D11" t="n">
         <v>0.00055</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00185</v>
+        <v>0.002</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0058</v>
+        <v>0.00585</v>
       </c>
       <c r="G11" t="n">
         <v>0.0111</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02035</v>
+        <v>0.02105</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04165</v>
+        <v>0.04025</v>
       </c>
       <c r="J11" t="n">
-        <v>0.07455000000000001</v>
+        <v>0.07585</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1159</v>
+        <v>0.1156</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1395</v>
+        <v>0.13915</v>
       </c>
       <c r="M11" t="n">
-        <v>0.13705</v>
+        <v>0.13725</v>
       </c>
       <c r="N11" t="n">
-        <v>0.12805</v>
+        <v>0.12705</v>
       </c>
       <c r="O11" t="n">
-        <v>0.09765</v>
+        <v>0.0985</v>
       </c>
       <c r="P11" t="n">
-        <v>0.08165</v>
+        <v>0.082</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.05635</v>
+        <v>0.056</v>
       </c>
       <c r="R11" t="n">
-        <v>0.03655</v>
+        <v>0.037</v>
       </c>
       <c r="S11" t="n">
-        <v>0.02485</v>
+        <v>0.02375</v>
       </c>
       <c r="T11" t="n">
         <v>0.0153</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0078</v>
+        <v>0.00765</v>
       </c>
       <c r="V11" t="n">
-        <v>0.00275</v>
+        <v>0.0033</v>
       </c>
       <c r="W11" t="n">
-        <v>0.00075</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="12">
@@ -20374,61 +20376,61 @@
         <v>0.00035</v>
       </c>
       <c r="E12" t="n">
-        <v>0.00175</v>
+        <v>0.0016</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0035</v>
+        <v>0.00385</v>
       </c>
       <c r="G12" t="n">
-        <v>0.00835</v>
+        <v>0.00805</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0148</v>
+        <v>0.0144</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0308</v>
+        <v>0.03035</v>
       </c>
       <c r="J12" t="n">
-        <v>0.05775</v>
+        <v>0.05935</v>
       </c>
       <c r="K12" t="n">
-        <v>0.09555</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.12485</v>
+        <v>0.12125</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1359</v>
+        <v>0.13895</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1293</v>
+        <v>0.13115</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1186</v>
+        <v>0.11635</v>
       </c>
       <c r="P12" t="n">
-        <v>0.09205000000000001</v>
+        <v>0.09495000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0684</v>
+        <v>0.06734999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>0.04945</v>
+        <v>0.04975</v>
       </c>
       <c r="S12" t="n">
-        <v>0.032</v>
+        <v>0.03105</v>
       </c>
       <c r="T12" t="n">
-        <v>0.02035</v>
+        <v>0.0199</v>
       </c>
       <c r="U12" t="n">
-        <v>0.01035</v>
+        <v>0.01085</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0049</v>
+        <v>0.00455</v>
       </c>
       <c r="W12" t="n">
-        <v>0.001</v>
+        <v>0.00125</v>
       </c>
     </row>
     <row r="13">
@@ -20447,61 +20449,61 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00085</v>
+        <v>0.00075</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00205</v>
+        <v>0.00195</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00455</v>
+        <v>0.0053</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01115</v>
+        <v>0.01125</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0245</v>
+        <v>0.02355</v>
       </c>
       <c r="K13" t="n">
-        <v>0.04845</v>
+        <v>0.0484</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.08125</v>
       </c>
       <c r="M13" t="n">
-        <v>0.10355</v>
+        <v>0.10035</v>
       </c>
       <c r="N13" t="n">
-        <v>0.11625</v>
+        <v>0.1158</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1246</v>
+        <v>0.1263</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1206</v>
+        <v>0.12025</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1079</v>
+        <v>0.10845</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0857</v>
+        <v>0.08665</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0678</v>
+        <v>0.0673</v>
       </c>
       <c r="T13" t="n">
-        <v>0.05095</v>
+        <v>0.0505</v>
       </c>
       <c r="U13" t="n">
-        <v>0.03215</v>
+        <v>0.03155</v>
       </c>
       <c r="V13" t="n">
-        <v>0.01575</v>
+        <v>0.0154</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0049</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="14">
@@ -20520,61 +20522,61 @@
         <v>5e-05</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0001</v>
+        <v>5e-05</v>
       </c>
       <c r="F14" t="n">
-        <v>0.00025</v>
+        <v>0.00035</v>
       </c>
       <c r="G14" t="n">
-        <v>0.00085</v>
+        <v>0.00075</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00305</v>
+        <v>0.0031</v>
       </c>
       <c r="I14" t="n">
         <v>0.00705</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01655</v>
+        <v>0.01695</v>
       </c>
       <c r="K14" t="n">
-        <v>0.032</v>
+        <v>0.03165</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0547</v>
+        <v>0.05625</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0799</v>
+        <v>0.079</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1054</v>
+        <v>0.10615</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1211</v>
+        <v>0.12125</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1198</v>
+        <v>0.1167</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1143</v>
+        <v>0.1155</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1033</v>
+        <v>0.1034</v>
       </c>
       <c r="S14" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.06435</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0485</v>
+        <v>0.04835</v>
       </c>
       <c r="V14" t="n">
-        <v>0.02935</v>
+        <v>0.0298</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01265</v>
+        <v>0.0123</v>
       </c>
     </row>
     <row r="15">
@@ -20599,55 +20601,55 @@
         <v>5e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003</v>
+        <v>0.0004</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00095</v>
+        <v>0.0008</v>
       </c>
       <c r="I15" t="n">
         <v>0.00255</v>
       </c>
       <c r="J15" t="n">
-        <v>0.00555</v>
+        <v>0.0057</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01545</v>
+        <v>0.01645</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0299</v>
+        <v>0.02885</v>
       </c>
       <c r="M15" t="n">
-        <v>0.047</v>
+        <v>0.0466</v>
       </c>
       <c r="N15" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.06715</v>
       </c>
       <c r="O15" t="n">
-        <v>0.08995</v>
+        <v>0.09014999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>0.10275</v>
+        <v>0.10105</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1181</v>
+        <v>0.11565</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1204</v>
+        <v>0.12205</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1155</v>
+        <v>0.1164</v>
       </c>
       <c r="T15" t="n">
-        <v>0.105</v>
+        <v>0.1088</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08765000000000001</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0629</v>
+        <v>0.06175</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0303</v>
+        <v>0.0316</v>
       </c>
     </row>
     <row r="16">
@@ -20672,55 +20674,55 @@
         <v>5e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0004</v>
+        <v>0.00025</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.00045</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00165</v>
+        <v>0.0023</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00685</v>
+        <v>0.0054</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0114</v>
+        <v>0.01305</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02395</v>
+        <v>0.02465</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0401</v>
+        <v>0.0407</v>
       </c>
       <c r="N16" t="n">
-        <v>0.05925</v>
+        <v>0.0566</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0789</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.10315</v>
+        <v>0.10195</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.113</v>
+        <v>0.11555</v>
       </c>
       <c r="R16" t="n">
-        <v>0.12315</v>
+        <v>0.12395</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1242</v>
+        <v>0.12495</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1187</v>
+        <v>0.11535</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.097</v>
       </c>
       <c r="V16" t="n">
-        <v>0.06615</v>
+        <v>0.06605</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0318</v>
+        <v>0.03255</v>
       </c>
     </row>
     <row r="17">
@@ -20742,58 +20744,58 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>5e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00015</v>
+        <v>0.00025</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0009</v>
+        <v>0.0008</v>
       </c>
       <c r="J17" t="n">
         <v>0.00285</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0081</v>
+        <v>0.008149999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0169</v>
+        <v>0.016</v>
       </c>
       <c r="M17" t="n">
-        <v>0.02955</v>
+        <v>0.0292</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0396</v>
+        <v>0.0404</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0597</v>
+        <v>0.0606</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0824</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1032</v>
+        <v>0.10465</v>
       </c>
       <c r="R17" t="n">
-        <v>0.12385</v>
+        <v>0.1188</v>
       </c>
       <c r="S17" t="n">
-        <v>0.12895</v>
+        <v>0.1313</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1301</v>
+        <v>0.12985</v>
       </c>
       <c r="U17" t="n">
-        <v>0.12545</v>
+        <v>0.12645</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0983</v>
+        <v>0.0988</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0498</v>
+        <v>0.04915</v>
       </c>
     </row>
     <row r="18">
@@ -20806,7 +20808,7 @@
         <v>39.6</v>
       </c>
       <c r="C18" t="n">
-        <v>15.66</v>
+        <v>15.67</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -20818,55 +20820,55 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>5e-05</v>
       </c>
       <c r="H18" t="n">
         <v>0.0002</v>
       </c>
       <c r="I18" t="n">
-        <v>0.00075</v>
+        <v>0.0007</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0025</v>
+        <v>0.0023</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0066</v>
+        <v>0.0063</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01355</v>
+        <v>0.01405</v>
       </c>
       <c r="M18" t="n">
-        <v>0.02565</v>
+        <v>0.0253</v>
       </c>
       <c r="N18" t="n">
-        <v>0.039</v>
+        <v>0.0403</v>
       </c>
       <c r="O18" t="n">
-        <v>0.05855</v>
+        <v>0.0562</v>
       </c>
       <c r="P18" t="n">
-        <v>0.0751</v>
+        <v>0.07815</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.09845</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1147</v>
+        <v>0.11415</v>
       </c>
       <c r="S18" t="n">
-        <v>0.13185</v>
+        <v>0.12865</v>
       </c>
       <c r="T18" t="n">
-        <v>0.13915</v>
+        <v>0.1372</v>
       </c>
       <c r="U18" t="n">
-        <v>0.12575</v>
+        <v>0.12985</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1035</v>
+        <v>0.10465</v>
       </c>
       <c r="W18" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.06435</v>
       </c>
     </row>
     <row r="19">
@@ -20897,49 +20899,49 @@
         <v>5e-05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0005</v>
+        <v>0.00065</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00295</v>
+        <v>0.0032</v>
       </c>
       <c r="L19" t="n">
-        <v>0.00685</v>
+        <v>0.0066</v>
       </c>
       <c r="M19" t="n">
-        <v>0.01035</v>
+        <v>0.01005</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0212</v>
+        <v>0.02015</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0357</v>
+        <v>0.0352</v>
       </c>
       <c r="P19" t="n">
-        <v>0.0523</v>
+        <v>0.0536</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0731</v>
+        <v>0.0741</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0968</v>
+        <v>0.09675</v>
       </c>
       <c r="S19" t="n">
-        <v>0.11665</v>
+        <v>0.11845</v>
       </c>
       <c r="T19" t="n">
-        <v>0.14425</v>
+        <v>0.14515</v>
       </c>
       <c r="U19" t="n">
-        <v>0.16895</v>
+        <v>0.16805</v>
       </c>
       <c r="V19" t="n">
-        <v>0.162</v>
+        <v>0.1585</v>
       </c>
       <c r="W19" t="n">
-        <v>0.10805</v>
+        <v>0.1093</v>
       </c>
     </row>
     <row r="20">
@@ -20964,55 +20966,55 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>5e-05</v>
       </c>
       <c r="H20" t="n">
         <v>5e-05</v>
       </c>
       <c r="I20" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="J20" t="n">
         <v>0.0001</v>
       </c>
-      <c r="J20" t="n">
-        <v>0.00015</v>
-      </c>
       <c r="K20" t="n">
-        <v>0.00095</v>
+        <v>0.0011</v>
       </c>
       <c r="L20" t="n">
-        <v>0.00205</v>
+        <v>0.00245</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0054</v>
+        <v>0.00555</v>
       </c>
       <c r="N20" t="n">
-        <v>0.01085</v>
+        <v>0.01035</v>
       </c>
       <c r="O20" t="n">
         <v>0.0166</v>
       </c>
       <c r="P20" t="n">
-        <v>0.029</v>
+        <v>0.02815</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.0453</v>
+        <v>0.04345</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0607</v>
+        <v>0.0611</v>
       </c>
       <c r="S20" t="n">
-        <v>0.09114999999999999</v>
+        <v>0.0907</v>
       </c>
       <c r="T20" t="n">
-        <v>0.11805</v>
+        <v>0.12125</v>
       </c>
       <c r="U20" t="n">
-        <v>0.16505</v>
+        <v>0.164</v>
       </c>
       <c r="V20" t="n">
-        <v>0.23245</v>
+        <v>0.2349</v>
       </c>
       <c r="W20" t="n">
-        <v>0.22215</v>
+        <v>0.22015</v>
       </c>
     </row>
     <row r="21">
@@ -21049,43 +21051,43 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>5e-05</v>
+        <v>0.00015</v>
       </c>
       <c r="L21" t="n">
-        <v>0.00055</v>
+        <v>0.0005</v>
       </c>
       <c r="M21" t="n">
-        <v>0.001</v>
+        <v>0.00135</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0028</v>
+        <v>0.00245</v>
       </c>
       <c r="O21" t="n">
-        <v>0.00465</v>
+        <v>0.00475</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0105</v>
+        <v>0.009350000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.0151</v>
+        <v>0.01555</v>
       </c>
       <c r="R21" t="n">
-        <v>0.0276</v>
+        <v>0.0288</v>
       </c>
       <c r="S21" t="n">
-        <v>0.04865</v>
+        <v>0.04685</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0745</v>
+        <v>0.0751</v>
       </c>
       <c r="U21" t="n">
-        <v>0.12275</v>
+        <v>0.1236</v>
       </c>
       <c r="V21" t="n">
-        <v>0.219</v>
+        <v>0.2191</v>
       </c>
       <c r="W21" t="n">
-        <v>0.47285</v>
+        <v>0.47245</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan/report.xlsx
+++ b/output/japan/report.xlsx
@@ -26,7 +26,8 @@
     <sheet name="jfl outrights" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="jfl positions" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="emperors_cup outrights" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="league_cup outrights" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="emperors_cup next" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="league_cup outrights" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14424,111 +14425,111 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>65.3</v>
+        <v>69.8</v>
       </c>
       <c r="C2" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="D2" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="E2" t="n">
-        <v>41.4</v>
+        <v>43.3</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G2" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="H2" t="n">
-        <v>25.6</v>
+        <v>26.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="K2" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="L2" t="n">
         <v>5.25</v>
       </c>
       <c r="M2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="D3" t="n">
-        <v>2.37</v>
+        <v>3.8</v>
       </c>
       <c r="E3" t="n">
-        <v>37.9</v>
+        <v>45.4</v>
       </c>
       <c r="F3" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="H3" t="n">
-        <v>22.1</v>
+        <v>25.9</v>
       </c>
       <c r="I3" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="J3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="K3" t="n">
-        <v>12.5</v>
+        <v>14.2</v>
       </c>
       <c r="L3" t="n">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="M3" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61.3</v>
+        <v>64.7</v>
       </c>
       <c r="C4" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="D4" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="E4" t="n">
-        <v>36.8</v>
+        <v>37.3</v>
       </c>
       <c r="F4" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="H4" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="I4" t="n">
         <v>3.85</v>
@@ -14537,7 +14538,7 @@
         <v>1.25</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="L4" t="n">
         <v>6.5</v>
@@ -14553,40 +14554,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.6</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G5" t="n">
         <v>1.57</v>
       </c>
-      <c r="D5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E5" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.45</v>
-      </c>
       <c r="H5" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="J5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="K5" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="L5" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="6">
@@ -14596,40 +14597,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58.9</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E6" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G6" t="n">
         <v>1.6</v>
       </c>
-      <c r="D6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E6" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.44</v>
-      </c>
       <c r="H6" t="n">
-        <v>18.6</v>
+        <v>22.3</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="K6" t="n">
-        <v>10.1</v>
+        <v>11.8</v>
       </c>
       <c r="L6" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="7">
@@ -14639,40 +14640,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>56.6</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="E7" t="n">
-        <v>31.7</v>
+        <v>35.7</v>
       </c>
       <c r="F7" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="H7" t="n">
-        <v>16.7</v>
+        <v>18.2</v>
       </c>
       <c r="I7" t="n">
-        <v>4.85</v>
+        <v>4.6</v>
       </c>
       <c r="J7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="K7" t="n">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="8">
@@ -14682,40 +14683,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52.8</v>
+        <v>51.6</v>
       </c>
       <c r="C8" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="D8" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="E8" t="n">
-        <v>27</v>
+        <v>24.8</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="G8" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="H8" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="J8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="K8" t="n">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="9">
@@ -14725,40 +14726,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52.3</v>
+        <v>35.3</v>
       </c>
       <c r="C9" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="E9" t="n">
-        <v>25.8</v>
+        <v>17.6</v>
       </c>
       <c r="F9" t="n">
-        <v>3.35</v>
+        <v>4.75</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="H9" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>6.25</v>
+        <v>9.5</v>
       </c>
       <c r="J9" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="10">
@@ -14768,16 +14769,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>49.6</v>
       </c>
       <c r="C10" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="D10" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="E10" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -14786,22 +14787,22 @@
         <v>1.22</v>
       </c>
       <c r="H10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I10" t="n">
         <v>9</v>
       </c>
-      <c r="I10" t="n">
-        <v>8.5</v>
-      </c>
       <c r="J10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="L10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="11">
@@ -14811,25 +14812,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46.9</v>
+        <v>48.4</v>
       </c>
       <c r="C11" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="D11" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="E11" t="n">
-        <v>20.8</v>
+        <v>20.3</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="G11" t="n">
         <v>1.22</v>
       </c>
       <c r="H11" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>9</v>
@@ -14838,10 +14839,10 @@
         <v>1.08</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M11" t="n">
         <v>1.03</v>
@@ -14850,17 +14851,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46.3</v>
+        <v>50.4</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="D12" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="E12" t="n">
         <v>20.3</v>
@@ -14872,56 +14873,56 @@
         <v>1.22</v>
       </c>
       <c r="H12" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="L12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>43.4</v>
+        <v>34.6</v>
       </c>
       <c r="C13" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="D13" t="n">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="E13" t="n">
-        <v>17.7</v>
+        <v>15.4</v>
       </c>
       <c r="F13" t="n">
-        <v>4.6</v>
+        <v>5.25</v>
       </c>
       <c r="G13" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="H13" t="n">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="I13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="K13" t="n">
         <v>2.5</v>
@@ -14936,87 +14937,87 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>40.4</v>
+        <v>30.2</v>
       </c>
       <c r="C14" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="D14" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="E14" t="n">
-        <v>16</v>
+        <v>11.2</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="H14" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="L14" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="M14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40</v>
+        <v>27.6</v>
       </c>
       <c r="C15" t="n">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="D15" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="E15" t="n">
-        <v>14.9</v>
+        <v>10.5</v>
       </c>
       <c r="F15" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="G15" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="H15" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="L15" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="M15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="16">
@@ -15026,40 +15027,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>34.9</v>
+        <v>22.4</v>
       </c>
       <c r="C16" t="n">
-        <v>2.55</v>
+        <v>3.8</v>
       </c>
       <c r="D16" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="E16" t="n">
-        <v>11.2</v>
+        <v>7.6</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="L16" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.007</v>
       </c>
     </row>
     <row r="17">
@@ -15069,40 +15070,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32</v>
+        <v>27.6</v>
       </c>
       <c r="C17" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="E17" t="n">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="I17" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J17" t="n">
         <v>1.02</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="L17" t="n">
         <v>81</v>
       </c>
       <c r="M17" t="n">
-        <v>1.007</v>
+        <v>1.006</v>
       </c>
     </row>
   </sheetData>
@@ -15874,6 +15875,637 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:S9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>home_elo</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>away_elo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>elo_diff_adj</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>home_tilt</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>away_tilt</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prob1</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>probX</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prob2</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>expg1</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>expg2</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>over25</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>odds1</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>oddsX</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>odds2</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>oddsO25</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>oddsU25</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Vissel Kobe</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Shimizu S-Pulse</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1558</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1402</v>
+      </c>
+      <c r="F2" t="n">
+        <v>199</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9514</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.5766</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2403</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.532</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.4081</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kashima Antlers</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cerezo Osaka</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1578</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1492</v>
+      </c>
+      <c r="F3" t="n">
+        <v>129</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.0221</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.0665</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.753</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Yokohama</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1334</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1554</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-176</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.0869</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2006</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2464</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.853</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5419</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kawasaki Frontale</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Yokohama F. Marinos</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1453</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.2031</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.0961</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.789</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.6806</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Machida Zelvia</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Tokyo Verdy</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1581</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1347</v>
+      </c>
+      <c r="F6" t="n">
+        <v>277</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9714</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8273</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.6511</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.2169</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kashiwa Reysol</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fagiano Okayama</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1539</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F7" t="n">
+        <v>137</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.0781</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.5123</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.2553</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2325</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.635</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.4997</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kyoto Sanga</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sanfrecce Hiroshima</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1390</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1607</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-174</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.0214</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.0478</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.2468</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.5512</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5416</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gamba Osaka</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Urawa Reds</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1417</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1459</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.0099</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.461</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.5636</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -15951,7 +16583,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="C2" t="n">
         <v>1.22</v>
@@ -15975,16 +16607,16 @@
         <v>2.05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="K2" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="L2" t="n">
         <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="3">
@@ -15994,7 +16626,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.09999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="C3" t="n">
         <v>1.3</v>
@@ -16003,7 +16635,7 @@
         <v>3.3</v>
       </c>
       <c r="E3" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="F3" t="n">
         <v>1.83</v>
@@ -16021,7 +16653,7 @@
         <v>1.42</v>
       </c>
       <c r="K3" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="L3" t="n">
         <v>4.5</v>
@@ -16037,16 +16669,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>67.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="C4" t="n">
         <v>1.42</v>
       </c>
       <c r="D4" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="E4" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="F4" t="n">
         <v>2.2</v>
@@ -16055,7 +16687,7 @@
         <v>1.6</v>
       </c>
       <c r="H4" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="I4" t="n">
         <v>3.85</v>
@@ -16064,7 +16696,7 @@
         <v>1.25</v>
       </c>
       <c r="K4" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="L4" t="n">
         <v>7.25</v>
@@ -16080,25 +16712,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="E5" t="n">
-        <v>39.7</v>
+        <v>39.9</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="G5" t="n">
         <v>1.57</v>
       </c>
       <c r="H5" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="I5" t="n">
         <v>3.85</v>
@@ -16123,7 +16755,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.1</v>
+        <v>60.9</v>
       </c>
       <c r="C6" t="n">
         <v>1.55</v>
@@ -16132,7 +16764,7 @@
         <v>2.3</v>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="F6" t="n">
         <v>2.75</v>
@@ -16141,7 +16773,7 @@
         <v>1.4</v>
       </c>
       <c r="H6" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="I6" t="n">
         <v>5.25</v>
@@ -16150,7 +16782,7 @@
         <v>1.16</v>
       </c>
       <c r="K6" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="L6" t="n">
         <v>11</v>
@@ -16166,13 +16798,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>60.5</v>
+        <v>60.2</v>
       </c>
       <c r="C7" t="n">
         <v>1.57</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="E7" t="n">
         <v>31.8</v>
@@ -16193,7 +16825,7 @@
         <v>1.15</v>
       </c>
       <c r="K7" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="L7" t="n">
         <v>12</v>
@@ -16209,7 +16841,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58.9</v>
+        <v>59.1</v>
       </c>
       <c r="C8" t="n">
         <v>1.6</v>
@@ -16227,7 +16859,7 @@
         <v>1.38</v>
       </c>
       <c r="H8" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="I8" t="n">
         <v>6</v>
@@ -16236,13 +16868,13 @@
         <v>1.14</v>
       </c>
       <c r="K8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="9">
@@ -16261,7 +16893,7 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="F9" t="n">
         <v>3.4</v>
@@ -16304,7 +16936,7 @@
         <v>1.95</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="F10" t="n">
         <v>3.75</v>
@@ -16313,16 +16945,16 @@
         <v>1.27</v>
       </c>
       <c r="H10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>8.5</v>
       </c>
       <c r="J10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L10" t="n">
         <v>21</v>
@@ -16338,7 +16970,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
       <c r="C11" t="n">
         <v>1.87</v>
@@ -16356,7 +16988,7 @@
         <v>1.22</v>
       </c>
       <c r="H11" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I11" t="n">
         <v>10</v>
@@ -16381,7 +17013,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="C12" t="n">
         <v>2.2</v>
@@ -16390,7 +17022,7 @@
         <v>1.61</v>
       </c>
       <c r="E12" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="F12" t="n">
         <v>5.75</v>
@@ -16399,7 +17031,7 @@
         <v>1.14</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
         <v>17</v>
@@ -16408,7 +17040,7 @@
         <v>1.04</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="L12" t="n">
         <v>51</v>
@@ -16424,7 +17056,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="C13" t="n">
         <v>2.15</v>
@@ -16442,7 +17074,7 @@
         <v>1.14</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I13" t="n">
         <v>17</v>
@@ -16467,7 +17099,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="C14" t="n">
         <v>3.05</v>
@@ -16479,7 +17111,7 @@
         <v>6.4</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G14" t="n">
         <v>1.06</v>
@@ -16497,7 +17129,7 @@
         <v>0.2</v>
       </c>
       <c r="L14" t="n">
-        <v>251</v>
+        <v>201</v>
       </c>
       <c r="M14" t="n">
         <v>1.002</v>
@@ -16510,7 +17142,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.3</v>
+        <v>27.5</v>
       </c>
       <c r="C15" t="n">
         <v>3.15</v>
@@ -16519,7 +17151,7 @@
         <v>1.33</v>
       </c>
       <c r="E15" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="F15" t="n">
         <v>13</v>
@@ -16528,7 +17160,7 @@
         <v>1.05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I15" t="n">
         <v>67</v>
@@ -16537,10 +17169,10 @@
         <v>1.008</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L15" t="n">
-        <v>351</v>
+        <v>301</v>
       </c>
       <c r="M15" t="n">
         <v>1.001</v>
@@ -16556,7 +17188,7 @@
         <v>17.6</v>
       </c>
       <c r="C16" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="D16" t="n">
         <v>1.18</v>
@@ -16596,7 +17228,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
         <v>4.6</v>
@@ -16620,13 +17252,13 @@
         <v>201</v>
       </c>
       <c r="J17" t="n">
-        <v>1.002</v>
+        <v>1.003</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2501</v>
+        <v>1501</v>
       </c>
       <c r="M17" t="n">
         <v>1.001</v>

--- a/output/japan/report.xlsx
+++ b/output/japan/report.xlsx
@@ -28,6 +28,7 @@
     <sheet name="emperors_cup outrights" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="emperors_cup next" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="league_cup outrights" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="league_cup next" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -15334,7 +15335,7 @@
         <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>204.7533443915497</v>
+        <v>204.7533443915498</v>
       </c>
       <c r="D6" t="n">
         <v>0.2916666666666667</v>
@@ -15402,7 +15403,7 @@
         <v>3990</v>
       </c>
       <c r="C8" t="n">
-        <v>29.75998964065703</v>
+        <v>29.75998964065702</v>
       </c>
       <c r="D8" t="n">
         <v>0.2491228070175439</v>
@@ -15414,7 +15415,7 @@
         <v>90</v>
       </c>
       <c r="G8" t="n">
-        <v>54.26504080002923</v>
+        <v>54.26504080002922</v>
       </c>
       <c r="H8" t="n">
         <v>0.2111111111111111</v>
@@ -15844,7 +15845,7 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>97.21521947451778</v>
+        <v>97.21521947451777</v>
       </c>
       <c r="D20" t="n">
         <v>0.08333333333333333</v>
@@ -16510,7 +16511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16587,31 +16588,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="E2" t="n">
-        <v>20.7</v>
+        <v>36.2</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="G2" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="H2" t="n">
-        <v>9.199999999999999</v>
+        <v>17.2</v>
       </c>
       <c r="I2" t="n">
-        <v>8.5</v>
+        <v>4.75</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -16624,35 +16625,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63</v>
+        <v>59.9</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="E3" t="n">
-        <v>28.9</v>
+        <v>28.1</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
         <v>1.35</v>
       </c>
       <c r="H3" t="n">
-        <v>15.1</v>
+        <v>11.4</v>
       </c>
       <c r="I3" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -16665,35 +16666,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47.7</v>
+        <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="E4" t="n">
-        <v>16.2</v>
+        <v>10.6</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>7.25</v>
       </c>
       <c r="G4" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="H4" t="n">
-        <v>6.1</v>
+        <v>2.7</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="J4" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -16706,35 +16707,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68.3</v>
+        <v>52.4</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="D5" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="E5" t="n">
-        <v>35.2</v>
+        <v>21.1</v>
       </c>
       <c r="F5" t="n">
-        <v>2.55</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="H5" t="n">
-        <v>21</v>
+        <v>7.3</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -16747,35 +16748,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29.9</v>
+        <v>22.3</v>
       </c>
       <c r="C6" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="D6" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="E6" t="n">
-        <v>5.9</v>
+        <v>3.8</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G6" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="I6" t="n">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1.004</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -16788,35 +16789,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>41.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>2.2</v>
+        <v>1.45</v>
       </c>
       <c r="D7" t="n">
-        <v>1.61</v>
+        <v>2.6</v>
       </c>
       <c r="E7" t="n">
-        <v>11.8</v>
+        <v>49.8</v>
       </c>
       <c r="F7" t="n">
-        <v>6.75</v>
+        <v>1.85</v>
       </c>
       <c r="G7" t="n">
-        <v>1.12</v>
+        <v>1.85</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9</v>
+        <v>36.9</v>
       </c>
       <c r="I7" t="n">
-        <v>17</v>
+        <v>2.45</v>
       </c>
       <c r="J7" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -16829,35 +16830,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.4</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>4.75</v>
+        <v>1.55</v>
       </c>
       <c r="D8" t="n">
-        <v>1.18</v>
+        <v>2.3</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>29.6</v>
       </c>
       <c r="F8" t="n">
-        <v>34</v>
+        <v>2.95</v>
       </c>
       <c r="G8" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3</v>
+        <v>11.9</v>
       </c>
       <c r="I8" t="n">
-        <v>151</v>
+        <v>6.5</v>
       </c>
       <c r="J8" t="n">
-        <v>1.003</v>
+        <v>1.12</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -16870,35 +16871,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71.40000000000001</v>
+        <v>34.1</v>
       </c>
       <c r="C9" t="n">
-        <v>1.35</v>
+        <v>2.6</v>
       </c>
       <c r="D9" t="n">
-        <v>3.05</v>
+        <v>1.45</v>
       </c>
       <c r="E9" t="n">
-        <v>38.6</v>
+        <v>20.8</v>
       </c>
       <c r="F9" t="n">
-        <v>2.35</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="H9" t="n">
-        <v>25.4</v>
+        <v>12.1</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -16908,86 +16909,375 @@
         <v>1.001</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>home_elo</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>away_elo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>elo_diff_adj</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>home_tilt</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>away_tilt</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prob1</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>probX</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prob2</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>expg1</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>expg2</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>over25</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>odds1</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>oddsX</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>odds2</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>oddsO25</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>oddsU25</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Yokohama F. Marinos</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sanfrecce Hiroshima</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1508</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1608</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-31</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.0987</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.0345</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2642</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.427</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.597</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Mito Hollyhock</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cerezo Osaka</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1340</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1494</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-84</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9845</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.0797</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2821</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2593</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.4586</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.205</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.623</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.5371</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nagoya Grampus</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>Urawa Reds</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="E10" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="F10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="n">
-        <v>11</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
-        <v>1.001</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Yokohama F. Marinos</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="C11" t="n">
+      <c r="D4" t="n">
+        <v>1420</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1470</v>
+      </c>
+      <c r="F4" t="n">
+        <v>19</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.0947</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.0171</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3882</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2647</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.437</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5682</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.65</v>
       </c>
-      <c r="D11" t="n">
+      <c r="S4" t="n">
         <v>2.1</v>
       </c>
-      <c r="E11" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="F11" t="n">
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sagan Tosu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Kawasaki Frontale</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1252</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1459</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-138</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9292</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.2071</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2336</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.845</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.5731000000000001</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P5" t="n">
         <v>3.6</v>
       </c>
-      <c r="G11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="H11" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="I11" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
-        <v>1.001</v>
+      <c r="Q5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.15</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan/report.xlsx
+++ b/output/japan/report.xlsx
@@ -14435,7 +14435,7 @@
         <v>2.9</v>
       </c>
       <c r="E2" t="n">
-        <v>43.6</v>
+        <v>43.4</v>
       </c>
       <c r="F2" t="n">
         <v>2.1</v>
@@ -14444,7 +14444,7 @@
         <v>1.66</v>
       </c>
       <c r="H2" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="I2" t="n">
         <v>3.25</v>
@@ -14478,7 +14478,7 @@
         <v>3.85</v>
       </c>
       <c r="E3" t="n">
-        <v>45.9</v>
+        <v>46.1</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -14487,19 +14487,19 @@
         <v>1.72</v>
       </c>
       <c r="H3" t="n">
-        <v>26.5</v>
+        <v>26.8</v>
       </c>
       <c r="I3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J3" t="n">
         <v>1.32</v>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="L3" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="M3" t="n">
         <v>1.16</v>
@@ -14521,10 +14521,10 @@
         <v>2.5</v>
       </c>
       <c r="E4" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="F4" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="G4" t="n">
         <v>1.53</v>
@@ -14555,7 +14555,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72</v>
+        <v>72.2</v>
       </c>
       <c r="C5" t="n">
         <v>1.33</v>
@@ -14564,7 +14564,7 @@
         <v>3.1</v>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="F5" t="n">
         <v>2.25</v>
@@ -14573,7 +14573,7 @@
         <v>1.57</v>
       </c>
       <c r="H5" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
@@ -14582,7 +14582,7 @@
         <v>1.25</v>
       </c>
       <c r="K5" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="L5" t="n">
         <v>7</v>
@@ -14598,37 +14598,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>71.5</v>
+        <v>70.3</v>
       </c>
       <c r="C6" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="D6" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="E6" t="n">
-        <v>38.6</v>
+        <v>37.9</v>
       </c>
       <c r="F6" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="G6" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="H6" t="n">
-        <v>20.3</v>
+        <v>19.8</v>
       </c>
       <c r="I6" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
         <v>1.22</v>
       </c>
       <c r="K6" t="n">
-        <v>10.3</v>
+        <v>9.9</v>
       </c>
       <c r="L6" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>67</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="C7" t="n">
         <v>1.42</v>
@@ -14650,31 +14650,31 @@
         <v>2.65</v>
       </c>
       <c r="E7" t="n">
-        <v>36.7</v>
+        <v>36.9</v>
       </c>
       <c r="F7" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="G7" t="n">
         <v>1.5</v>
       </c>
       <c r="H7" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="I7" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="J7" t="n">
         <v>1.2</v>
       </c>
       <c r="K7" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="L7" t="n">
         <v>8</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="8">
@@ -14693,16 +14693,16 @@
         <v>1.87</v>
       </c>
       <c r="E8" t="n">
-        <v>25.1</v>
+        <v>24.7</v>
       </c>
       <c r="F8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="H8" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="I8" t="n">
         <v>6.5</v>
@@ -14711,7 +14711,7 @@
         <v>1.12</v>
       </c>
       <c r="K8" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L8" t="n">
         <v>13</v>
@@ -14727,7 +14727,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="C9" t="n">
         <v>1.83</v>
@@ -14745,7 +14745,7 @@
         <v>1.25</v>
       </c>
       <c r="H9" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="I9" t="n">
         <v>8</v>
@@ -14754,10 +14754,10 @@
         <v>1.09</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
@@ -14779,7 +14779,7 @@
         <v>1.83</v>
       </c>
       <c r="E10" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F10" t="n">
         <v>3.85</v>
@@ -14788,10 +14788,10 @@
         <v>1.25</v>
       </c>
       <c r="H10" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="I10" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
         <v>1.09</v>
@@ -14831,7 +14831,7 @@
         <v>1.18</v>
       </c>
       <c r="H11" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I11" t="n">
         <v>9</v>
@@ -14856,7 +14856,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="C12" t="n">
         <v>1.87</v>
@@ -14883,7 +14883,7 @@
         <v>1.07</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="L12" t="n">
         <v>26</v>
@@ -14899,7 +14899,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="C13" t="n">
         <v>2.65</v>
@@ -14908,10 +14908,10 @@
         <v>1.42</v>
       </c>
       <c r="E13" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="F13" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
         <v>1.14</v>
@@ -14929,7 +14929,7 @@
         <v>2.1</v>
       </c>
       <c r="L13" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
@@ -14951,7 +14951,7 @@
         <v>1.38</v>
       </c>
       <c r="E14" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="F14" t="n">
         <v>6.75</v>
@@ -14969,13 +14969,13 @@
         <v>1.04</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="L14" t="n">
         <v>41</v>
       </c>
       <c r="M14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="15">
@@ -14985,7 +14985,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="C15" t="n">
         <v>3.1</v>
@@ -14994,25 +14994,25 @@
         <v>1.33</v>
       </c>
       <c r="E15" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="F15" t="n">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="G15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="H15" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="I15" t="n">
         <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="L15" t="n">
         <v>51</v>
@@ -15024,29 +15024,29 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21.6</v>
+        <v>29.7</v>
       </c>
       <c r="C16" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="D16" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="G16" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="I16" t="n">
         <v>29</v>
@@ -15058,38 +15058,38 @@
         <v>0.6</v>
       </c>
       <c r="L16" t="n">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="M16" t="n">
-        <v>1.005</v>
+        <v>1.006</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28.5</v>
+        <v>21.6</v>
       </c>
       <c r="C17" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="D17" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="E17" t="n">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="I17" t="n">
         <v>29</v>
@@ -15098,7 +15098,7 @@
         <v>1.02</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="L17" t="n">
         <v>101</v>
@@ -15335,7 +15335,7 @@
         <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>204.7533443915497</v>
+        <v>204.7533443915498</v>
       </c>
       <c r="D6" t="n">
         <v>0.2916666666666667</v>
@@ -15403,7 +15403,7 @@
         <v>3990</v>
       </c>
       <c r="C8" t="n">
-        <v>29.75998964065703</v>
+        <v>29.75998964065702</v>
       </c>
       <c r="D8" t="n">
         <v>0.2491228070175439</v>
@@ -15415,7 +15415,7 @@
         <v>90</v>
       </c>
       <c r="G8" t="n">
-        <v>54.26504080002923</v>
+        <v>54.26504080002922</v>
       </c>
       <c r="H8" t="n">
         <v>0.2111111111111111</v>
@@ -15841,7 +15841,7 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>97.21521947451778</v>
+        <v>97.21521947451777</v>
       </c>
       <c r="D20" t="n">
         <v>0.08333333333333333</v>
@@ -16584,7 +16584,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>65.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="C2" t="n">
         <v>1.45</v>
@@ -16593,7 +16593,7 @@
         <v>2.6</v>
       </c>
       <c r="E2" t="n">
-        <v>36.1</v>
+        <v>35.9</v>
       </c>
       <c r="F2" t="n">
         <v>2.5</v>
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
       <c r="C3" t="n">
         <v>1.57</v>
@@ -16666,16 +16666,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37.9</v>
+        <v>37.6</v>
       </c>
       <c r="C4" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="D4" t="n">
         <v>1.53</v>
       </c>
       <c r="E4" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="F4" t="n">
         <v>7.5</v>
@@ -16707,7 +16707,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="C5" t="n">
         <v>1.75</v>
@@ -16716,7 +16716,7 @@
         <v>1.95</v>
       </c>
       <c r="E5" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -16725,7 +16725,7 @@
         <v>1.22</v>
       </c>
       <c r="H5" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="I5" t="n">
         <v>10</v>
@@ -16748,16 +16748,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.6</v>
+        <v>23.5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="F6" t="n">
         <v>17</v>
@@ -16772,7 +16772,7 @@
         <v>101</v>
       </c>
       <c r="J6" t="n">
-        <v>1.005</v>
+        <v>1.006</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -16798,7 +16798,7 @@
         <v>2.62</v>
       </c>
       <c r="E7" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="F7" t="n">
         <v>1.85</v>
@@ -16807,7 +16807,7 @@
         <v>1.85</v>
       </c>
       <c r="H7" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="I7" t="n">
         <v>2.4</v>
@@ -16830,7 +16830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>61.3</v>
+        <v>61.1</v>
       </c>
       <c r="C8" t="n">
         <v>1.55</v>
@@ -16839,10 +16839,10 @@
         <v>2.3</v>
       </c>
       <c r="E8" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="F8" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>1.36</v>

--- a/output/japan/report.xlsx
+++ b/output/japan/report.xlsx
@@ -14426,40 +14426,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="C2" t="n">
         <v>1.38</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="E2" t="n">
-        <v>43.4</v>
+        <v>43.1</v>
       </c>
       <c r="F2" t="n">
         <v>2.1</v>
       </c>
       <c r="G2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H2" t="n">
-        <v>26.4</v>
+        <v>26</v>
       </c>
       <c r="I2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="K2" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="M2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="3">
@@ -14469,22 +14469,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="C3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="D3" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>46.1</v>
+        <v>46.5</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="H3" t="n">
         <v>26.8</v>
@@ -14496,7 +14496,7 @@
         <v>1.32</v>
       </c>
       <c r="K3" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="L3" t="n">
         <v>5.25</v>
@@ -14512,34 +14512,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>64.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="C4" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="E4" t="n">
-        <v>38.1</v>
+        <v>39.1</v>
       </c>
       <c r="F4" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="G4" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="H4" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="I4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J4" t="n">
         <v>1.25</v>
       </c>
       <c r="K4" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="L4" t="n">
         <v>6.5</v>
@@ -14555,80 +14555,80 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="E5" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="F5" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="H5" t="n">
-        <v>21.5</v>
+        <v>22.4</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J5" t="n">
         <v>1.25</v>
       </c>
       <c r="K5" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70.3</v>
+        <v>68.7</v>
       </c>
       <c r="C6" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="D6" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="E6" t="n">
-        <v>37.9</v>
+        <v>37.3</v>
       </c>
       <c r="F6" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="G6" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="H6" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
         <v>1.22</v>
       </c>
       <c r="K6" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
@@ -14637,38 +14637,38 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>67.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="E7" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="G7" t="n">
         <v>1.5</v>
       </c>
       <c r="H7" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="I7" t="n">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="J7" t="n">
         <v>1.2</v>
       </c>
       <c r="K7" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L7" t="n">
         <v>8</v>
@@ -14684,13 +14684,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.9</v>
+        <v>50.2</v>
       </c>
       <c r="C8" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="D8" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="E8" t="n">
         <v>24.7</v>
@@ -14711,7 +14711,7 @@
         <v>1.12</v>
       </c>
       <c r="K8" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="L8" t="n">
         <v>13</v>
@@ -14727,40 +14727,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50.7</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="D9" t="n">
         <v>1.83</v>
       </c>
-      <c r="D9" t="n">
-        <v>1.87</v>
-      </c>
       <c r="E9" t="n">
-        <v>22.3</v>
+        <v>21.8</v>
       </c>
       <c r="F9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G9" t="n">
         <v>1.25</v>
       </c>
       <c r="H9" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J9" t="n">
         <v>1.09</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
         <v>19</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="10">
@@ -14770,16 +14770,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49.1</v>
+        <v>49.8</v>
       </c>
       <c r="C10" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="D10" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="E10" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="F10" t="n">
         <v>3.85</v>
@@ -14788,16 +14788,16 @@
         <v>1.25</v>
       </c>
       <c r="H10" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J10" t="n">
         <v>1.09</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L10" t="n">
         <v>19</v>
@@ -14813,25 +14813,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>35.4</v>
+        <v>34</v>
       </c>
       <c r="C11" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="D11" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="E11" t="n">
-        <v>17.4</v>
+        <v>17</v>
       </c>
       <c r="F11" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="G11" t="n">
         <v>1.18</v>
       </c>
       <c r="H11" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>9</v>
@@ -14840,7 +14840,7 @@
         <v>1.08</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
         <v>19</v>
@@ -14856,34 +14856,34 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49.3</v>
+        <v>50.9</v>
       </c>
       <c r="C12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="D12" t="n">
         <v>1.87</v>
       </c>
-      <c r="D12" t="n">
-        <v>1.83</v>
-      </c>
       <c r="E12" t="n">
-        <v>19.4</v>
+        <v>20.5</v>
       </c>
       <c r="F12" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="G12" t="n">
         <v>1.22</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
         <v>1.07</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="L12" t="n">
         <v>26</v>
@@ -14899,25 +14899,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.9</v>
+        <v>31.3</v>
       </c>
       <c r="C13" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="D13" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="E13" t="n">
-        <v>13.6</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
         <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="H13" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="I13" t="n">
         <v>13</v>
@@ -14929,7 +14929,7 @@
         <v>2.1</v>
       </c>
       <c r="L13" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
@@ -14942,16 +14942,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.2</v>
+        <v>30.9</v>
       </c>
       <c r="C14" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="D14" t="n">
         <v>1.38</v>
       </c>
       <c r="E14" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="F14" t="n">
         <v>6.75</v>
@@ -14960,7 +14960,7 @@
         <v>1.12</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
         <v>17</v>
@@ -14969,7 +14969,7 @@
         <v>1.04</v>
       </c>
       <c r="K14" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="L14" t="n">
         <v>41</v>
@@ -14985,25 +14985,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.8</v>
+        <v>26.1</v>
       </c>
       <c r="C15" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="D15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="E15" t="n">
-        <v>10.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
         <v>1.1</v>
       </c>
       <c r="H15" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I15" t="n">
         <v>19</v>
@@ -15028,16 +15028,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29.7</v>
+        <v>31.1</v>
       </c>
       <c r="C16" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="D16" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="E16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F16" t="n">
         <v>8.5</v>
@@ -15046,22 +15046,22 @@
         <v>1.09</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="I16" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
         <v>1.02</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="L16" t="n">
         <v>81</v>
       </c>
       <c r="M16" t="n">
-        <v>1.006</v>
+        <v>1.007</v>
       </c>
     </row>
     <row r="17">
@@ -15071,34 +15071,34 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21.6</v>
+        <v>20.7</v>
       </c>
       <c r="C17" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="F17" t="n">
         <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J17" t="n">
         <v>1.02</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L17" t="n">
         <v>101</v>
@@ -15335,7 +15335,7 @@
         <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>204.7533443915498</v>
+        <v>204.7533443915497</v>
       </c>
       <c r="D6" t="n">
         <v>0.2916666666666667</v>
@@ -15403,7 +15403,7 @@
         <v>3990</v>
       </c>
       <c r="C8" t="n">
-        <v>29.75998964065702</v>
+        <v>29.75998964065703</v>
       </c>
       <c r="D8" t="n">
         <v>0.2491228070175439</v>
@@ -15415,7 +15415,7 @@
         <v>90</v>
       </c>
       <c r="G8" t="n">
-        <v>54.26504080002922</v>
+        <v>54.26504080002923</v>
       </c>
       <c r="H8" t="n">
         <v>0.2111111111111111</v>
@@ -15841,7 +15841,7 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>97.21521947451777</v>
+        <v>97.21521947451778</v>
       </c>
       <c r="D20" t="n">
         <v>0.08333333333333333</v>
@@ -15999,7 +15999,7 @@
         <v>1395</v>
       </c>
       <c r="F2" t="n">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G2" t="n">
         <v>0.9503</v>
@@ -16008,37 +16008,37 @@
         <v>0.9167999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5825</v>
+        <v>0.6031</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2387</v>
+        <v>0.2222</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1788</v>
+        <v>0.1747</v>
       </c>
       <c r="L2" t="n">
-        <v>1.543</v>
+        <v>1.565</v>
       </c>
       <c r="M2" t="n">
-        <v>0.774</v>
+        <v>0.723</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4086</v>
+        <v>0.4009</v>
       </c>
       <c r="O2" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="P2" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
         <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="3">
@@ -16064,7 +16064,7 @@
         <v>1491</v>
       </c>
       <c r="F3" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G3" t="n">
         <v>1.0212</v>
@@ -16073,37 +16073,37 @@
         <v>1.0806</v>
       </c>
       <c r="I3" t="n">
-        <v>0.504</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2568</v>
+        <v>0.2403</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2392</v>
+        <v>0.2349</v>
       </c>
       <c r="L3" t="n">
-        <v>1.777</v>
+        <v>1.805</v>
       </c>
       <c r="M3" t="n">
-        <v>1.158</v>
+        <v>1.094</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5622</v>
+        <v>0.5538</v>
       </c>
       <c r="O3" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="P3" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="R3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="4">
@@ -16129,7 +16129,7 @@
         <v>1539</v>
       </c>
       <c r="F4" t="n">
-        <v>-169</v>
+        <v>-159</v>
       </c>
       <c r="G4" t="n">
         <v>1.0955</v>
@@ -16138,37 +16138,37 @@
         <v>0.9728</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2061</v>
+        <v>0.2183</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2481</v>
+        <v>0.2362</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5458</v>
+        <v>0.5455</v>
       </c>
       <c r="L4" t="n">
-        <v>1.006</v>
+        <v>1.027</v>
       </c>
       <c r="M4" t="n">
-        <v>1.829</v>
+        <v>1.773</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.5305</v>
       </c>
       <c r="O4" t="n">
-        <v>4.35</v>
+        <v>4.15</v>
       </c>
       <c r="P4" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="Q4" t="n">
         <v>1.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="5">
@@ -16194,7 +16194,7 @@
         <v>1508</v>
       </c>
       <c r="F5" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>1.2064</v>
@@ -16203,34 +16203,34 @@
         <v>1.0981</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3589</v>
+        <v>0.3771</v>
       </c>
       <c r="J5" t="n">
-        <v>0.27</v>
+        <v>0.255</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3712</v>
+        <v>0.368</v>
       </c>
       <c r="L5" t="n">
-        <v>1.731</v>
+        <v>1.763</v>
       </c>
       <c r="M5" t="n">
-        <v>1.793</v>
+        <v>1.717</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6835</v>
+        <v>0.6755</v>
       </c>
       <c r="O5" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P5" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
         <v>2.75</v>
@@ -16259,7 +16259,7 @@
         <v>1346</v>
       </c>
       <c r="F6" t="n">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="G6" t="n">
         <v>0.9522</v>
@@ -16268,37 +16268,37 @@
         <v>0.8296</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6548</v>
+        <v>0.6744</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2155</v>
+        <v>0.1996</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1297</v>
+        <v>0.126</v>
       </c>
       <c r="L6" t="n">
-        <v>1.52</v>
+        <v>1.538</v>
       </c>
       <c r="M6" t="n">
-        <v>0.581</v>
+        <v>0.537</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3507</v>
+        <v>0.3437</v>
       </c>
       <c r="O6" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="P6" t="n">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="Q6" t="n">
         <v>6.75</v>
       </c>
       <c r="R6" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="S6" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="7">
@@ -16324,7 +16324,7 @@
         <v>1436</v>
       </c>
       <c r="F7" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="G7" t="n">
         <v>1.0998</v>
@@ -16333,37 +16333,37 @@
         <v>0.9548</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5276</v>
+        <v>0.5484</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2522</v>
+        <v>0.2356</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2202</v>
+        <v>0.216</v>
       </c>
       <c r="L7" t="n">
-        <v>1.742</v>
+        <v>1.769</v>
       </c>
       <c r="M7" t="n">
-        <v>1.051</v>
+        <v>0.99</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5289</v>
+        <v>0.5206</v>
       </c>
       <c r="O7" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="P7" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="Q7" t="n">
         <v>4.15</v>
       </c>
       <c r="R7" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="S7" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="8">
@@ -16389,7 +16389,7 @@
         <v>1608</v>
       </c>
       <c r="F8" t="n">
-        <v>-179</v>
+        <v>-169</v>
       </c>
       <c r="G8" t="n">
         <v>1.0003</v>
@@ -16398,28 +16398,28 @@
         <v>1.0369</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1982</v>
+        <v>0.21</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2456</v>
+        <v>0.2339</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5562</v>
+        <v>0.5561</v>
       </c>
       <c r="L8" t="n">
-        <v>0.957</v>
+        <v>0.977</v>
       </c>
       <c r="M8" t="n">
-        <v>1.802</v>
+        <v>1.748</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5208</v>
+        <v>0.5125</v>
       </c>
       <c r="O8" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="P8" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q8" t="n">
         <v>1.72</v>
@@ -16454,7 +16454,7 @@
         <v>1469</v>
       </c>
       <c r="F9" t="n">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="G9" t="n">
         <v>1.1148</v>
@@ -16463,34 +16463,34 @@
         <v>1.0167</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3492</v>
+        <v>0.3671</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2698</v>
+        <v>0.255</v>
       </c>
       <c r="K9" t="n">
-        <v>0.381</v>
+        <v>0.3779</v>
       </c>
       <c r="L9" t="n">
-        <v>1.457</v>
+        <v>1.484</v>
       </c>
       <c r="M9" t="n">
-        <v>1.558</v>
+        <v>1.493</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.5717</v>
       </c>
       <c r="O9" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="P9" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
         <v>2.45</v>
       </c>
       <c r="R9" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="S9" t="n">
         <v>2.15</v>
@@ -16507,7 +16507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16584,31 +16584,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>65.59999999999999</v>
+        <v>54.3</v>
       </c>
       <c r="C2" t="n">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>35.9</v>
+        <v>21</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="H2" t="n">
-        <v>16.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="J2" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -16621,35 +16621,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59.6</v>
+        <v>62</v>
       </c>
       <c r="C3" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="D3" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="E3" t="n">
-        <v>27.7</v>
+        <v>27.9</v>
       </c>
       <c r="F3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
         <v>1.33</v>
       </c>
       <c r="H3" t="n">
-        <v>11.5</v>
+        <v>14.7</v>
       </c>
       <c r="I3" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -16662,35 +16662,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37.6</v>
+        <v>48.4</v>
       </c>
       <c r="C4" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="D4" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="E4" t="n">
-        <v>10.4</v>
+        <v>16.6</v>
       </c>
       <c r="F4" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -16703,35 +16703,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.5</v>
+        <v>68.3</v>
       </c>
       <c r="C5" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="E5" t="n">
-        <v>20.9</v>
+        <v>35.4</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="H5" t="n">
-        <v>7.3</v>
+        <v>21.8</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="J5" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -16744,35 +16744,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.5</v>
+        <v>30</v>
       </c>
       <c r="C6" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="D6" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="I6" t="n">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="J6" t="n">
-        <v>1.006</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -16785,35 +16785,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>66.2</v>
+        <v>41.3</v>
       </c>
       <c r="C7" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="D7" t="n">
-        <v>2.62</v>
+        <v>1.61</v>
       </c>
       <c r="E7" t="n">
-        <v>50.2</v>
+        <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>1.85</v>
+        <v>6.5</v>
       </c>
       <c r="G7" t="n">
-        <v>1.85</v>
+        <v>1.12</v>
       </c>
       <c r="H7" t="n">
-        <v>36.9</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4</v>
+        <v>17</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -16826,35 +16826,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>61.1</v>
+        <v>18.2</v>
       </c>
       <c r="C8" t="n">
-        <v>1.55</v>
+        <v>4.6</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="E8" t="n">
-        <v>29.3</v>
+        <v>2.2</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="H8" t="n">
-        <v>12.1</v>
+        <v>0.3</v>
       </c>
       <c r="I8" t="n">
-        <v>6.5</v>
+        <v>151</v>
       </c>
       <c r="J8" t="n">
-        <v>1.12</v>
+        <v>1.003</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -16867,41 +16867,123 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.8</v>
+        <v>71.7</v>
       </c>
       <c r="C9" t="n">
-        <v>2.62</v>
+        <v>1.35</v>
       </c>
       <c r="D9" t="n">
-        <v>1.44</v>
+        <v>3.05</v>
       </c>
       <c r="E9" t="n">
-        <v>21.2</v>
+        <v>39.2</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="H9" t="n">
-        <v>12.4</v>
+        <v>25.8</v>
       </c>
       <c r="I9" t="n">
-        <v>6.5</v>
+        <v>3.35</v>
       </c>
       <c r="J9" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
+        <v>1.001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Urawa Reds</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E10" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>11</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>1.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Yokohama F. Marinos</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
         <v>1.001</v>
       </c>
     </row>
@@ -17039,7 +17121,7 @@
         <v>1608</v>
       </c>
       <c r="F2" t="n">
-        <v>-31</v>
+        <v>-39</v>
       </c>
       <c r="G2" t="n">
         <v>1.0981</v>
@@ -17048,37 +17130,37 @@
         <v>1.0369</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3351</v>
+        <v>0.3261</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2642</v>
+        <v>0.2658</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4007</v>
+        <v>0.4081</v>
       </c>
       <c r="L2" t="n">
-        <v>1.428</v>
+        <v>1.511</v>
       </c>
       <c r="M2" t="n">
-        <v>1.601</v>
+        <v>1.768</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.6364</v>
       </c>
       <c r="O2" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P2" t="n">
         <v>3.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="3">
@@ -17104,7 +17186,7 @@
         <v>1491</v>
       </c>
       <c r="F3" t="n">
-        <v>-81</v>
+        <v>-89</v>
       </c>
       <c r="G3" t="n">
         <v>0.9844000000000001</v>
@@ -17113,37 +17195,37 @@
         <v>1.0806</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2852</v>
+        <v>0.2769</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2598</v>
+        <v>0.2607</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4551</v>
+        <v>0.4624</v>
       </c>
       <c r="L3" t="n">
-        <v>1.213</v>
+        <v>1.287</v>
       </c>
       <c r="M3" t="n">
-        <v>1.616</v>
+        <v>1.777</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5376</v>
+        <v>0.5909</v>
       </c>
       <c r="O3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
         <v>3.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="4">
@@ -17169,7 +17251,7 @@
         <v>1469</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>1.094</v>
@@ -17178,37 +17260,37 @@
         <v>1.0167</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3874</v>
+        <v>0.3779</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2647</v>
+        <v>0.2669</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3479</v>
+        <v>0.3551</v>
       </c>
       <c r="L4" t="n">
-        <v>1.521</v>
+        <v>1.607</v>
       </c>
       <c r="M4" t="n">
-        <v>1.437</v>
+        <v>1.596</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5674</v>
+        <v>0.6208</v>
       </c>
       <c r="O4" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="P4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="5">
@@ -17234,7 +17316,7 @@
         <v>1459</v>
       </c>
       <c r="F5" t="n">
-        <v>-137</v>
+        <v>-145</v>
       </c>
       <c r="G5" t="n">
         <v>0.929</v>
@@ -17243,37 +17325,37 @@
         <v>1.2064</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2342</v>
+        <v>0.2268</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2505</v>
+        <v>0.2508</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5153</v>
+        <v>0.5224</v>
       </c>
       <c r="L5" t="n">
-        <v>1.139</v>
+        <v>1.212</v>
       </c>
       <c r="M5" t="n">
-        <v>1.842</v>
+        <v>2.016</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5726</v>
+        <v>0.6259</v>
       </c>
       <c r="O5" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
         <v>3.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R5" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan/report.xlsx
+++ b/output/japan/report.xlsx
@@ -14426,40 +14426,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="C2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="D2" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>43.1</v>
+        <v>43.4</v>
       </c>
       <c r="F2" t="n">
         <v>2.1</v>
       </c>
       <c r="G2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H2" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="K2" t="n">
-        <v>15.3</v>
+        <v>15.8</v>
       </c>
       <c r="L2" t="n">
         <v>5.25</v>
       </c>
       <c r="M2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="3">
@@ -14469,25 +14469,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79.3</v>
+        <v>78.2</v>
       </c>
       <c r="C3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="E3" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="G3" t="n">
         <v>1.75</v>
       </c>
       <c r="H3" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="I3" t="n">
         <v>3.2</v>
@@ -14496,7 +14496,7 @@
         <v>1.32</v>
       </c>
       <c r="K3" t="n">
-        <v>15.1</v>
+        <v>15.4</v>
       </c>
       <c r="L3" t="n">
         <v>5.25</v>
@@ -14512,34 +14512,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="D4" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="E4" t="n">
-        <v>39.1</v>
+        <v>37.9</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="G4" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="H4" t="n">
-        <v>22.4</v>
+        <v>21.5</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J4" t="n">
         <v>1.25</v>
       </c>
       <c r="K4" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
         <v>6.5</v>
@@ -14555,77 +14555,77 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="E5" t="n">
-        <v>41.1</v>
+        <v>40.2</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="H5" t="n">
-        <v>22.4</v>
+        <v>21.6</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J5" t="n">
         <v>1.25</v>
       </c>
       <c r="K5" t="n">
-        <v>11.9</v>
+        <v>11.3</v>
       </c>
       <c r="L5" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="M5" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="D6" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="E6" t="n">
-        <v>37.3</v>
+        <v>38.2</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="H6" t="n">
-        <v>19.4</v>
+        <v>20.4</v>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="J6" t="n">
         <v>1.22</v>
       </c>
       <c r="K6" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="L6" t="n">
         <v>7.5</v>
@@ -14637,17 +14637,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>68.90000000000001</v>
+        <v>67</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="D7" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="E7" t="n">
         <v>36.7</v>
@@ -14659,10 +14659,10 @@
         <v>1.5</v>
       </c>
       <c r="H7" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="I7" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="J7" t="n">
         <v>1.2</v>
@@ -14684,25 +14684,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.2</v>
+        <v>51.3</v>
       </c>
       <c r="C8" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="D8" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="E8" t="n">
-        <v>24.7</v>
+        <v>25.2</v>
       </c>
       <c r="F8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="H8" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="I8" t="n">
         <v>6.5</v>
@@ -14727,120 +14727,120 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>51.3</v>
       </c>
       <c r="C9" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="D9" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="E9" t="n">
-        <v>21.8</v>
+        <v>22.7</v>
       </c>
       <c r="F9" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="G9" t="n">
         <v>1.25</v>
       </c>
       <c r="H9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
         <v>1.09</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49.8</v>
+        <v>35.9</v>
       </c>
       <c r="C10" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="E10" t="n">
-        <v>21.8</v>
+        <v>17.4</v>
       </c>
       <c r="F10" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="G10" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="H10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
         <v>19</v>
       </c>
       <c r="M10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>48.7</v>
       </c>
       <c r="C11" t="n">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="D11" t="n">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="E11" t="n">
-        <v>17</v>
+        <v>21.3</v>
       </c>
       <c r="F11" t="n">
-        <v>4.85</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="H11" t="n">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="J11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L11" t="n">
         <v>19</v>
@@ -14856,34 +14856,34 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50.9</v>
+        <v>48.7</v>
       </c>
       <c r="C12" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="D12" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="E12" t="n">
-        <v>20.5</v>
+        <v>18.8</v>
       </c>
       <c r="F12" t="n">
-        <v>4.15</v>
+        <v>4.35</v>
       </c>
       <c r="G12" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="H12" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J12" t="n">
         <v>1.07</v>
       </c>
       <c r="K12" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="L12" t="n">
         <v>26</v>
@@ -14899,25 +14899,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31.3</v>
+        <v>33.1</v>
       </c>
       <c r="C13" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>14.1</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="G13" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="H13" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I13" t="n">
         <v>13</v>
@@ -14926,7 +14926,7 @@
         <v>1.05</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>34</v>
@@ -14942,25 +14942,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.9</v>
+        <v>29.2</v>
       </c>
       <c r="C14" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="E14" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="F14" t="n">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="G14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
         <v>17</v>
@@ -14969,7 +14969,7 @@
         <v>1.04</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="L14" t="n">
         <v>41</v>
@@ -14985,34 +14985,34 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26.1</v>
+        <v>27.5</v>
       </c>
       <c r="C15" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="E15" t="n">
-        <v>9.800000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G15" t="n">
         <v>1.1</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I15" t="n">
         <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="L15" t="n">
         <v>51</v>
@@ -15024,38 +15024,38 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31.1</v>
+        <v>21.8</v>
       </c>
       <c r="C16" t="n">
-        <v>2.85</v>
+        <v>3.85</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="E16" t="n">
-        <v>9.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="F16" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J16" t="n">
         <v>1.02</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="L16" t="n">
         <v>81</v>
@@ -15067,44 +15067,44 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20.7</v>
+        <v>29.4</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="D17" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="E17" t="n">
-        <v>6.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I17" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J17" t="n">
         <v>1.02</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="L17" t="n">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="M17" t="n">
-        <v>1.005</v>
+        <v>1.006</v>
       </c>
     </row>
   </sheetData>
@@ -15335,7 +15335,7 @@
         <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>204.7533443915497</v>
+        <v>204.7533443915498</v>
       </c>
       <c r="D6" t="n">
         <v>0.2916666666666667</v>
@@ -15403,7 +15403,7 @@
         <v>3990</v>
       </c>
       <c r="C8" t="n">
-        <v>29.75998964065703</v>
+        <v>29.75998964065702</v>
       </c>
       <c r="D8" t="n">
         <v>0.2491228070175439</v>
@@ -15415,7 +15415,7 @@
         <v>90</v>
       </c>
       <c r="G8" t="n">
-        <v>54.26504080002923</v>
+        <v>54.26504080002922</v>
       </c>
       <c r="H8" t="n">
         <v>0.2111111111111111</v>
@@ -15841,7 +15841,7 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>97.21521947451778</v>
+        <v>97.21521947451777</v>
       </c>
       <c r="D20" t="n">
         <v>0.08333333333333333</v>
@@ -15999,7 +15999,7 @@
         <v>1395</v>
       </c>
       <c r="F2" t="n">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="G2" t="n">
         <v>0.9503</v>
@@ -16008,37 +16008,37 @@
         <v>0.9167999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6031</v>
+        <v>0.5826</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2222</v>
+        <v>0.2341</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1747</v>
+        <v>0.1832</v>
       </c>
       <c r="L2" t="n">
-        <v>1.565</v>
+        <v>1.495</v>
       </c>
       <c r="M2" t="n">
-        <v>0.723</v>
+        <v>0.729</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4009</v>
+        <v>0.3837</v>
       </c>
       <c r="O2" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="R2" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S2" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="3">
@@ -16064,7 +16064,7 @@
         <v>1491</v>
       </c>
       <c r="F3" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="G3" t="n">
         <v>1.0212</v>
@@ -16073,37 +16073,37 @@
         <v>1.0806</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.5036</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2403</v>
+        <v>0.2516</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2349</v>
+        <v>0.2448</v>
       </c>
       <c r="L3" t="n">
-        <v>1.805</v>
+        <v>1.718</v>
       </c>
       <c r="M3" t="n">
-        <v>1.094</v>
+        <v>1.099</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5538</v>
+        <v>0.5346</v>
       </c>
       <c r="O3" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="P3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.85</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="S3" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="4">
@@ -16129,7 +16129,7 @@
         <v>1539</v>
       </c>
       <c r="F4" t="n">
-        <v>-159</v>
+        <v>-173</v>
       </c>
       <c r="G4" t="n">
         <v>1.0955</v>
@@ -16138,37 +16138,37 @@
         <v>0.9728</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2183</v>
+        <v>0.2044</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2362</v>
+        <v>0.2412</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5455</v>
+        <v>0.5544</v>
       </c>
       <c r="L4" t="n">
-        <v>1.027</v>
+        <v>0.959</v>
       </c>
       <c r="M4" t="n">
-        <v>1.773</v>
+        <v>1.761</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5305</v>
+        <v>0.5114</v>
       </c>
       <c r="O4" t="n">
-        <v>4.15</v>
+        <v>4.35</v>
       </c>
       <c r="P4" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="R4" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="S4" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="5">
@@ -16194,7 +16194,7 @@
         <v>1508</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
       <c r="G5" t="n">
         <v>1.2064</v>
@@ -16203,37 +16203,37 @@
         <v>1.0981</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3771</v>
+        <v>0.3575</v>
       </c>
       <c r="J5" t="n">
-        <v>0.255</v>
+        <v>0.2637</v>
       </c>
       <c r="K5" t="n">
-        <v>0.368</v>
+        <v>0.3788</v>
       </c>
       <c r="L5" t="n">
-        <v>1.763</v>
+        <v>1.665</v>
       </c>
       <c r="M5" t="n">
         <v>1.717</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6755</v>
+        <v>0.6567</v>
       </c>
       <c r="O5" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P5" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="6">
@@ -16259,7 +16259,7 @@
         <v>1346</v>
       </c>
       <c r="F6" t="n">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="G6" t="n">
         <v>0.9522</v>
@@ -16268,37 +16268,37 @@
         <v>0.8296</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6744</v>
+        <v>0.6555</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1996</v>
+        <v>0.2116</v>
       </c>
       <c r="K6" t="n">
-        <v>0.126</v>
+        <v>0.1329</v>
       </c>
       <c r="L6" t="n">
-        <v>1.538</v>
+        <v>1.475</v>
       </c>
       <c r="M6" t="n">
-        <v>0.537</v>
+        <v>0.542</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3437</v>
+        <v>0.3278</v>
       </c>
       <c r="O6" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="P6" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="R6" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="S6" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="7">
@@ -16324,7 +16324,7 @@
         <v>1436</v>
       </c>
       <c r="F7" t="n">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="G7" t="n">
         <v>1.0998</v>
@@ -16333,37 +16333,37 @@
         <v>0.9548</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5484</v>
+        <v>0.5274</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2356</v>
+        <v>0.2471</v>
       </c>
       <c r="K7" t="n">
-        <v>0.216</v>
+        <v>0.2255</v>
       </c>
       <c r="L7" t="n">
-        <v>1.769</v>
+        <v>1.685</v>
       </c>
       <c r="M7" t="n">
-        <v>0.99</v>
+        <v>0.995</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5206</v>
+        <v>0.5016</v>
       </c>
       <c r="O7" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="P7" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="S7" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="8">
@@ -16389,7 +16389,7 @@
         <v>1608</v>
       </c>
       <c r="F8" t="n">
-        <v>-169</v>
+        <v>-183</v>
       </c>
       <c r="G8" t="n">
         <v>1.0003</v>
@@ -16398,37 +16398,37 @@
         <v>1.0369</v>
       </c>
       <c r="I8" t="n">
-        <v>0.21</v>
+        <v>0.1965</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2339</v>
+        <v>0.2387</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5561</v>
+        <v>0.5648</v>
       </c>
       <c r="L8" t="n">
-        <v>0.977</v>
+        <v>0.912</v>
       </c>
       <c r="M8" t="n">
-        <v>1.748</v>
+        <v>1.736</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5125</v>
+        <v>0.4935</v>
       </c>
       <c r="O8" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="P8" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="S8" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="9">
@@ -16454,7 +16454,7 @@
         <v>1469</v>
       </c>
       <c r="F9" t="n">
-        <v>-5</v>
+        <v>-19</v>
       </c>
       <c r="G9" t="n">
         <v>1.1148</v>
@@ -16463,37 +16463,37 @@
         <v>1.0167</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3671</v>
+        <v>0.3478</v>
       </c>
       <c r="J9" t="n">
-        <v>0.255</v>
+        <v>0.2635</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3779</v>
+        <v>0.3887</v>
       </c>
       <c r="L9" t="n">
-        <v>1.484</v>
+        <v>1.401</v>
       </c>
       <c r="M9" t="n">
-        <v>1.493</v>
+        <v>1.492</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5717</v>
+        <v>0.5525</v>
       </c>
       <c r="O9" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="S9" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
     </row>
   </sheetData>
@@ -16507,7 +16507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16580,329 +16580,337 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54.3</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
+        <v>1.001</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>21</v>
+        <v>60.8</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>1.55</v>
       </c>
       <c r="G2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="K2" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="M2" t="n">
         <v>1.22</v>
-      </c>
-      <c r="H2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>1.001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2.37</v>
-      </c>
+        <v>1.001</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>27.9</v>
+        <v>60.6</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1</v>
+        <v>1.55</v>
       </c>
       <c r="G3" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="H3" t="n">
-        <v>14.7</v>
+        <v>34.7</v>
       </c>
       <c r="I3" t="n">
-        <v>5.5</v>
+        <v>2.55</v>
       </c>
       <c r="J3" t="n">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>18.8</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.35</v>
+      </c>
       <c r="M3" t="n">
-        <v>1.001</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48.4</v>
+        <v>66.2</v>
       </c>
       <c r="C4" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="E4" t="n">
-        <v>16.6</v>
+        <v>42.7</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>2.15</v>
       </c>
       <c r="G4" t="n">
-        <v>1.17</v>
+        <v>1.65</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>26.4</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>3.25</v>
       </c>
       <c r="J4" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5.5</v>
+      </c>
       <c r="M4" t="n">
-        <v>1.001</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68.3</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.75</v>
-      </c>
+        <v>1.001</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>35.4</v>
+        <v>56.5</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5</v>
+        <v>1.66</v>
       </c>
       <c r="G5" t="n">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="H5" t="n">
-        <v>21.8</v>
+        <v>29.6</v>
       </c>
       <c r="I5" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="J5" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.5</v>
+      </c>
       <c r="M5" t="n">
-        <v>1.001</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="C6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.37</v>
-      </c>
+        <v>1.001</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="K6" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="L6" t="n">
         <v>6</v>
       </c>
-      <c r="F6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>51</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>1.001</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>41.3</v>
+        <v>73.3</v>
       </c>
       <c r="C7" t="n">
-        <v>2.2</v>
+        <v>1.32</v>
       </c>
       <c r="D7" t="n">
-        <v>1.61</v>
+        <v>3.25</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>31.8</v>
       </c>
       <c r="F7" t="n">
-        <v>6.5</v>
+        <v>2.75</v>
       </c>
       <c r="G7" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>12.8</v>
       </c>
       <c r="I7" t="n">
-        <v>17</v>
+        <v>6.25</v>
       </c>
       <c r="J7" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
+        <v>5.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>13</v>
+      </c>
       <c r="M7" t="n">
-        <v>1.001</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>4.6</v>
+        <v>1.22</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2</v>
+        <v>4.25</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2</v>
+        <v>30.5</v>
       </c>
       <c r="F8" t="n">
-        <v>29</v>
+        <v>2.87</v>
       </c>
       <c r="G8" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>151</v>
+        <v>7.25</v>
       </c>
       <c r="J8" t="n">
-        <v>1.003</v>
+        <v>1.11</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>3.9</v>
+      </c>
+      <c r="L8" t="n">
+        <v>17</v>
+      </c>
       <c r="M8" t="n">
-        <v>1.001</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71.7</v>
+        <v>33.8</v>
       </c>
       <c r="C9" t="n">
-        <v>1.35</v>
+        <v>2.62</v>
       </c>
       <c r="D9" t="n">
-        <v>3.05</v>
+        <v>1.44</v>
       </c>
       <c r="E9" t="n">
-        <v>39.2</v>
+        <v>16.4</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55</v>
+        <v>1.17</v>
       </c>
       <c r="H9" t="n">
-        <v>25.8</v>
+        <v>7.8</v>
       </c>
       <c r="I9" t="n">
-        <v>3.35</v>
+        <v>9.5</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>19</v>
+      </c>
       <c r="M9" t="n">
-        <v>1.001</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="10">
@@ -16912,78 +16920,168 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49.5</v>
+        <v>58.2</v>
       </c>
       <c r="C10" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="D10" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="E10" t="n">
-        <v>17.3</v>
+        <v>23.1</v>
       </c>
       <c r="F10" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="G10" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>3.3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>21</v>
+      </c>
       <c r="M10" t="n">
-        <v>1.001</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>56.5</v>
+        <v>41.8</v>
       </c>
       <c r="C11" t="n">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="D11" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="E11" t="n">
-        <v>22.4</v>
+        <v>13.8</v>
       </c>
       <c r="F11" t="n">
-        <v>3.75</v>
+        <v>5.75</v>
       </c>
       <c r="G11" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="H11" t="n">
-        <v>10.3</v>
+        <v>4.1</v>
       </c>
       <c r="I11" t="n">
-        <v>7.5</v>
+        <v>17</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>1.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>41</v>
+      </c>
       <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Mito Hollyhock</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>51</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>201</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.002</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sagan Tosu</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>26</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>151</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>751</v>
+      </c>
+      <c r="M13" t="n">
         <v>1.001</v>
       </c>
     </row>
@@ -17121,7 +17219,7 @@
         <v>1608</v>
       </c>
       <c r="F2" t="n">
-        <v>-39</v>
+        <v>-42</v>
       </c>
       <c r="G2" t="n">
         <v>1.0981</v>
@@ -17130,37 +17228,37 @@
         <v>1.0369</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3261</v>
+        <v>0.323</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2658</v>
+        <v>0.2662</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4081</v>
+        <v>0.4108</v>
       </c>
       <c r="L2" t="n">
-        <v>1.511</v>
+        <v>1.399</v>
       </c>
       <c r="M2" t="n">
-        <v>1.768</v>
+        <v>1.636</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6364</v>
+        <v>0.5845</v>
       </c>
       <c r="O2" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="P2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q2" t="n">
         <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="S2" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="3">
@@ -17186,7 +17284,7 @@
         <v>1491</v>
       </c>
       <c r="F3" t="n">
-        <v>-89</v>
+        <v>-92</v>
       </c>
       <c r="G3" t="n">
         <v>0.9844000000000001</v>
@@ -17195,25 +17293,25 @@
         <v>1.0806</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2769</v>
+        <v>0.274</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2607</v>
+        <v>0.2609</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4624</v>
+        <v>0.4651</v>
       </c>
       <c r="L3" t="n">
-        <v>1.287</v>
+        <v>1.187</v>
       </c>
       <c r="M3" t="n">
-        <v>1.777</v>
+        <v>1.648</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5909</v>
+        <v>0.5389</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
         <v>3.5</v>
@@ -17222,10 +17320,10 @@
         <v>2.05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -17251,7 +17349,7 @@
         <v>1469</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
         <v>1.094</v>
@@ -17260,37 +17358,37 @@
         <v>1.0167</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3779</v>
+        <v>0.3746</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2669</v>
+        <v>0.2676</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3551</v>
+        <v>0.3578</v>
       </c>
       <c r="L4" t="n">
-        <v>1.607</v>
+        <v>1.493</v>
       </c>
       <c r="M4" t="n">
-        <v>1.596</v>
+        <v>1.472</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6208</v>
+        <v>0.5687</v>
       </c>
       <c r="O4" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="P4" t="n">
         <v>3.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="5">
@@ -17316,7 +17414,7 @@
         <v>1459</v>
       </c>
       <c r="F5" t="n">
-        <v>-145</v>
+        <v>-148</v>
       </c>
       <c r="G5" t="n">
         <v>0.929</v>
@@ -17325,22 +17423,22 @@
         <v>1.2064</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2268</v>
+        <v>0.2243</v>
       </c>
       <c r="J5" t="n">
         <v>0.2508</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5224</v>
+        <v>0.525</v>
       </c>
       <c r="L5" t="n">
-        <v>1.212</v>
+        <v>1.113</v>
       </c>
       <c r="M5" t="n">
-        <v>2.016</v>
+        <v>1.874</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6259</v>
+        <v>0.5739</v>
       </c>
       <c r="O5" t="n">
         <v>4</v>
@@ -17352,10 +17450,10 @@
         <v>1.83</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan/report.xlsx
+++ b/output/japan/report.xlsx
@@ -12128,63 +12128,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J-Lease FC</t>
+          <t>Honda</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tokyo Musashino City</t>
+          <t>Maruyasu Okazaki</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>662</v>
+        <v>1032</v>
       </c>
       <c r="E2" t="n">
-        <v>830</v>
+        <v>881</v>
       </c>
       <c r="F2" t="n">
-        <v>-152</v>
+        <v>168</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9701</v>
+        <v>0.948</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9104</v>
+        <v>0.9179</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2222</v>
+        <v>0.5493</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2448</v>
+        <v>0.2413</v>
       </c>
       <c r="K2" t="n">
-        <v>0.533</v>
+        <v>0.2094</v>
       </c>
       <c r="L2" t="n">
-        <v>0.853</v>
+        <v>1.459</v>
       </c>
       <c r="M2" t="n">
-        <v>1.447</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>0.404</v>
+        <v>0.395</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>1.75</v>
       </c>
       <c r="P2" t="n">
         <v>3.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="R2" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S2" t="n">
         <v>1.57</v>
@@ -12198,61 +12198,61 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Honda</t>
+          <t>Honda Lock</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Maruyasu Okazaki</t>
+          <t>J-Lease FC</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1032</v>
+        <v>883</v>
       </c>
       <c r="E3" t="n">
-        <v>881</v>
+        <v>662</v>
       </c>
       <c r="F3" t="n">
-        <v>168</v>
+        <v>237</v>
       </c>
       <c r="G3" t="n">
-        <v>0.948</v>
+        <v>1.024</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9179</v>
+        <v>0.9701</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5493</v>
+        <v>0.6196</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2413</v>
+        <v>0.2225</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2094</v>
+        <v>0.1579</v>
       </c>
       <c r="L3" t="n">
-        <v>1.459</v>
+        <v>1.809</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.779</v>
       </c>
       <c r="N3" t="n">
-        <v>0.395</v>
+        <v>0.4783</v>
       </c>
       <c r="O3" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="P3" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="S3" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="4">
@@ -12263,61 +12263,61 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Honda Lock</t>
+          <t>Tokyo Musashino City</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>J-Lease FC</t>
+          <t>Urayasu</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>883</v>
+        <v>830</v>
       </c>
       <c r="E4" t="n">
-        <v>662</v>
+        <v>924</v>
       </c>
       <c r="F4" t="n">
-        <v>237</v>
+        <v>-78</v>
       </c>
       <c r="G4" t="n">
-        <v>1.024</v>
+        <v>0.9104</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9701</v>
+        <v>0.9114</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6196</v>
+        <v>0.2895</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2225</v>
+        <v>0.2576</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1579</v>
+        <v>0.453</v>
       </c>
       <c r="L4" t="n">
-        <v>1.809</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.779</v>
+        <v>1.224</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4783</v>
+        <v>0.3668</v>
       </c>
       <c r="O4" t="n">
-        <v>1.57</v>
+        <v>3.15</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
@@ -12328,61 +12328,61 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tokyo Musashino City</t>
+          <t>VONDS Ichihara</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Urayasu</t>
+          <t>Okinawa SV</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>830</v>
+        <v>921</v>
       </c>
       <c r="E5" t="n">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="F5" t="n">
-        <v>-78</v>
+        <v>17</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9104</v>
+        <v>0.9648</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9114</v>
+        <v>1.0684</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2895</v>
+        <v>0.3874</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2576</v>
+        <v>0.2621</v>
       </c>
       <c r="K5" t="n">
-        <v>0.453</v>
+        <v>0.3505</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9360000000000001</v>
+        <v>1.385</v>
       </c>
       <c r="M5" t="n">
-        <v>1.224</v>
+        <v>1.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3668</v>
+        <v>0.5026</v>
       </c>
       <c r="O5" t="n">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="P5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="R5" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="6">
@@ -12393,61 +12393,61 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VONDS Ichihara</t>
+          <t>Veertien Mie</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Okinawa SV</t>
+          <t>Azul Claro Numazu</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>921</v>
+        <v>1011</v>
       </c>
       <c r="E6" t="n">
-        <v>920</v>
+        <v>966</v>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9648</v>
+        <v>0.896</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0684</v>
+        <v>0.9951</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3874</v>
+        <v>0.4349</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2621</v>
+        <v>0.2594</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3505</v>
+        <v>0.3058</v>
       </c>
       <c r="L6" t="n">
-        <v>1.385</v>
+        <v>1.286</v>
       </c>
       <c r="M6" t="n">
-        <v>1.3</v>
+        <v>1.036</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5026</v>
+        <v>0.4098</v>
       </c>
       <c r="O6" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="P6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="S6" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="7">
@@ -12458,61 +12458,61 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Veertien Mie</t>
+          <t>YSCC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azul Claro Numazu</t>
+          <t>Reinmeer Aomori</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1011</v>
+        <v>877</v>
       </c>
       <c r="E7" t="n">
-        <v>966</v>
+        <v>954</v>
       </c>
       <c r="F7" t="n">
-        <v>61</v>
+        <v>-60</v>
       </c>
       <c r="G7" t="n">
-        <v>0.896</v>
+        <v>1.1926</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9951</v>
+        <v>0.9447</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4349</v>
+        <v>0.3066</v>
       </c>
       <c r="J7" t="n">
         <v>0.2594</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3058</v>
+        <v>0.4339</v>
       </c>
       <c r="L7" t="n">
-        <v>1.286</v>
+        <v>1.316</v>
       </c>
       <c r="M7" t="n">
-        <v>1.036</v>
+        <v>1.619</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4098</v>
+        <v>0.5619</v>
       </c>
       <c r="O7" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
         <v>3.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="8">
@@ -12718,16 +12718,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.6</v>
+        <v>30.2</v>
       </c>
       <c r="C2" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="D2" t="n">
         <v>1.38</v>
       </c>
       <c r="E2" t="n">
-        <v>76.5</v>
+        <v>76.2</v>
       </c>
       <c r="F2" t="n">
         <v>1.27</v>
@@ -12739,7 +12739,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>3501</v>
+        <v>1501</v>
       </c>
       <c r="J2" t="n">
         <v>1.001</v>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="C3" t="n">
         <v>4</v>
@@ -12761,13 +12761,13 @@
         <v>1.22</v>
       </c>
       <c r="E3" t="n">
-        <v>66.90000000000001</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="G3" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -12786,7 +12786,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>16.3</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
@@ -12795,10 +12795,10 @@
         <v>1.17</v>
       </c>
       <c r="E4" t="n">
-        <v>59.1</v>
+        <v>58.3</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G4" t="n">
         <v>2.2</v>
@@ -12820,16 +12820,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="E5" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
       <c r="F5" t="n">
         <v>1.95</v>
@@ -12838,10 +12838,10 @@
         <v>1.75</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>501</v>
+        <v>301</v>
       </c>
       <c r="J5" t="n">
         <v>1.001</v>
@@ -12854,7 +12854,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="C6" t="n">
         <v>8.5</v>
@@ -12863,10 +12863,10 @@
         <v>1.09</v>
       </c>
       <c r="E6" t="n">
-        <v>44.1</v>
+        <v>43.9</v>
       </c>
       <c r="F6" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="G6" t="n">
         <v>1.67</v>
@@ -12875,7 +12875,7 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>201</v>
+        <v>251</v>
       </c>
       <c r="J6" t="n">
         <v>1.002</v>
@@ -12888,19 +12888,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="E7" t="n">
-        <v>37.9</v>
+        <v>38.2</v>
       </c>
       <c r="F7" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="G7" t="n">
         <v>1.53</v>
@@ -12909,10 +12909,10 @@
         <v>0.3</v>
       </c>
       <c r="I7" t="n">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="J7" t="n">
-        <v>1.003</v>
+        <v>1.002</v>
       </c>
     </row>
     <row r="8">
@@ -12922,7 +12922,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="C8" t="n">
         <v>23</v>
@@ -12931,22 +12931,22 @@
         <v>1.03</v>
       </c>
       <c r="E8" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="F8" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G8" t="n">
         <v>1.25</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="I8" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>1.008</v>
       </c>
     </row>
     <row r="9">
@@ -12956,25 +12956,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="C9" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
         <v>1.02</v>
       </c>
       <c r="E9" t="n">
-        <v>16.9</v>
+        <v>17.4</v>
       </c>
       <c r="F9" t="n">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="G9" t="n">
         <v>1.18</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="I9" t="n">
         <v>41</v>
@@ -12990,7 +12990,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="C10" t="n">
         <v>67</v>
@@ -13030,19 +13030,19 @@
         <v>101</v>
       </c>
       <c r="D11" t="n">
-        <v>1.006</v>
+        <v>1.005</v>
       </c>
       <c r="E11" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
         <v>1.08</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
         <v>17</v>
@@ -13058,7 +13058,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C12" t="n">
         <v>151</v>
@@ -13076,13 +13076,13 @@
         <v>1.05</v>
       </c>
       <c r="H12" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
         <v>11</v>
       </c>
       <c r="J12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="13">
@@ -13092,10 +13092,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C13" t="n">
-        <v>501</v>
+        <v>301</v>
       </c>
       <c r="D13" t="n">
         <v>1.001</v>
@@ -13110,13 +13110,13 @@
         <v>1.02</v>
       </c>
       <c r="H13" t="n">
-        <v>12.1</v>
+        <v>12.6</v>
       </c>
       <c r="I13" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="J13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="14">
@@ -13135,7 +13135,7 @@
         <v>1.001</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
         <v>34</v>
@@ -13144,13 +13144,13 @@
         <v>1.02</v>
       </c>
       <c r="H14" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="I14" t="n">
         <v>5.75</v>
       </c>
       <c r="J14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="15">
@@ -13169,7 +13169,7 @@
         <v>1.001</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F15" t="n">
         <v>34</v>
@@ -13178,13 +13178,13 @@
         <v>1.02</v>
       </c>
       <c r="H15" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="J15" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="16">
@@ -13212,7 +13212,7 @@
         <v>1.002</v>
       </c>
       <c r="H16" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
@@ -13237,7 +13237,9 @@
       <c r="E17" t="n">
         <v>0</v>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>5001</v>
+      </c>
       <c r="G17" t="n">
         <v>1.001</v>
       </c>
@@ -13369,55 +13371,55 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
       <c r="C2" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3057</v>
+        <v>0.30155</v>
       </c>
       <c r="E2" t="n">
-        <v>0.20345</v>
+        <v>0.2048</v>
       </c>
       <c r="F2" t="n">
-        <v>0.14665</v>
+        <v>0.1465</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1095</v>
+        <v>0.1089</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07704999999999999</v>
+        <v>0.07925</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0541</v>
+        <v>0.05485</v>
       </c>
       <c r="J2" t="n">
-        <v>0.038</v>
+        <v>0.03935</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0266</v>
+        <v>0.02615</v>
       </c>
       <c r="L2" t="n">
-        <v>0.017</v>
+        <v>0.01655</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0105</v>
+        <v>0.00975</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00585</v>
+        <v>0.0071</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0034</v>
+        <v>0.00305</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0017</v>
+        <v>0.0015</v>
       </c>
       <c r="Q2" t="n">
         <v>0.0004</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0001</v>
+        <v>0.0003</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -13433,49 +13435,49 @@
         <v>51.3</v>
       </c>
       <c r="C3" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2102</v>
+        <v>0.20695</v>
       </c>
       <c r="E3" t="n">
-        <v>0.18745</v>
+        <v>0.1902</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1524</v>
+        <v>0.15355</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1185</v>
+        <v>0.12315</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09555</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.074</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0549</v>
+        <v>0.05295</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0392</v>
+        <v>0.0401</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02755</v>
+        <v>0.02465</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01715</v>
+        <v>0.01885</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01125</v>
+        <v>0.0106</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00665</v>
+        <v>0.0054</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0035</v>
+        <v>0.00345</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00135</v>
+        <v>0.0013</v>
       </c>
       <c r="R3" t="n">
         <v>0.00035</v>
@@ -13494,52 +13496,52 @@
         <v>50.2</v>
       </c>
       <c r="C4" t="n">
-        <v>4.38</v>
+        <v>4.4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.15985</v>
+        <v>0.1629</v>
       </c>
       <c r="E4" t="n">
-        <v>0.15765</v>
+        <v>0.15125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.14545</v>
+        <v>0.14285</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1277</v>
+        <v>0.12625</v>
       </c>
       <c r="H4" t="n">
-        <v>0.101</v>
+        <v>0.11025</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08735</v>
+        <v>0.08795</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07025000000000001</v>
+        <v>0.06455</v>
       </c>
       <c r="K4" t="n">
         <v>0.05155</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03735</v>
+        <v>0.0386</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02535</v>
+        <v>0.0266</v>
       </c>
       <c r="N4" t="n">
-        <v>0.018</v>
+        <v>0.0174</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0097</v>
+        <v>0.0101</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00565</v>
+        <v>0.0062</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0026</v>
+        <v>0.0029</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0005</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>5e-05</v>
@@ -13558,52 +13560,52 @@
         <v>5.18</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0961</v>
+        <v>0.099</v>
       </c>
       <c r="E5" t="n">
-        <v>0.121</v>
+        <v>0.1165</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1231</v>
+        <v>0.12625</v>
       </c>
       <c r="G5" t="n">
-        <v>0.12745</v>
+        <v>0.12385</v>
       </c>
       <c r="H5" t="n">
-        <v>0.11965</v>
+        <v>0.1218</v>
       </c>
       <c r="I5" t="n">
-        <v>0.10615</v>
+        <v>0.1043</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08655</v>
+        <v>0.0878</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07155</v>
+        <v>0.0693</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05365</v>
+        <v>0.05375</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03535</v>
+        <v>0.03965</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0261</v>
+        <v>0.0258</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01705</v>
+        <v>0.0172</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0107</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.00465</v>
+        <v>0.00435</v>
       </c>
       <c r="R5" t="n">
-        <v>0.00085</v>
+        <v>0.00145</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="6">
@@ -13613,58 +13615,58 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
       <c r="C6" t="n">
-        <v>5.4</v>
+        <v>5.42</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.09064999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.10935</v>
+        <v>0.11005</v>
       </c>
       <c r="F6" t="n">
-        <v>0.12</v>
+        <v>0.1184</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1209</v>
+        <v>0.11995</v>
       </c>
       <c r="H6" t="n">
-        <v>0.119</v>
+        <v>0.11495</v>
       </c>
       <c r="I6" t="n">
-        <v>0.10425</v>
+        <v>0.1062</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0924</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0731</v>
+        <v>0.07335</v>
       </c>
       <c r="L6" t="n">
-        <v>0.057</v>
+        <v>0.0575</v>
       </c>
       <c r="M6" t="n">
-        <v>0.04245</v>
+        <v>0.04435</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03005</v>
+        <v>0.02945</v>
       </c>
       <c r="O6" t="n">
         <v>0.02105</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01205</v>
+        <v>0.01315</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0056</v>
+        <v>0.0061</v>
       </c>
       <c r="R6" t="n">
-        <v>0.00215</v>
+        <v>0.002</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00025</v>
+        <v>5e-05</v>
       </c>
     </row>
     <row r="7">
@@ -13677,55 +13679,55 @@
         <v>47.1</v>
       </c>
       <c r="C7" t="n">
-        <v>5.9</v>
+        <v>5.88</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0687</v>
+        <v>0.0674</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0905</v>
       </c>
       <c r="F7" t="n">
-        <v>0.10525</v>
+        <v>0.1102</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1144</v>
+        <v>0.1137</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1183</v>
+        <v>0.11245</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1063</v>
+        <v>0.10985</v>
       </c>
       <c r="J7" t="n">
-        <v>0.09304999999999999</v>
+        <v>0.09594999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0822</v>
+        <v>0.0808</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06795</v>
+        <v>0.07174999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05435</v>
+        <v>0.05365</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0415</v>
+        <v>0.03945</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0285</v>
+        <v>0.0263</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0172</v>
+        <v>0.0173</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0081</v>
+        <v>0.008149999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00325</v>
+        <v>0.00245</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00015</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="8">
@@ -13738,52 +13740,52 @@
         <v>44.1</v>
       </c>
       <c r="C8" t="n">
-        <v>7.31</v>
+        <v>7.33</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02845</v>
+        <v>0.0289</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0459</v>
+        <v>0.0499</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0696</v>
+        <v>0.064</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0804</v>
+        <v>0.0818</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.10415</v>
+        <v>0.10105</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1131</v>
+        <v>0.10785</v>
       </c>
       <c r="K8" t="n">
-        <v>0.10115</v>
+        <v>0.10635</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09415</v>
+        <v>0.09404999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0815</v>
+        <v>0.08525000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0658</v>
+        <v>0.06745</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05235</v>
+        <v>0.05195</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0375</v>
+        <v>0.0377</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0216</v>
+        <v>0.0232</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01005</v>
+        <v>0.008149999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>0.0005999999999999999</v>
@@ -13799,55 +13801,55 @@
         <v>42.7</v>
       </c>
       <c r="C9" t="n">
-        <v>7.96</v>
+        <v>7.95</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0199</v>
+        <v>0.0208</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0341</v>
+        <v>0.03745</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0491</v>
+        <v>0.0503</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0663</v>
+        <v>0.065</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08065</v>
+        <v>0.07845000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.09395000000000001</v>
       </c>
       <c r="J9" t="n">
+        <v>0.10235</v>
+      </c>
+      <c r="K9" t="n">
         <v>0.1056</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.1102</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.10135</v>
+        <v>0.10385</v>
       </c>
       <c r="M9" t="n">
-        <v>0.09395000000000001</v>
+        <v>0.09675</v>
       </c>
       <c r="N9" t="n">
-        <v>0.08225</v>
+        <v>0.081</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0679</v>
+        <v>0.06755</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0487</v>
+        <v>0.0501</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03065</v>
+        <v>0.03145</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0153</v>
+        <v>0.0142</v>
       </c>
       <c r="S9" t="n">
-        <v>0.00125</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="10">
@@ -13860,55 +13862,55 @@
         <v>40.8</v>
       </c>
       <c r="C10" t="n">
-        <v>9.1</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0086</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01875</v>
+        <v>0.01845</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0296</v>
+        <v>0.0287</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0414</v>
+        <v>0.0426</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0531</v>
+        <v>0.0568</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.07035</v>
       </c>
       <c r="J10" t="n">
-        <v>0.08555</v>
+        <v>0.0873</v>
       </c>
       <c r="K10" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.098</v>
       </c>
       <c r="L10" t="n">
-        <v>0.11025</v>
+        <v>0.1073</v>
       </c>
       <c r="M10" t="n">
-        <v>0.11185</v>
+        <v>0.10975</v>
       </c>
       <c r="N10" t="n">
-        <v>0.11085</v>
+        <v>0.10745</v>
       </c>
       <c r="O10" t="n">
-        <v>0.09755</v>
+        <v>0.0993</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0766</v>
+        <v>0.07545</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.05515</v>
+        <v>0.0607</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0251</v>
+        <v>0.0261</v>
       </c>
       <c r="S10" t="n">
-        <v>0.00365</v>
+        <v>0.00335</v>
       </c>
     </row>
     <row r="11">
@@ -13921,55 +13923,55 @@
         <v>40.2</v>
       </c>
       <c r="C11" t="n">
-        <v>9.460000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0062</v>
+        <v>0.0061</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01475</v>
+        <v>0.0145</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02565</v>
+        <v>0.02425</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0344</v>
+        <v>0.0373</v>
       </c>
       <c r="H11" t="n">
-        <v>0.05115</v>
+        <v>0.0503</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06405</v>
+        <v>0.0669</v>
       </c>
       <c r="J11" t="n">
-        <v>0.07785</v>
+        <v>0.08</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0941</v>
+        <v>0.09254999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1096</v>
+        <v>0.10455</v>
       </c>
       <c r="M11" t="n">
-        <v>0.11405</v>
+        <v>0.1101</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1063</v>
+        <v>0.11365</v>
       </c>
       <c r="O11" t="n">
-        <v>0.10585</v>
+        <v>0.104</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0881</v>
+        <v>0.08595</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.06975000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>0.03745</v>
+        <v>0.0359</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0039</v>
+        <v>0.0042</v>
       </c>
     </row>
     <row r="12">
@@ -13982,55 +13984,55 @@
         <v>38.2</v>
       </c>
       <c r="C12" t="n">
-        <v>10.34</v>
+        <v>10.32</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00325</v>
+        <v>0.00355</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0072</v>
+        <v>0.0081</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0141</v>
+        <v>0.01445</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02545</v>
+        <v>0.02345</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0345</v>
+        <v>0.03505</v>
       </c>
       <c r="I12" t="n">
-        <v>0.04675</v>
+        <v>0.0454</v>
       </c>
       <c r="J12" t="n">
-        <v>0.05875</v>
+        <v>0.0639</v>
       </c>
       <c r="K12" t="n">
-        <v>0.08</v>
+        <v>0.07895000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0948</v>
+        <v>0.0958</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1095</v>
+        <v>0.10685</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1201</v>
+        <v>0.1171</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1196</v>
+        <v>0.1243</v>
       </c>
       <c r="P12" t="n">
-        <v>0.11485</v>
+        <v>0.1154</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.10385</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>0.05785</v>
+        <v>0.0613</v>
       </c>
       <c r="S12" t="n">
-        <v>0.00945</v>
+        <v>0.0092</v>
       </c>
     </row>
     <row r="13">
@@ -14043,55 +14045,55 @@
         <v>36.3</v>
       </c>
       <c r="C13" t="n">
-        <v>11.24</v>
+        <v>11.25</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0008</v>
+        <v>0.00165</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0032</v>
+        <v>0.00355</v>
       </c>
       <c r="F13" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.008149999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0141</v>
+        <v>0.01285</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0222</v>
+        <v>0.0214</v>
       </c>
       <c r="I13" t="n">
-        <v>0.03045</v>
+        <v>0.0313</v>
       </c>
       <c r="J13" t="n">
-        <v>0.04525</v>
+        <v>0.04485</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0592</v>
+        <v>0.0624</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07795000000000001</v>
+        <v>0.07704999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>0.09535</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>0.11515</v>
+        <v>0.11265</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1261</v>
+        <v>0.12885</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1398</v>
+        <v>0.1409</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.14195</v>
+        <v>0.138</v>
       </c>
       <c r="R13" t="n">
-        <v>0.10505</v>
+        <v>0.10955</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01555</v>
+        <v>0.01655</v>
       </c>
     </row>
     <row r="14">
@@ -14104,55 +14106,55 @@
         <v>35.5</v>
       </c>
       <c r="C14" t="n">
-        <v>11.6</v>
+        <v>11.58</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00095</v>
+        <v>0.00105</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0032</v>
+        <v>0.0022</v>
       </c>
       <c r="F14" t="n">
-        <v>0.00515</v>
+        <v>0.00635</v>
       </c>
       <c r="G14" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.01015</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0161</v>
+        <v>0.01625</v>
       </c>
       <c r="I14" t="n">
-        <v>0.02575</v>
+        <v>0.0248</v>
       </c>
       <c r="J14" t="n">
-        <v>0.03855</v>
+        <v>0.03875</v>
       </c>
       <c r="K14" t="n">
-        <v>0.05195</v>
+        <v>0.0518</v>
       </c>
       <c r="L14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0667</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0878</v>
+        <v>0.09035</v>
       </c>
       <c r="N14" t="n">
-        <v>0.10655</v>
+        <v>0.1121</v>
       </c>
       <c r="O14" t="n">
-        <v>0.13135</v>
+        <v>0.13335</v>
       </c>
       <c r="P14" t="n">
-        <v>0.15365</v>
+        <v>0.14805</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1577</v>
+        <v>0.1569</v>
       </c>
       <c r="R14" t="n">
-        <v>0.12085</v>
+        <v>0.11985</v>
       </c>
       <c r="S14" t="n">
-        <v>0.02195</v>
+        <v>0.02135</v>
       </c>
     </row>
     <row r="15">
@@ -14165,55 +14167,55 @@
         <v>35.3</v>
       </c>
       <c r="C15" t="n">
-        <v>11.79</v>
+        <v>11.78</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00085</v>
+        <v>0.00105</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00295</v>
+        <v>0.00225</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00555</v>
+        <v>0.00515</v>
       </c>
       <c r="G15" t="n">
-        <v>0.009549999999999999</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0155</v>
+        <v>0.01505</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02395</v>
+        <v>0.02175</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0323</v>
+        <v>0.0332</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0478</v>
+        <v>0.0487</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0581</v>
+        <v>0.06485</v>
       </c>
       <c r="M15" t="n">
-        <v>0.08495</v>
+        <v>0.08284999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.10415</v>
+        <v>0.10015</v>
       </c>
       <c r="O15" t="n">
-        <v>0.12605</v>
+        <v>0.1252</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1537</v>
+        <v>0.15985</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1752</v>
+        <v>0.173</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1354</v>
+        <v>0.1328</v>
       </c>
       <c r="S15" t="n">
-        <v>0.024</v>
+        <v>0.02425</v>
       </c>
     </row>
     <row r="16">
@@ -14226,55 +14228,55 @@
         <v>30.1</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63</v>
+        <v>13.62</v>
       </c>
       <c r="D16" t="n">
         <v>5e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>0.00025</v>
+        <v>0.0003</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0005</v>
+        <v>0.0009</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00145</v>
+        <v>0.0011</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00255</v>
+        <v>0.00295</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00555</v>
+        <v>0.00605</v>
       </c>
       <c r="J16" t="n">
-        <v>0.007849999999999999</v>
+        <v>0.0083</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01365</v>
+        <v>0.0144</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02285</v>
+        <v>0.0227</v>
       </c>
       <c r="M16" t="n">
-        <v>0.03515</v>
+        <v>0.03415</v>
       </c>
       <c r="N16" t="n">
-        <v>0.05365</v>
+        <v>0.0566</v>
       </c>
       <c r="O16" t="n">
-        <v>0.08245</v>
+        <v>0.07795000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1247</v>
+        <v>0.12215</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1902</v>
+        <v>0.1942</v>
       </c>
       <c r="R16" t="n">
-        <v>0.35535</v>
+        <v>0.35755</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1038</v>
+        <v>0.10065</v>
       </c>
     </row>
     <row r="17">
@@ -14299,43 +14301,43 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>5e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>5e-05</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>5e-05</v>
+        <v>0.0001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.00015</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.00045</v>
+        <v>0.00035</v>
       </c>
       <c r="M17" t="n">
-        <v>0.00075</v>
+        <v>0.0008</v>
       </c>
       <c r="N17" t="n">
-        <v>0.00245</v>
+        <v>0.00205</v>
       </c>
       <c r="O17" t="n">
         <v>0.00445</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0116</v>
+        <v>0.01405</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0344</v>
+        <v>0.0324</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1304</v>
+        <v>0.12745</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8153</v>
+        <v>0.81825</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan/report.xlsx
+++ b/output/japan/report.xlsx
@@ -15337,7 +15337,7 @@
         <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>204.7533443915498</v>
+        <v>204.7533443915497</v>
       </c>
       <c r="D6" t="n">
         <v>0.2916666666666667</v>
@@ -15405,7 +15405,7 @@
         <v>3990</v>
       </c>
       <c r="C8" t="n">
-        <v>29.75998964065702</v>
+        <v>29.75998964065703</v>
       </c>
       <c r="D8" t="n">
         <v>0.2491228070175439</v>
@@ -15417,7 +15417,7 @@
         <v>90</v>
       </c>
       <c r="G8" t="n">
-        <v>54.26504080002922</v>
+        <v>54.26504080002923</v>
       </c>
       <c r="H8" t="n">
         <v>0.2111111111111111</v>
@@ -15843,7 +15843,7 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>97.21521947451777</v>
+        <v>97.21521947451778</v>
       </c>
       <c r="D20" t="n">
         <v>0.08333333333333333</v>

--- a/output/japan/report.xlsx
+++ b/output/japan/report.xlsx
@@ -14422,87 +14422,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71.7</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="D2" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="E2" t="n">
-        <v>45.1</v>
+        <v>53.1</v>
       </c>
       <c r="F2" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="H2" t="n">
-        <v>28.3</v>
+        <v>32.6</v>
       </c>
       <c r="I2" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="J2" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="K2" t="n">
-        <v>16.9</v>
+        <v>18.3</v>
       </c>
       <c r="L2" t="n">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="M2" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79.7</v>
+        <v>71.5</v>
       </c>
       <c r="C3" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="D3" t="n">
-        <v>4.15</v>
+        <v>3.05</v>
       </c>
       <c r="E3" t="n">
-        <v>47.4</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="G3" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="H3" t="n">
-        <v>27.2</v>
+        <v>28.7</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="K3" t="n">
-        <v>15.4</v>
+        <v>16.9</v>
       </c>
       <c r="L3" t="n">
-        <v>5.25</v>
+        <v>4.85</v>
       </c>
       <c r="M3" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="4">
@@ -14512,7 +14512,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="C4" t="n">
         <v>1.3</v>
@@ -14521,31 +14521,31 @@
         <v>3.4</v>
       </c>
       <c r="E4" t="n">
-        <v>43.3</v>
+        <v>42.4</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="G4" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="H4" t="n">
-        <v>24.1</v>
+        <v>26.2</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J4" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="K4" t="n">
-        <v>13</v>
+        <v>13.9</v>
       </c>
       <c r="L4" t="n">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="5">
@@ -14555,34 +14555,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67.09999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="C5" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="D5" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="E5" t="n">
-        <v>39.4</v>
+        <v>34.8</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="G5" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="H5" t="n">
-        <v>22.3</v>
+        <v>21.9</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J5" t="n">
         <v>1.25</v>
       </c>
       <c r="K5" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="L5" t="n">
         <v>6.5</v>
@@ -14598,37 +14598,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>72.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C6" t="n">
         <v>1.32</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="E6" t="n">
-        <v>40.3</v>
+        <v>45.8</v>
       </c>
       <c r="F6" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="H6" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="I6" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
         <v>1.25</v>
       </c>
       <c r="K6" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="L6" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="M6" t="n">
         <v>1.11</v>
@@ -14641,25 +14641,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>65.5</v>
+        <v>65.7</v>
       </c>
       <c r="C7" t="n">
         <v>1.45</v>
       </c>
       <c r="D7" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="E7" t="n">
-        <v>33.1</v>
+        <v>28.2</v>
       </c>
       <c r="F7" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="G7" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="H7" t="n">
-        <v>15.7</v>
+        <v>15.1</v>
       </c>
       <c r="I7" t="n">
         <v>5.25</v>
@@ -14668,10 +14668,10 @@
         <v>1.16</v>
       </c>
       <c r="K7" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="L7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -14684,40 +14684,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="D8" t="n">
         <v>1.8</v>
       </c>
       <c r="E8" t="n">
-        <v>23.3</v>
+        <v>22.3</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="G8" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="J8" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="K8" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="9">
@@ -14727,117 +14727,117 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52.2</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
         <v>1.8</v>
       </c>
       <c r="D9" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="E9" t="n">
-        <v>24.2</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="G9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H9" t="n">
-        <v>10.7</v>
+        <v>8.9</v>
       </c>
       <c r="I9" t="n">
-        <v>7.25</v>
+        <v>8.5</v>
       </c>
       <c r="J9" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49.8</v>
+        <v>33.8</v>
       </c>
       <c r="C10" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="D10" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="E10" t="n">
-        <v>21.8</v>
+        <v>13.7</v>
       </c>
       <c r="F10" t="n">
-        <v>3.85</v>
+        <v>5.75</v>
       </c>
       <c r="G10" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="H10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32.9</v>
+        <v>50.4</v>
       </c>
       <c r="C11" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="D11" t="n">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="E11" t="n">
-        <v>15.4</v>
+        <v>18.5</v>
       </c>
       <c r="F11" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="H11" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="I11" t="n">
         <v>11</v>
       </c>
       <c r="J11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="K11" t="n">
         <v>2.9</v>
@@ -14856,40 +14856,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50.2</v>
+        <v>49.6</v>
       </c>
       <c r="C12" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="D12" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="E12" t="n">
-        <v>20.1</v>
+        <v>16.3</v>
       </c>
       <c r="F12" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="H12" t="n">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J12" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="L12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="13">
@@ -14899,40 +14899,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="C13" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="D13" t="n">
         <v>1.45</v>
       </c>
       <c r="E13" t="n">
-        <v>13.8</v>
+        <v>11.2</v>
       </c>
       <c r="F13" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="H13" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="L13" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="M13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="14">
@@ -14942,7 +14942,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28.3</v>
+        <v>28.5</v>
       </c>
       <c r="C14" t="n">
         <v>3.05</v>
@@ -14951,25 +14951,25 @@
         <v>1.35</v>
       </c>
       <c r="E14" t="n">
-        <v>10.1</v>
+        <v>13.2</v>
       </c>
       <c r="F14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="L14" t="n">
         <v>51</v>
@@ -14985,7 +14985,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="C15" t="n">
         <v>3.4</v>
@@ -14994,7 +14994,7 @@
         <v>1.3</v>
       </c>
       <c r="E15" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="F15" t="n">
         <v>8.5</v>
@@ -15003,22 +15003,22 @@
         <v>1.09</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J15" t="n">
         <v>1.03</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="L15" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="M15" t="n">
-        <v>1.008</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="16">
@@ -15028,40 +15028,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20.3</v>
+        <v>19.9</v>
       </c>
       <c r="C16" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="D16" t="n">
         <v>1.22</v>
       </c>
       <c r="E16" t="n">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="I16" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="J16" t="n">
         <v>1.02</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="L16" t="n">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="M16" t="n">
-        <v>1.004</v>
+        <v>1.006</v>
       </c>
     </row>
     <row r="17">
@@ -15071,22 +15071,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27.1</v>
+        <v>26.4</v>
       </c>
       <c r="C17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="D17" t="n">
         <v>1.32</v>
       </c>
       <c r="E17" t="n">
-        <v>7.6</v>
+        <v>8.9</v>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="H17" t="n">
         <v>1.9</v>
@@ -15335,7 +15335,7 @@
         <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>204.7533443915498</v>
+        <v>204.7533443915497</v>
       </c>
       <c r="D6" t="n">
         <v>0.2916666666666667</v>
@@ -15517,7 +15517,7 @@
         <v>3600</v>
       </c>
       <c r="C11" t="n">
-        <v>40.88989855451107</v>
+        <v>40.88989855451108</v>
       </c>
       <c r="D11" t="n">
         <v>0.2436111111111111</v>
@@ -15841,7 +15841,7 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>97.21521947451777</v>
+        <v>97.21521947451778</v>
       </c>
       <c r="D20" t="n">
         <v>0.08333333333333333</v>
@@ -16591,16 +16591,16 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>61.7</v>
+        <v>61.5</v>
       </c>
       <c r="F2" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="G2" t="n">
         <v>2.35</v>
       </c>
       <c r="H2" t="n">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="I2" t="n">
         <v>2.45</v>
@@ -16632,16 +16632,16 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>60.6</v>
+        <v>60.7</v>
       </c>
       <c r="F3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="G3" t="n">
         <v>2.3</v>
       </c>
       <c r="H3" t="n">
-        <v>34.9</v>
+        <v>35.1</v>
       </c>
       <c r="I3" t="n">
         <v>2.55</v>
@@ -16650,7 +16650,7 @@
         <v>1.47</v>
       </c>
       <c r="K3" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="L3" t="n">
         <v>4.3</v>
@@ -16673,16 +16673,16 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>58.8</v>
+        <v>58.7</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G4" t="n">
         <v>2.2</v>
       </c>
       <c r="H4" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="I4" t="n">
         <v>2.75</v>
@@ -16691,7 +16691,7 @@
         <v>1.42</v>
       </c>
       <c r="K4" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="L4" t="n">
         <v>4.85</v>
@@ -16707,16 +16707,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68.5</v>
+        <v>68.7</v>
       </c>
       <c r="C5" t="n">
         <v>1.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="E5" t="n">
-        <v>44.4</v>
+        <v>44.6</v>
       </c>
       <c r="F5" t="n">
         <v>2.05</v>
@@ -16757,16 +16757,16 @@
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="H6" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="I6" t="n">
         <v>3.8</v>
@@ -16791,16 +16791,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="C7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="D7" t="n">
         <v>4.6</v>
       </c>
       <c r="E7" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="F7" t="n">
         <v>2.6</v>
@@ -16809,16 +16809,16 @@
         <v>1.45</v>
       </c>
       <c r="H7" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="I7" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
         <v>1.13</v>
       </c>
       <c r="K7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L7" t="n">
         <v>13</v>
@@ -16834,13 +16834,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C8" t="n">
         <v>1.33</v>
       </c>
       <c r="D8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="E8" t="n">
         <v>29.4</v>
@@ -16852,7 +16852,7 @@
         <v>1.36</v>
       </c>
       <c r="H8" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="I8" t="n">
         <v>7</v>
@@ -16861,7 +16861,7 @@
         <v>1.11</v>
       </c>
       <c r="K8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
         <v>15</v>
@@ -16877,7 +16877,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>54.9</v>
       </c>
       <c r="C9" t="n">
         <v>1.7</v>
@@ -16886,16 +16886,16 @@
         <v>2.05</v>
       </c>
       <c r="E9" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="F9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G9" t="n">
         <v>1.25</v>
       </c>
       <c r="H9" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I9" t="n">
         <v>9</v>
@@ -16904,10 +16904,10 @@
         <v>1.08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
@@ -16920,10 +16920,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="C10" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="D10" t="n">
         <v>1.4</v>
@@ -16963,7 +16963,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
       <c r="C11" t="n">
         <v>2.05</v>
@@ -17006,10 +17006,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27.6</v>
+        <v>27.8</v>
       </c>
       <c r="C12" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="D12" t="n">
         <v>1.33</v>
@@ -17024,7 +17024,7 @@
         <v>1.05</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I12" t="n">
         <v>51</v>
@@ -17039,7 +17039,7 @@
         <v>201</v>
       </c>
       <c r="M12" t="n">
-        <v>1.002</v>
+        <v>1.003</v>
       </c>
     </row>
     <row r="13">
@@ -17049,13 +17049,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="C13" t="n">
         <v>4.6</v>
       </c>
       <c r="D13" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="E13" t="n">
         <v>2.7</v>

--- a/output/japan/report.xlsx
+++ b/output/japan/report.xlsx
@@ -15457,7 +15457,7 @@
         <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>204.7533443915497</v>
+        <v>204.7533443915498</v>
       </c>
       <c r="D6" t="n">
         <v>0.2916666666666667</v>
@@ -15963,7 +15963,7 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>97.21521947451778</v>
+        <v>97.21521947451777</v>
       </c>
       <c r="D20" t="n">
         <v>0.08333333333333333</v>

--- a/output/japan/report.xlsx
+++ b/output/japan/report.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j1 table" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j1 next" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j1 outrights" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j1 positions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j2 table" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j2 next" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j2 outrights" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j2 positions" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j3 table" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j3 next" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j3 outrights" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="j3 positions" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jfl table" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jfl next" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jfl outrights" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jfl positions" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="emperors_cup outrights" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="emperors_cup next" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="league_cup outrights" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Ratings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Parameters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="j1 table" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="j1 next" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="j1 outrights" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="j1 positions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="j2 table" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="j2 next" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="j2 outrights" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="j2 positions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="j3 table" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="j3 next" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="j3 outrights" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="j3 positions" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="jfl table" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="jfl next" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="jfl outrights" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="jfl positions" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="emperors_cup outrights" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="emperors_cup next" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="league_cup outrights" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37,16 +37,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -57,7 +54,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -65,21 +62,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,27 +437,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>elo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>tilt</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>last_match</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>last_tournament</t>
         </is>
@@ -5182,117 +5170,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>exp_pts</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>exp_pos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>P12</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>P13</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>P14</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>P15</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>P16</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>P17</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>P18</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>P19</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>P20</t>
         </is>
@@ -6773,52 +6761,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>GF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>GD</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Pts</t>
         </is>
@@ -7519,97 +7507,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>away</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>home_elo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>away_elo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_diff_adj</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_tilt</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>away_tilt</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>probX</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>expg1</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>expg2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>odds1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>oddsX</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>odds2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>oddsO25</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>oddsU25</t>
         </is>
@@ -8930,67 +8918,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Winner %</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Winner Yes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Winner No</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Top 2 %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Top 2 Yes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Top 2 No</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Top 6 %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Top 6 Yes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Top 6 No</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Bottom 2 %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Bottom 2 Yes</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Bottom 2 No</t>
         </is>
@@ -9847,117 +9835,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>exp_pts</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>exp_pos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>P12</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>P13</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>P14</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>P15</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>P16</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>P17</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>P18</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>P19</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>P20</t>
         </is>
@@ -11438,52 +11426,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>GF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>GD</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Pts</t>
         </is>
@@ -12048,97 +12036,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>away</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>home_elo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>away_elo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_diff_adj</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_tilt</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>away_tilt</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>probX</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>expg1</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>expg2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>odds1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>oddsX</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>odds2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>oddsO25</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>oddsU25</t>
         </is>
@@ -12809,52 +12797,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Winner %</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Winner Yes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Winner No</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Top 4 %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Top 4 Yes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Top 4 No</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Bottom 2 %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Bottom 2 Yes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Bottom 2 No</t>
         </is>
@@ -13415,97 +13403,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>exp_pts</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>exp_pos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>P12</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>P13</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>P14</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>P15</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>P16</t>
         </is>
@@ -14502,67 +14490,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Reach QF %</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Reach QF Yes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Reach QF No</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Reach SF %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Reach SF Yes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Reach SF No</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Reach Final %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Reach Final Yes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Reach Final No</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Winner %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Winner Yes</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Winner No</t>
         </is>
@@ -15271,62 +15259,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tournament</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>matches</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>hfa_elo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>draw_rate</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>avg_goals_x</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>season_matches</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>season_hfa_elo</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>season_draw_rate</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>season_avg_goals</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>elo_hfa</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>avg_goals_y</t>
         </is>
@@ -15484,7 +15472,7 @@
         <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>204.7533443915497</v>
+        <v>204.7533443915498</v>
       </c>
       <c r="D6" t="n">
         <v>0.2916666666666667</v>
@@ -15990,7 +15978,7 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>97.21521947451778</v>
+        <v>97.21521947451777</v>
       </c>
       <c r="D20" t="n">
         <v>0.08333333333333333</v>
@@ -16029,97 +16017,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>away</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>home_elo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>away_elo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_diff_adj</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_tilt</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>away_tilt</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>probX</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>expg1</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>expg2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>odds1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>oddsX</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>odds2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>oddsO25</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>oddsU25</t>
         </is>
@@ -16660,67 +16648,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Reach QF %</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Reach QF Yes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Reach QF No</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Reach SF %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Reach SF Yes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Reach SF No</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Reach Final %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Reach Final Yes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Reach Final No</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Winner %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Winner Yes</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Winner No</t>
         </is>
@@ -17209,52 +17197,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>GF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>GD</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Pts</t>
         </is>
@@ -17955,97 +17943,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>away</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>home_elo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>away_elo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_diff_adj</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_tilt</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>away_tilt</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>probX</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>expg1</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>expg2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>odds1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>oddsX</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>odds2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>oddsO25</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>oddsU25</t>
         </is>
@@ -18716,52 +18704,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Winner %</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Winner Yes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Winner No</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Top 3 %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Top 3 Yes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Top 3 No</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Relegation %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Relegation Yes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Relegation No</t>
         </is>
@@ -19426,117 +19414,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>exp_pts</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>exp_pos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>P12</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>P13</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>P14</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>P15</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>P16</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>P17</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>P18</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>P19</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>P20</t>
         </is>
@@ -21017,52 +21005,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>GF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>GD</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Pts</t>
         </is>
@@ -21763,97 +21751,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>away</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>home_elo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>away_elo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_diff_adj</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_tilt</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>away_tilt</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>prob1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>probX</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>prob2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>expg1</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>expg2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>odds1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>oddsX</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>odds2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>oddsO25</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>oddsU25</t>
         </is>
@@ -23174,67 +23162,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Winner %</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Winner Yes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Winner No</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Top 2 %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Top 2 Yes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Top 2 No</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Top 6 %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Top 6 Yes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Top 6 No</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Relegation %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Relegation Yes</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Relegation No</t>
         </is>

--- a/output/japan/report.xlsx
+++ b/output/japan/report.xlsx
@@ -15472,7 +15472,7 @@
         <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>204.7533443915498</v>
+        <v>204.7533443915497</v>
       </c>
       <c r="D6" t="n">
         <v>0.2916666666666667</v>
@@ -15978,7 +15978,7 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>97.21521947451777</v>
+        <v>97.21521947451778</v>
       </c>
       <c r="D20" t="n">
         <v>0.08333333333333333</v>
